--- a/MEDIÇÕES_CONSOLIDADO.xlsx
+++ b/MEDIÇÕES_CONSOLIDADO.xlsx
@@ -3078,19 +3078,19 @@
         </is>
       </c>
       <c r="M9" s="7" t="n">
-        <v>7755221.32</v>
+        <v>4610802.86</v>
       </c>
       <c r="N9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O9" s="7" t="n">
-        <v>29490283.93</v>
+        <v>26345865.47</v>
       </c>
       <c r="P9" s="9" t="n">
-        <v>0.4870912202951318</v>
+        <v>0.4351548391997349</v>
       </c>
       <c r="Q9" s="7" t="n">
-        <v>31053373.4</v>
+        <v>34197791.86</v>
       </c>
       <c r="R9" s="7" t="n">
         <v>0</v>
@@ -3237,7 +3237,7 @@
         <v>0</v>
       </c>
       <c r="BN9" s="7" t="n">
-        <v>1572209.23</v>
+        <v>-1572209.23</v>
       </c>
       <c r="BO9" s="7" t="n">
         <v>873599.05</v>
@@ -4210,19 +4210,19 @@
         </is>
       </c>
       <c r="M13" s="7" t="n">
-        <v>0</v>
+        <v>842876.36</v>
       </c>
       <c r="N13" s="7" t="n">
-        <v>0</v>
+        <v>1284711.9</v>
       </c>
       <c r="O13" s="7" t="n">
-        <v>0</v>
+        <v>2127588.26</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>0</v>
+        <v>0.271098746870728</v>
       </c>
       <c r="Q13" s="7" t="n">
-        <v>7848019.53</v>
+        <v>5720431.27</v>
       </c>
       <c r="R13" s="7" t="n">
         <v>0</v>
@@ -4402,10 +4402,10 @@
         <v>0</v>
       </c>
       <c r="BY13" s="7" t="n">
-        <v>0</v>
+        <v>842876.36</v>
       </c>
       <c r="BZ13" s="7" t="n">
-        <v>0</v>
+        <v>1284711.9</v>
       </c>
       <c r="CA13" s="7" t="n">
         <v>0</v>
@@ -4738,9 +4738,15 @@
           <t>CIVIS</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="n">
+        <v>-370</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>46810</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>46440</v>
+      </c>
       <c r="G15" s="7" t="n">
         <v>1302281.25</v>
       </c>
@@ -5619,19 +5625,19 @@
         </is>
       </c>
       <c r="M18" s="7" t="n">
-        <v>4712016.07</v>
+        <v>-748873.51</v>
       </c>
       <c r="N18" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="7" t="n">
-        <v>29153437.02</v>
+        <v>20145177.51</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>0.4438806423451114</v>
+        <v>0.3067238462195937</v>
       </c>
       <c r="Q18" s="7" t="n">
-        <v>36525113.11</v>
+        <v>45533372.62</v>
       </c>
       <c r="R18" s="7" t="n">
         <v>0</v>
@@ -5724,31 +5730,31 @@
         <v>285800.97</v>
       </c>
       <c r="AV18" s="7" t="n">
-        <v>499897.23</v>
+        <v>-594778.3199999999</v>
       </c>
       <c r="AW18" s="7" t="n">
-        <v>127585.61</v>
+        <v>-127585.61</v>
       </c>
       <c r="AX18" s="7" t="n">
-        <v>34252.28</v>
+        <v>-34252.28</v>
       </c>
       <c r="AY18" s="7" t="n">
-        <v>135219.39</v>
+        <v>-135219.39</v>
       </c>
       <c r="AZ18" s="7" t="n">
-        <v>273099.03</v>
+        <v>-273099.03</v>
       </c>
       <c r="BA18" s="7" t="n">
-        <v>60128.5</v>
+        <v>-60128.5</v>
       </c>
       <c r="BB18" s="7" t="n">
-        <v>508655.36</v>
+        <v>-508655.36</v>
       </c>
       <c r="BC18" s="7" t="n">
-        <v>56896.96</v>
+        <v>-56896.96</v>
       </c>
       <c r="BD18" s="7" t="n">
-        <v>30510.06</v>
+        <v>-30510.06</v>
       </c>
       <c r="BE18" s="7" t="n">
         <v>59095.88</v>
@@ -5796,19 +5802,19 @@
         <v>0</v>
       </c>
       <c r="BT18" s="7" t="n">
-        <v>229823.05</v>
+        <v>-229823.05</v>
       </c>
       <c r="BU18" s="7" t="n">
-        <v>14426.39</v>
+        <v>-14426.39</v>
       </c>
       <c r="BV18" s="7" t="n">
-        <v>1114030.22</v>
+        <v>-1114030.22</v>
       </c>
       <c r="BW18" s="7" t="n">
-        <v>208164.15</v>
+        <v>-208164.15</v>
       </c>
       <c r="BX18" s="7" t="n">
-        <v>1164000.98</v>
+        <v>-1164000.98</v>
       </c>
       <c r="BY18" s="7" t="n">
         <v>1981571.28</v>
@@ -8120,7 +8126,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>330018/000569/2021</t>
+          <t>330018/000681/2021</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -8129,16 +8135,16 @@
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1599</v>
+        <v>1450</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>44623</v>
+        <v>44641</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>46222</v>
+        <v>46091</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>45726170.25</v>
+        <v>43796954.98</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -8166,19 +8172,19 @@
         </is>
       </c>
       <c r="M27" s="7" t="n">
-        <v>5250302.04</v>
+        <v>8362397.14</v>
       </c>
       <c r="N27" s="7" t="n">
-        <v>499862.54</v>
+        <v>0</v>
       </c>
       <c r="O27" s="7" t="n">
-        <v>36377601.26</v>
+        <v>42048979.52</v>
       </c>
       <c r="P27" s="9" t="n">
-        <v>0.7955532042397536</v>
+        <v>0.9600891098297082</v>
       </c>
       <c r="Q27" s="7" t="n">
-        <v>9348568.99</v>
+        <v>1747975.46</v>
       </c>
       <c r="R27" s="7" t="n">
         <v>0</v>
@@ -8226,142 +8232,142 @@
         <v>0</v>
       </c>
       <c r="AG27" s="7" t="n">
-        <v>1204582.26</v>
+        <v>1322646.63</v>
       </c>
       <c r="AH27" s="7" t="n">
-        <v>1757227.52</v>
+        <v>259186.89</v>
       </c>
       <c r="AI27" s="7" t="n">
-        <v>3544813.72</v>
+        <v>906196.47</v>
       </c>
       <c r="AJ27" s="7" t="n">
-        <v>2662837.02</v>
+        <v>901242.74</v>
       </c>
       <c r="AK27" s="7" t="n">
-        <v>335644.95</v>
+        <v>0</v>
       </c>
       <c r="AL27" s="7" t="n">
-        <v>4794234.02</v>
+        <v>942216.9300000001</v>
       </c>
       <c r="AM27" s="7" t="n">
-        <v>2840498.07</v>
+        <v>729529.63</v>
       </c>
       <c r="AN27" s="7" t="n">
-        <v>2423189.51</v>
+        <v>904885.4399999999</v>
       </c>
       <c r="AO27" s="7" t="n">
-        <v>1499279.53</v>
+        <v>727233.4</v>
       </c>
       <c r="AP27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AQ27" s="7" t="n">
-        <v>2887209.93</v>
+        <v>1173096.21</v>
       </c>
       <c r="AR27" s="7" t="n">
-        <v>1484140.51</v>
+        <v>665680.85</v>
       </c>
       <c r="AS27" s="7" t="n">
-        <v>654423.03</v>
+        <v>754744.55</v>
       </c>
       <c r="AT27" s="7" t="n">
-        <v>847458.4</v>
+        <v>815425.79</v>
       </c>
       <c r="AU27" s="7" t="n">
-        <v>996428.8</v>
+        <v>827149.58</v>
       </c>
       <c r="AV27" s="7" t="n">
-        <v>213985.3</v>
+        <v>536795.13</v>
       </c>
       <c r="AW27" s="7" t="n">
-        <v>122099.63</v>
+        <v>606470.7</v>
       </c>
       <c r="AX27" s="7" t="n">
-        <v>22712.68</v>
+        <v>608799.9399999999</v>
       </c>
       <c r="AY27" s="7" t="n">
-        <v>11075.14</v>
+        <v>806871.74</v>
       </c>
       <c r="AZ27" s="7" t="n">
-        <v>355697.23</v>
+        <v>443107.49</v>
       </c>
       <c r="BA27" s="7" t="n">
-        <v>38575.01</v>
+        <v>289836.99</v>
       </c>
       <c r="BB27" s="7" t="n">
-        <v>95773.89</v>
+        <v>650306.5</v>
       </c>
       <c r="BC27" s="7" t="n">
-        <v>88467.31</v>
+        <v>467855.5</v>
       </c>
       <c r="BD27" s="7" t="n">
-        <v>74942.06</v>
+        <v>951169.12</v>
       </c>
       <c r="BE27" s="7" t="n">
-        <v>72616.48</v>
+        <v>3933611.63</v>
       </c>
       <c r="BF27" s="7" t="n">
-        <v>96643.81</v>
+        <v>1775490.1</v>
       </c>
       <c r="BG27" s="7" t="n">
-        <v>37894.61</v>
+        <v>1935304.86</v>
       </c>
       <c r="BH27" s="7" t="n">
-        <v>22383.33</v>
+        <v>3230614.04</v>
       </c>
       <c r="BI27" s="7" t="n">
-        <v>804674.41</v>
+        <v>924327.16</v>
       </c>
       <c r="BJ27" s="7" t="n">
-        <v>380702.03</v>
+        <v>1907541.45</v>
       </c>
       <c r="BK27" s="7" t="n">
-        <v>257226.49</v>
+        <v>619218.05</v>
       </c>
       <c r="BL27" s="7" t="n">
-        <v>0</v>
+        <v>2197992</v>
       </c>
       <c r="BM27" s="7" t="n">
-        <v>0</v>
+        <v>872034.87</v>
       </c>
       <c r="BN27" s="7" t="n">
-        <v>146829.08</v>
+        <v>408232.85</v>
       </c>
       <c r="BO27" s="7" t="n">
-        <v>195771.65</v>
+        <v>441742.25</v>
       </c>
       <c r="BP27" s="7" t="n">
-        <v>163538.64</v>
+        <v>579038.64</v>
       </c>
       <c r="BQ27" s="7" t="n">
-        <v>60019.79</v>
+        <v>1083708.11</v>
       </c>
       <c r="BR27" s="7" t="n">
-        <v>333479.78</v>
+        <v>714576.99</v>
       </c>
       <c r="BS27" s="7" t="n">
-        <v>310210.43</v>
+        <v>785422.9399999999</v>
       </c>
       <c r="BT27" s="7" t="n">
-        <v>289529.71</v>
+        <v>780132.95</v>
       </c>
       <c r="BU27" s="7" t="n">
-        <v>532646.8</v>
+        <v>718055.63</v>
       </c>
       <c r="BV27" s="7" t="n">
-        <v>485170.46</v>
+        <v>1495738.36</v>
       </c>
       <c r="BW27" s="7" t="n">
-        <v>1012783.71</v>
+        <v>810543.05</v>
       </c>
       <c r="BX27" s="7" t="n">
-        <v>883134.2</v>
+        <v>210535.57</v>
       </c>
       <c r="BY27" s="7" t="n">
-        <v>837187.79</v>
+        <v>334669.8</v>
       </c>
       <c r="BZ27" s="7" t="n">
-        <v>499862.54</v>
+        <v>0</v>
       </c>
       <c r="CA27" s="7" t="n">
         <v>0</v>
@@ -8403,7 +8409,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>330018/000681/2021</t>
+          <t>330018/000569/2021</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -8412,16 +8418,16 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1450</v>
+        <v>1599</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>44641</v>
+        <v>44623</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>46091</v>
+        <v>46222</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>43796954.98</v>
+        <v>45726170.25</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
@@ -8449,19 +8455,19 @@
         </is>
       </c>
       <c r="M28" s="7" t="n">
-        <v>8362397.14</v>
+        <v>5250302.04</v>
       </c>
       <c r="N28" s="7" t="n">
-        <v>0</v>
+        <v>499862.54</v>
       </c>
       <c r="O28" s="7" t="n">
-        <v>42048979.52</v>
+        <v>36377601.26</v>
       </c>
       <c r="P28" s="9" t="n">
-        <v>0.9600891098297082</v>
+        <v>0.7955532042397536</v>
       </c>
       <c r="Q28" s="7" t="n">
-        <v>1747975.46</v>
+        <v>9348568.99</v>
       </c>
       <c r="R28" s="7" t="n">
         <v>0</v>
@@ -8509,142 +8515,142 @@
         <v>0</v>
       </c>
       <c r="AG28" s="7" t="n">
-        <v>1322646.63</v>
+        <v>1204582.26</v>
       </c>
       <c r="AH28" s="7" t="n">
-        <v>259186.89</v>
+        <v>1757227.52</v>
       </c>
       <c r="AI28" s="7" t="n">
-        <v>906196.47</v>
+        <v>3544813.72</v>
       </c>
       <c r="AJ28" s="7" t="n">
-        <v>901242.74</v>
+        <v>2662837.02</v>
       </c>
       <c r="AK28" s="7" t="n">
-        <v>0</v>
+        <v>335644.95</v>
       </c>
       <c r="AL28" s="7" t="n">
-        <v>942216.9300000001</v>
+        <v>4794234.02</v>
       </c>
       <c r="AM28" s="7" t="n">
-        <v>729529.63</v>
+        <v>2840498.07</v>
       </c>
       <c r="AN28" s="7" t="n">
-        <v>904885.4399999999</v>
+        <v>2423189.51</v>
       </c>
       <c r="AO28" s="7" t="n">
-        <v>727233.4</v>
+        <v>1499279.53</v>
       </c>
       <c r="AP28" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AQ28" s="7" t="n">
-        <v>1173096.21</v>
+        <v>2887209.93</v>
       </c>
       <c r="AR28" s="7" t="n">
-        <v>665680.85</v>
+        <v>1484140.51</v>
       </c>
       <c r="AS28" s="7" t="n">
-        <v>754744.55</v>
+        <v>654423.03</v>
       </c>
       <c r="AT28" s="7" t="n">
-        <v>815425.79</v>
+        <v>847458.4</v>
       </c>
       <c r="AU28" s="7" t="n">
-        <v>827149.58</v>
+        <v>996428.8</v>
       </c>
       <c r="AV28" s="7" t="n">
-        <v>536795.13</v>
+        <v>213985.3</v>
       </c>
       <c r="AW28" s="7" t="n">
-        <v>606470.7</v>
+        <v>122099.63</v>
       </c>
       <c r="AX28" s="7" t="n">
-        <v>608799.9399999999</v>
+        <v>22712.68</v>
       </c>
       <c r="AY28" s="7" t="n">
-        <v>806871.74</v>
+        <v>11075.14</v>
       </c>
       <c r="AZ28" s="7" t="n">
-        <v>443107.49</v>
+        <v>355697.23</v>
       </c>
       <c r="BA28" s="7" t="n">
-        <v>289836.99</v>
+        <v>38575.01</v>
       </c>
       <c r="BB28" s="7" t="n">
-        <v>650306.5</v>
+        <v>95773.89</v>
       </c>
       <c r="BC28" s="7" t="n">
-        <v>467855.5</v>
+        <v>88467.31</v>
       </c>
       <c r="BD28" s="7" t="n">
-        <v>951169.12</v>
+        <v>74942.06</v>
       </c>
       <c r="BE28" s="7" t="n">
-        <v>3933611.63</v>
+        <v>72616.48</v>
       </c>
       <c r="BF28" s="7" t="n">
-        <v>1775490.1</v>
+        <v>96643.81</v>
       </c>
       <c r="BG28" s="7" t="n">
-        <v>1935304.86</v>
+        <v>37894.61</v>
       </c>
       <c r="BH28" s="7" t="n">
-        <v>3230614.04</v>
+        <v>22383.33</v>
       </c>
       <c r="BI28" s="7" t="n">
-        <v>924327.16</v>
+        <v>804674.41</v>
       </c>
       <c r="BJ28" s="7" t="n">
-        <v>1907541.45</v>
+        <v>380702.03</v>
       </c>
       <c r="BK28" s="7" t="n">
-        <v>619218.05</v>
+        <v>257226.49</v>
       </c>
       <c r="BL28" s="7" t="n">
-        <v>2197992</v>
+        <v>0</v>
       </c>
       <c r="BM28" s="7" t="n">
-        <v>872034.87</v>
+        <v>0</v>
       </c>
       <c r="BN28" s="7" t="n">
-        <v>408232.85</v>
+        <v>146829.08</v>
       </c>
       <c r="BO28" s="7" t="n">
-        <v>441742.25</v>
+        <v>195771.65</v>
       </c>
       <c r="BP28" s="7" t="n">
-        <v>579038.64</v>
+        <v>163538.64</v>
       </c>
       <c r="BQ28" s="7" t="n">
-        <v>1083708.11</v>
+        <v>60019.79</v>
       </c>
       <c r="BR28" s="7" t="n">
-        <v>714576.99</v>
+        <v>333479.78</v>
       </c>
       <c r="BS28" s="7" t="n">
-        <v>785422.9399999999</v>
+        <v>310210.43</v>
       </c>
       <c r="BT28" s="7" t="n">
-        <v>780132.95</v>
+        <v>289529.71</v>
       </c>
       <c r="BU28" s="7" t="n">
-        <v>718055.63</v>
+        <v>532646.8</v>
       </c>
       <c r="BV28" s="7" t="n">
-        <v>1495738.36</v>
+        <v>485170.46</v>
       </c>
       <c r="BW28" s="7" t="n">
-        <v>810543.05</v>
+        <v>1012783.71</v>
       </c>
       <c r="BX28" s="7" t="n">
-        <v>210535.57</v>
+        <v>883134.2</v>
       </c>
       <c r="BY28" s="7" t="n">
-        <v>334669.8</v>
+        <v>837187.79</v>
       </c>
       <c r="BZ28" s="7" t="n">
-        <v>0</v>
+        <v>499862.54</v>
       </c>
       <c r="CA28" s="7" t="n">
         <v>0</v>
@@ -12131,16 +12137,16 @@
         <v>11147804.81</v>
       </c>
       <c r="N41" s="7" t="n">
-        <v>1980228.97</v>
+        <v>3468001.87</v>
       </c>
       <c r="O41" s="7" t="n">
-        <v>13128033.78</v>
+        <v>14615806.68</v>
       </c>
       <c r="P41" s="9" t="n">
-        <v>0.5427619407936779</v>
+        <v>0.6042720283053692</v>
       </c>
       <c r="Q41" s="7" t="n">
-        <v>11059428.15</v>
+        <v>9571655.25</v>
       </c>
       <c r="R41" s="7" t="n">
         <v>0</v>
@@ -12326,7 +12332,7 @@
         <v>1980228.97</v>
       </c>
       <c r="CA41" s="7" t="n">
-        <v>0</v>
+        <v>1487772.9</v>
       </c>
       <c r="CB41" s="7" t="n">
         <v>0</v>
@@ -13826,19 +13832,19 @@
         </is>
       </c>
       <c r="M47" s="7" t="n">
-        <v>54247300.54</v>
+        <v>54247297.54</v>
       </c>
       <c r="N47" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O47" s="7" t="n">
-        <v>54247300.54</v>
+        <v>54247297.54</v>
       </c>
       <c r="P47" s="9" t="n">
-        <v>0.5169375489655642</v>
+        <v>0.5169375203777334</v>
       </c>
       <c r="Q47" s="7" t="n">
-        <v>50692456.01</v>
+        <v>50692459.01</v>
       </c>
       <c r="R47" s="7" t="n">
         <v>0</v>
@@ -14009,7 +14015,7 @@
         <v>27887043.3</v>
       </c>
       <c r="BV47" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BW47" s="7" t="n">
         <v>0</v>
@@ -15181,7 +15187,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>330018/000423/2021</t>
+          <t>330018/000424/2021</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -15199,7 +15205,7 @@
         <v>45329</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>84484346.70999999</v>
+        <v>69450000</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
@@ -15229,13 +15235,13 @@
         <v>0</v>
       </c>
       <c r="O3" s="7" t="n">
-        <v>75957961.34</v>
+        <v>32682339.39</v>
       </c>
       <c r="P3" s="9" t="n">
-        <v>0.8990773356007883</v>
+        <v>0.4705880401727862</v>
       </c>
       <c r="Q3" s="7" t="n">
-        <v>8526385.369999999</v>
+        <v>36767660.61</v>
       </c>
       <c r="R3" s="7" t="n">
         <v>0</v>
@@ -15256,55 +15262,55 @@
         <v>0</v>
       </c>
       <c r="X3" s="7" t="n">
-        <v>37978980.67</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Z3" s="7" t="n">
-        <v>3196722.51</v>
+        <v>3345192.94</v>
       </c>
       <c r="AA3" s="7" t="n">
-        <v>2513879.17</v>
+        <v>3421703.14</v>
       </c>
       <c r="AB3" s="7" t="n">
-        <v>6884270.64</v>
+        <v>3206803.11</v>
       </c>
       <c r="AC3" s="7" t="n">
-        <v>6063547.32</v>
+        <v>4041013.22</v>
       </c>
       <c r="AD3" s="7" t="n">
-        <v>5103543.55</v>
+        <v>4898342.26</v>
       </c>
       <c r="AE3" s="7" t="n">
-        <v>2128722.27</v>
+        <v>2613441.33</v>
       </c>
       <c r="AF3" s="7" t="n">
-        <v>2027531.46</v>
+        <v>2016538.08</v>
       </c>
       <c r="AG3" s="7" t="n">
-        <v>2096828.26</v>
+        <v>2018030.13</v>
       </c>
       <c r="AH3" s="7" t="n">
-        <v>1852452.82</v>
+        <v>1591520.36</v>
       </c>
       <c r="AI3" s="7" t="n">
-        <v>1185028.45</v>
+        <v>1004318.24</v>
       </c>
       <c r="AJ3" s="7" t="n">
-        <v>2299328.44</v>
+        <v>2268052.17</v>
       </c>
       <c r="AK3" s="7" t="n">
-        <v>302435.78</v>
+        <v>524475.5</v>
       </c>
       <c r="AL3" s="7" t="n">
-        <v>1374521.12</v>
+        <v>955557.1899999999</v>
       </c>
       <c r="AM3" s="7" t="n">
-        <v>411572.18</v>
+        <v>386041</v>
       </c>
       <c r="AN3" s="7" t="n">
-        <v>538596.7</v>
+        <v>391310.72</v>
       </c>
       <c r="AO3" s="7" t="n">
         <v>0</v>
@@ -15460,7 +15466,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>330018/000424/2021</t>
+          <t>330018/000423/2021</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -15478,7 +15484,7 @@
         <v>45329</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>69450000</v>
+        <v>84484346.70999999</v>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
@@ -15508,13 +15514,13 @@
         <v>0</v>
       </c>
       <c r="O4" s="7" t="n">
-        <v>32682339.39</v>
+        <v>75957961.34</v>
       </c>
       <c r="P4" s="9" t="n">
-        <v>0.4705880401727862</v>
+        <v>0.8990773356007883</v>
       </c>
       <c r="Q4" s="7" t="n">
-        <v>36767660.61</v>
+        <v>8526385.369999999</v>
       </c>
       <c r="R4" s="7" t="n">
         <v>0</v>
@@ -15535,55 +15541,55 @@
         <v>0</v>
       </c>
       <c r="X4" s="7" t="n">
-        <v>0</v>
+        <v>37978980.67</v>
       </c>
       <c r="Y4" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Z4" s="7" t="n">
-        <v>3345192.94</v>
+        <v>3196722.51</v>
       </c>
       <c r="AA4" s="7" t="n">
-        <v>3421703.14</v>
+        <v>2513879.17</v>
       </c>
       <c r="AB4" s="7" t="n">
-        <v>3206803.11</v>
+        <v>6884270.64</v>
       </c>
       <c r="AC4" s="7" t="n">
-        <v>4041013.22</v>
+        <v>6063547.32</v>
       </c>
       <c r="AD4" s="7" t="n">
-        <v>4898342.26</v>
+        <v>5103543.55</v>
       </c>
       <c r="AE4" s="7" t="n">
-        <v>2613441.33</v>
+        <v>2128722.27</v>
       </c>
       <c r="AF4" s="7" t="n">
-        <v>2016538.08</v>
+        <v>2027531.46</v>
       </c>
       <c r="AG4" s="7" t="n">
-        <v>2018030.13</v>
+        <v>2096828.26</v>
       </c>
       <c r="AH4" s="7" t="n">
-        <v>1591520.36</v>
+        <v>1852452.82</v>
       </c>
       <c r="AI4" s="7" t="n">
-        <v>1004318.24</v>
+        <v>1185028.45</v>
       </c>
       <c r="AJ4" s="7" t="n">
-        <v>2268052.17</v>
+        <v>2299328.44</v>
       </c>
       <c r="AK4" s="7" t="n">
-        <v>524475.5</v>
+        <v>302435.78</v>
       </c>
       <c r="AL4" s="7" t="n">
-        <v>955557.1899999999</v>
+        <v>1374521.12</v>
       </c>
       <c r="AM4" s="7" t="n">
-        <v>386041</v>
+        <v>411572.18</v>
       </c>
       <c r="AN4" s="7" t="n">
-        <v>391310.72</v>
+        <v>538596.7</v>
       </c>
       <c r="AO4" s="7" t="n">
         <v>0</v>
@@ -18553,7 +18559,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>170026/002680/2021</t>
+          <t>330018/001037/2021</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -18562,27 +18568,23 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>567</v>
+        <v>-45</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>44918</v>
+        <v>45061</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>45485</v>
+        <v>45016</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>4645152.25</v>
+        <v>3607367.42</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>CONCLUIDA</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>GISELLE G. FONSECA</t>
-        </is>
-      </c>
+          <t>CONCLUÍDA</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
       <c r="J15" s="8" t="inlineStr">
         <is>
           <t>SL</t>
@@ -18605,13 +18607,13 @@
         <v>0</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>4625557.49</v>
+        <v>3607318.65</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>0.9957816754014897</v>
+        <v>0.999986480445621</v>
       </c>
       <c r="Q15" s="7" t="n">
-        <v>19594.76</v>
+        <v>48.77</v>
       </c>
       <c r="R15" s="7" t="n">
         <v>0</v>
@@ -18668,28 +18670,28 @@
         <v>0</v>
       </c>
       <c r="AJ15" s="7" t="n">
-        <v>0</v>
+        <v>439274.56</v>
       </c>
       <c r="AK15" s="7" t="n">
-        <v>0</v>
+        <v>275326.58</v>
       </c>
       <c r="AL15" s="7" t="n">
-        <v>0</v>
+        <v>1094135.61</v>
       </c>
       <c r="AM15" s="7" t="n">
-        <v>0</v>
+        <v>160193.12</v>
       </c>
       <c r="AN15" s="7" t="n">
-        <v>0</v>
+        <v>536762.41</v>
       </c>
       <c r="AO15" s="7" t="n">
-        <v>0</v>
+        <v>468162.08</v>
       </c>
       <c r="AP15" s="7" t="n">
-        <v>0</v>
+        <v>482635</v>
       </c>
       <c r="AQ15" s="7" t="n">
-        <v>0</v>
+        <v>150829.29</v>
       </c>
       <c r="AR15" s="7" t="n">
         <v>0</v>
@@ -18698,49 +18700,49 @@
         <v>0</v>
       </c>
       <c r="AT15" s="7" t="n">
-        <v>238919.75</v>
+        <v>0</v>
       </c>
       <c r="AU15" s="7" t="n">
-        <v>591880.41</v>
+        <v>0</v>
       </c>
       <c r="AV15" s="7" t="n">
-        <v>140614.75</v>
+        <v>0</v>
       </c>
       <c r="AW15" s="7" t="n">
-        <v>319668.5</v>
+        <v>0</v>
       </c>
       <c r="AX15" s="7" t="n">
-        <v>164215.33</v>
+        <v>0</v>
       </c>
       <c r="AY15" s="7" t="n">
-        <v>132243.75</v>
+        <v>0</v>
       </c>
       <c r="AZ15" s="7" t="n">
-        <v>626140.15</v>
+        <v>0</v>
       </c>
       <c r="BA15" s="7" t="n">
-        <v>296595.78</v>
+        <v>0</v>
       </c>
       <c r="BB15" s="7" t="n">
-        <v>142165.38</v>
+        <v>0</v>
       </c>
       <c r="BC15" s="7" t="n">
-        <v>155215.38</v>
+        <v>0</v>
       </c>
       <c r="BD15" s="7" t="n">
-        <v>120984.77</v>
+        <v>0</v>
       </c>
       <c r="BE15" s="7" t="n">
-        <v>883217.4</v>
+        <v>0</v>
       </c>
       <c r="BF15" s="7" t="n">
-        <v>492856.12</v>
+        <v>0</v>
       </c>
       <c r="BG15" s="7" t="n">
-        <v>306122.34</v>
+        <v>0</v>
       </c>
       <c r="BH15" s="7" t="n">
-        <v>14717.68</v>
+        <v>0</v>
       </c>
       <c r="BI15" s="7" t="n">
         <v>0</v>
@@ -18836,7 +18838,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>330018/001037/2021</t>
+          <t>170026/002680/2021</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -18845,23 +18847,27 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-45</v>
+        <v>567</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>45061</v>
+        <v>44918</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>45016</v>
+        <v>45485</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>3607367.42</v>
+        <v>4645152.25</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>CONCLUÍDA</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr"/>
+          <t>CONCLUIDA</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>GISELLE G. FONSECA</t>
+        </is>
+      </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
           <t>SL</t>
@@ -18884,13 +18890,13 @@
         <v>0</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>3607318.65</v>
+        <v>4625557.49</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>0.999986480445621</v>
+        <v>0.9957816754014897</v>
       </c>
       <c r="Q16" s="7" t="n">
-        <v>48.77</v>
+        <v>19594.76</v>
       </c>
       <c r="R16" s="7" t="n">
         <v>0</v>
@@ -18947,28 +18953,28 @@
         <v>0</v>
       </c>
       <c r="AJ16" s="7" t="n">
-        <v>439274.56</v>
+        <v>0</v>
       </c>
       <c r="AK16" s="7" t="n">
-        <v>275326.58</v>
+        <v>0</v>
       </c>
       <c r="AL16" s="7" t="n">
-        <v>1094135.61</v>
+        <v>0</v>
       </c>
       <c r="AM16" s="7" t="n">
-        <v>160193.12</v>
+        <v>0</v>
       </c>
       <c r="AN16" s="7" t="n">
-        <v>536762.41</v>
+        <v>0</v>
       </c>
       <c r="AO16" s="7" t="n">
-        <v>468162.08</v>
+        <v>0</v>
       </c>
       <c r="AP16" s="7" t="n">
-        <v>482635</v>
+        <v>0</v>
       </c>
       <c r="AQ16" s="7" t="n">
-        <v>150829.29</v>
+        <v>0</v>
       </c>
       <c r="AR16" s="7" t="n">
         <v>0</v>
@@ -18977,49 +18983,49 @@
         <v>0</v>
       </c>
       <c r="AT16" s="7" t="n">
-        <v>0</v>
+        <v>238919.75</v>
       </c>
       <c r="AU16" s="7" t="n">
-        <v>0</v>
+        <v>591880.41</v>
       </c>
       <c r="AV16" s="7" t="n">
-        <v>0</v>
+        <v>140614.75</v>
       </c>
       <c r="AW16" s="7" t="n">
-        <v>0</v>
+        <v>319668.5</v>
       </c>
       <c r="AX16" s="7" t="n">
-        <v>0</v>
+        <v>164215.33</v>
       </c>
       <c r="AY16" s="7" t="n">
-        <v>0</v>
+        <v>132243.75</v>
       </c>
       <c r="AZ16" s="7" t="n">
-        <v>0</v>
+        <v>626140.15</v>
       </c>
       <c r="BA16" s="7" t="n">
-        <v>0</v>
+        <v>296595.78</v>
       </c>
       <c r="BB16" s="7" t="n">
-        <v>0</v>
+        <v>142165.38</v>
       </c>
       <c r="BC16" s="7" t="n">
-        <v>0</v>
+        <v>155215.38</v>
       </c>
       <c r="BD16" s="7" t="n">
-        <v>0</v>
+        <v>120984.77</v>
       </c>
       <c r="BE16" s="7" t="n">
-        <v>0</v>
+        <v>883217.4</v>
       </c>
       <c r="BF16" s="7" t="n">
-        <v>0</v>
+        <v>492856.12</v>
       </c>
       <c r="BG16" s="7" t="n">
-        <v>0</v>
+        <v>306122.34</v>
       </c>
       <c r="BH16" s="7" t="n">
-        <v>0</v>
+        <v>14717.68</v>
       </c>
       <c r="BI16" s="7" t="n">
         <v>0</v>
@@ -34365,13 +34371,13 @@
         <v>0</v>
       </c>
       <c r="O71" s="7" t="n">
-        <v>0</v>
+        <v>266299.23</v>
       </c>
       <c r="P71" s="9" t="n">
-        <v>0</v>
+        <v>0.02960229523721647</v>
       </c>
       <c r="Q71" s="7" t="n">
-        <v>8995898.050000001</v>
+        <v>8729598.82</v>
       </c>
       <c r="R71" s="7" t="n">
         <v>0</v>
@@ -34440,13 +34446,13 @@
         <v>0</v>
       </c>
       <c r="AN71" s="7" t="n">
-        <v>0</v>
+        <v>92866.86</v>
       </c>
       <c r="AO71" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AP71" s="7" t="n">
-        <v>0</v>
+        <v>173432.37</v>
       </c>
       <c r="AQ71" s="7" t="n">
         <v>0</v>
@@ -39710,13 +39716,13 @@
         <v>0</v>
       </c>
       <c r="O90" s="7" t="n">
-        <v>46178509.21</v>
+        <v>31178236.21</v>
       </c>
       <c r="P90" s="9" t="n">
-        <v>1.406304655299222</v>
+        <v>0.9494914295900844</v>
       </c>
       <c r="Q90" s="7" t="n">
-        <v>-13341734.45</v>
+        <v>1658538.55</v>
       </c>
       <c r="R90" s="7" t="n">
         <v>0</v>
@@ -39761,7 +39767,7 @@
         <v>2696269.1</v>
       </c>
       <c r="AF90" s="7" t="n">
-        <v>4871747.25</v>
+        <v>4871474.25</v>
       </c>
       <c r="AG90" s="7" t="n">
         <v>4497352.58</v>
@@ -39782,7 +39788,7 @@
         <v>4888556.81</v>
       </c>
       <c r="AM90" s="7" t="n">
-        <v>16660361.27</v>
+        <v>1660361.27</v>
       </c>
       <c r="AN90" s="7" t="n">
         <v>426548.56</v>
@@ -45029,7 +45035,7 @@
         <v>44011</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>0</v>
+        <v>62980000</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
@@ -45066,10 +45072,10 @@
         <v>62980000</v>
       </c>
       <c r="P109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q109" s="7" t="n">
-        <v>-62980000</v>
+        <v>0</v>
       </c>
       <c r="R109" s="7" t="n">
         <v>27179207.94</v>
@@ -46992,7 +46998,7 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>170026/001756/2021</t>
+          <t>170026/001757/2021</t>
         </is>
       </c>
       <c r="C116" s="14" t="inlineStr">
@@ -47001,16 +47007,16 @@
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>888</v>
+        <v>468</v>
       </c>
       <c r="E116" s="6" t="n">
-        <v>44538</v>
+        <v>44791</v>
       </c>
       <c r="F116" s="6" t="n">
-        <v>45426</v>
+        <v>45259</v>
       </c>
       <c r="G116" s="7" t="n">
-        <v>24165422.12</v>
+        <v>3615856.15</v>
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
@@ -47044,13 +47050,13 @@
         <v>0</v>
       </c>
       <c r="O116" s="7" t="n">
-        <v>8398407.23</v>
+        <v>255684.47</v>
       </c>
       <c r="P116" s="9" t="n">
-        <v>0.3475381968622528</v>
+        <v>0.07071201380619081</v>
       </c>
       <c r="Q116" s="7" t="n">
-        <v>15767014.89</v>
+        <v>3360171.68</v>
       </c>
       <c r="R116" s="7" t="n">
         <v>0</v>
@@ -47086,40 +47092,40 @@
         <v>0</v>
       </c>
       <c r="AC116" s="7" t="n">
-        <v>5630.73</v>
+        <v>0</v>
       </c>
       <c r="AD116" s="7" t="n">
-        <v>85270.45</v>
+        <v>0</v>
       </c>
       <c r="AE116" s="7" t="n">
-        <v>183497.2</v>
+        <v>0</v>
       </c>
       <c r="AF116" s="7" t="n">
-        <v>269577.72</v>
+        <v>0</v>
       </c>
       <c r="AG116" s="7" t="n">
-        <v>270437.77</v>
+        <v>0</v>
       </c>
       <c r="AH116" s="7" t="n">
-        <v>273799.2</v>
+        <v>0</v>
       </c>
       <c r="AI116" s="7" t="n">
-        <v>371021.51</v>
+        <v>0</v>
       </c>
       <c r="AJ116" s="7" t="n">
-        <v>954612.39</v>
+        <v>0</v>
       </c>
       <c r="AK116" s="7" t="n">
-        <v>656379.84</v>
+        <v>3879.08</v>
       </c>
       <c r="AL116" s="7" t="n">
-        <v>317135.78</v>
+        <v>4074.61</v>
       </c>
       <c r="AM116" s="7" t="n">
-        <v>161899.02</v>
+        <v>17364.98</v>
       </c>
       <c r="AN116" s="7" t="n">
-        <v>367581.73</v>
+        <v>0</v>
       </c>
       <c r="AO116" s="7" t="n">
         <v>0</v>
@@ -47128,34 +47134,34 @@
         <v>0</v>
       </c>
       <c r="AQ116" s="7" t="n">
-        <v>578603.54</v>
+        <v>0</v>
       </c>
       <c r="AR116" s="7" t="n">
-        <v>182465.36</v>
+        <v>19750.62</v>
       </c>
       <c r="AS116" s="7" t="n">
-        <v>205227.45</v>
+        <v>88980.25</v>
       </c>
       <c r="AT116" s="7" t="n">
-        <v>102363.86</v>
+        <v>20906.54</v>
       </c>
       <c r="AU116" s="7" t="n">
-        <v>82676.64999999999</v>
+        <v>16695.77</v>
       </c>
       <c r="AV116" s="7" t="n">
-        <v>86196.17</v>
+        <v>42691.31</v>
       </c>
       <c r="AW116" s="7" t="n">
-        <v>133423.93</v>
+        <v>16197.36</v>
       </c>
       <c r="AX116" s="7" t="n">
-        <v>33929.2</v>
+        <v>6051.68</v>
       </c>
       <c r="AY116" s="7" t="n">
-        <v>1505821.47</v>
+        <v>15072.3</v>
       </c>
       <c r="AZ116" s="7" t="n">
-        <v>1570856.26</v>
+        <v>4019.97</v>
       </c>
       <c r="BA116" s="7" t="n">
         <v>0</v>
@@ -47275,7 +47281,7 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>170026/001757/2021</t>
+          <t>170026/001756/2021</t>
         </is>
       </c>
       <c r="C117" s="14" t="inlineStr">
@@ -47284,16 +47290,16 @@
         </is>
       </c>
       <c r="D117" s="4" t="n">
-        <v>468</v>
+        <v>888</v>
       </c>
       <c r="E117" s="6" t="n">
-        <v>44791</v>
+        <v>44538</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>45259</v>
+        <v>45426</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>3615856.15</v>
+        <v>24165422.12</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
@@ -47327,13 +47333,13 @@
         <v>0</v>
       </c>
       <c r="O117" s="7" t="n">
-        <v>255684.47</v>
+        <v>8398407.23</v>
       </c>
       <c r="P117" s="9" t="n">
-        <v>0.07071201380619081</v>
+        <v>0.3475381968622528</v>
       </c>
       <c r="Q117" s="7" t="n">
-        <v>3360171.68</v>
+        <v>15767014.89</v>
       </c>
       <c r="R117" s="7" t="n">
         <v>0</v>
@@ -47369,40 +47375,40 @@
         <v>0</v>
       </c>
       <c r="AC117" s="7" t="n">
-        <v>0</v>
+        <v>5630.73</v>
       </c>
       <c r="AD117" s="7" t="n">
-        <v>0</v>
+        <v>85270.45</v>
       </c>
       <c r="AE117" s="7" t="n">
-        <v>0</v>
+        <v>183497.2</v>
       </c>
       <c r="AF117" s="7" t="n">
-        <v>0</v>
+        <v>269577.72</v>
       </c>
       <c r="AG117" s="7" t="n">
-        <v>0</v>
+        <v>270437.77</v>
       </c>
       <c r="AH117" s="7" t="n">
-        <v>0</v>
+        <v>273799.2</v>
       </c>
       <c r="AI117" s="7" t="n">
-        <v>0</v>
+        <v>371021.51</v>
       </c>
       <c r="AJ117" s="7" t="n">
-        <v>0</v>
+        <v>954612.39</v>
       </c>
       <c r="AK117" s="7" t="n">
-        <v>3879.08</v>
+        <v>656379.84</v>
       </c>
       <c r="AL117" s="7" t="n">
-        <v>4074.61</v>
+        <v>317135.78</v>
       </c>
       <c r="AM117" s="7" t="n">
-        <v>17364.98</v>
+        <v>161899.02</v>
       </c>
       <c r="AN117" s="7" t="n">
-        <v>0</v>
+        <v>367581.73</v>
       </c>
       <c r="AO117" s="7" t="n">
         <v>0</v>
@@ -47411,34 +47417,34 @@
         <v>0</v>
       </c>
       <c r="AQ117" s="7" t="n">
-        <v>0</v>
+        <v>578603.54</v>
       </c>
       <c r="AR117" s="7" t="n">
-        <v>19750.62</v>
+        <v>182465.36</v>
       </c>
       <c r="AS117" s="7" t="n">
-        <v>88980.25</v>
+        <v>205227.45</v>
       </c>
       <c r="AT117" s="7" t="n">
-        <v>20906.54</v>
+        <v>102363.86</v>
       </c>
       <c r="AU117" s="7" t="n">
-        <v>16695.77</v>
+        <v>82676.64999999999</v>
       </c>
       <c r="AV117" s="7" t="n">
-        <v>42691.31</v>
+        <v>86196.17</v>
       </c>
       <c r="AW117" s="7" t="n">
-        <v>16197.36</v>
+        <v>133423.93</v>
       </c>
       <c r="AX117" s="7" t="n">
-        <v>6051.68</v>
+        <v>33929.2</v>
       </c>
       <c r="AY117" s="7" t="n">
-        <v>15072.3</v>
+        <v>1505821.47</v>
       </c>
       <c r="AZ117" s="7" t="n">
-        <v>4019.97</v>
+        <v>1570856.26</v>
       </c>
       <c r="BA117" s="7" t="n">
         <v>0</v>
@@ -48713,24 +48719,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>170026/001848/2022</t>
+          <t>330018/000445/2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GEOSONDA S/A  - EM RECUPERAÇÃO JUDICIAL</t>
+          <t>OMEGA CONSTRUTORA E SERVICOS LTDA</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>330018/000445/2023</t>
+          <t>170026/001848/2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OMEGA CONSTRUTORA E SERVICOS LTDA</t>
+          <t>GEOSONDA S/A  - EM RECUPERAÇÃO JUDICIAL</t>
         </is>
       </c>
     </row>
@@ -48797,60 +48803,60 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>330018/000423/2021</t>
+          <t>330018/000426/2021</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ALBERTO COUTO ALVES - BRASIL LTDA.</t>
+          <t>OMEGA CONSTRUTORA E SERVICOS LTDA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>330018/000424/2021</t>
+          <t>330018/001071/2021</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ALBERTO COUTO ALVES - BRASIL LTDA.</t>
+          <t>HYDRA ENGENHARIA E SANEAMENTO LTDA</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>330018/000426/2021</t>
+          <t>330018/001077/2021</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OMEGA CONSTRUTORA E SERVICOS LTDA</t>
+          <t>SEEL SERVICOS ESPECIAIS DE ENGENHARIA LTDA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>330018/001071/2021</t>
+          <t>330018/000424/2021</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HYDRA ENGENHARIA E SANEAMENTO LTDA</t>
+          <t>ALBERTO COUTO ALVES - BRASIL LTDA.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>330018/001077/2021</t>
+          <t>330018/000423/2021</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SEEL SERVICOS ESPECIAIS DE ENGENHARIA LTDA</t>
+          <t>ALBERTO COUTO ALVES - BRASIL LTDA.</t>
         </is>
       </c>
     </row>
@@ -48965,96 +48971,96 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>170026/000537/2022</t>
+          <t>170026/000549/2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ERWIL CONSTRUÇÕES LTDA</t>
+          <t>BARRA NOVA ENGENHARIA LTDA</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>170026/000539/2022</t>
+          <t>170026/001072/2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CONSTRUTORA SOLIDUM  LTDA</t>
+          <t>COORDENA COORDENAÇÃO DE PROJETOS LTDA</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>170026/000545/2022</t>
+          <t>170026/000548/2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GEOLOGUS ENGENHARIA LTDA</t>
+          <t>ENGE PRAT ENGENHARIA E SERVICOS LTDA.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>170026/000548/2022</t>
+          <t>170026/000537/2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ENGE PRAT ENGENHARIA E SERVICOS LTDA.</t>
+          <t>ERWIL CONSTRUÇÕES LTDA</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>170026/000549/2022</t>
+          <t>170026/000545/2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BARRA NOVA ENGENHARIA LTDA</t>
+          <t>GEOLOGUS ENGENHARIA LTDA</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>170026/001072/2022</t>
+          <t>170026/000539/2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>COORDENA COORDENAÇÃO DE PROJETOS LTDA</t>
+          <t>CONSTRUTORA SOLIDUM  LTDA</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>170026/001303/2020</t>
+          <t>330018/000580/2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WTE ENGENHARIA EIRELI</t>
+          <t>MEDEIROS E MEDEIROS CIVIL E MONTAGEM LTDA-ME</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>330018/000580/2022</t>
+          <t>170026/001303/2020</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MEDEIROS E MEDEIROS CIVIL E MONTAGEM LTDA-ME</t>
+          <t>WTE ENGENHARIA EIRELI</t>
         </is>
       </c>
     </row>
@@ -49109,24 +49115,24 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>e-17/026/1892/2019-1</t>
+          <t>e-17/026/1892/2019-2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>METALURGICA BIG FARM LTDA</t>
+          <t>FAB MIX CONCRETOS LTDA</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>e-17/026/1892/2019-2</t>
+          <t>e-17/026/1892/2019-1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FAB MIX CONCRETOS LTDA</t>
+          <t>METALURGICA BIG FARM LTDA</t>
         </is>
       </c>
     </row>

--- a/MEDIÇÕES_CONSOLIDADO.xlsx
+++ b/MEDIÇÕES_CONSOLIDADO.xlsx
@@ -1103,10 +1103,10 @@
         <v>0</v>
       </c>
       <c r="O2" s="7" t="n">
-        <v>31106158.75</v>
+        <v>36782151.81</v>
       </c>
       <c r="P2" s="9" t="n">
-        <v>0.8456862151698025</v>
+        <v>0.8456999999999999</v>
       </c>
       <c r="Q2" s="7" t="n">
         <v>5675993.06</v>
@@ -1386,13 +1386,13 @@
         <v>0</v>
       </c>
       <c r="O3" s="7" t="n">
-        <v>16018051.24</v>
+        <v>31022838.12</v>
       </c>
       <c r="P3" s="9" t="n">
-        <v>0.5163309423219207</v>
+        <v>0.5163</v>
       </c>
       <c r="Q3" s="7" t="n">
-        <v>15004786.88</v>
+        <v>15004786.89</v>
       </c>
       <c r="R3" s="7" t="n">
         <v>0</v>
@@ -1669,13 +1669,13 @@
         <v>0</v>
       </c>
       <c r="O4" s="7" t="n">
-        <v>13076583.13</v>
+        <v>51119038.92</v>
       </c>
       <c r="P4" s="9" t="n">
-        <v>0.2558065137035248</v>
+        <v>0.2558</v>
       </c>
       <c r="Q4" s="7" t="n">
-        <v>38042455.79</v>
+        <v>38042440.77</v>
       </c>
       <c r="R4" s="7" t="n">
         <v>0</v>
@@ -1952,10 +1952,10 @@
         <v>1122659.32</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>3806174.66</v>
+        <v>18990162.94</v>
       </c>
       <c r="P5" s="9" t="n">
-        <v>0.2004287520873689</v>
+        <v>0.2004</v>
       </c>
       <c r="Q5" s="7" t="n">
         <v>15183988.28</v>
@@ -2235,10 +2235,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="7" t="n">
-        <v>7322834.12</v>
+        <v>8463890.939999999</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>0.8651853115678262</v>
+        <v>0.8652</v>
       </c>
       <c r="Q6" s="7" t="n">
         <v>1141056.82</v>
@@ -2518,10 +2518,10 @@
         <v>0</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>1222003.41</v>
+        <v>1528883.61</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>0.799278245909118</v>
+        <v>0.7993000000000001</v>
       </c>
       <c r="Q7" s="7" t="n">
         <v>306880.2</v>
@@ -2801,10 +2801,10 @@
         <v>0</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>1038880.21</v>
+        <v>3294597.99</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>0.3153283687883267</v>
+        <v>0.3153</v>
       </c>
       <c r="Q8" s="7" t="n">
         <v>2255717.78</v>
@@ -3084,10 +3084,10 @@
         <v>1602190.92</v>
       </c>
       <c r="O9" s="7" t="n">
-        <v>27948056.39</v>
+        <v>62211091.02</v>
       </c>
       <c r="P9" s="9" t="n">
-        <v>0.4492455594616576</v>
+        <v>0.4492</v>
       </c>
       <c r="Q9" s="7" t="n">
         <v>34263034.63</v>
@@ -3367,10 +3367,10 @@
         <v>294296.16</v>
       </c>
       <c r="O10" s="7" t="n">
-        <v>54809333.5</v>
+        <v>56189486.28</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>0.9754375262816516</v>
+        <v>0.9754</v>
       </c>
       <c r="Q10" s="7" t="n">
         <v>1380152.78</v>
@@ -3650,10 +3650,10 @@
         <v>63006.28</v>
       </c>
       <c r="O11" s="7" t="n">
-        <v>63006.28</v>
+        <v>4705907.3</v>
       </c>
       <c r="P11" s="9" t="n">
-        <v>0.01338876352281737</v>
+        <v>0.0134</v>
       </c>
       <c r="Q11" s="7" t="n">
         <v>4642901.02</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="O12" s="7" t="n">
-        <v>1739254.2</v>
+        <v>2860442.12</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>0.6080368443183182</v>
+        <v>0.608</v>
       </c>
       <c r="Q12" s="7" t="n">
         <v>1121187.92</v>
@@ -4212,7 +4212,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="7" t="n">
-        <v>0</v>
+        <v>5054505.24</v>
       </c>
       <c r="P13" s="9" t="n">
         <v>0</v>
@@ -4495,13 +4495,13 @@
         <v>1284711.9</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>2127588.26</v>
+        <v>7848019.53</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>0.271098746870728</v>
+        <v>0.1637</v>
       </c>
       <c r="Q14" s="7" t="n">
-        <v>5720431.27</v>
+        <v>6563307.63</v>
       </c>
       <c r="R14" s="7" t="n">
         <v>0</v>
@@ -4778,10 +4778,10 @@
         <v>0</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>32294745.04</v>
+        <v>48872552.26</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>0.6607951405564674</v>
+        <v>0.6607999999999999</v>
       </c>
       <c r="Q15" s="7" t="n">
         <v>16577807.22</v>
@@ -5061,7 +5061,7 @@
         <v>0</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>0</v>
+        <v>1302281.25</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>0</v>
@@ -5344,13 +5344,13 @@
         <v>0</v>
       </c>
       <c r="O17" s="7" t="n">
-        <v>29783885.44</v>
+        <v>34662990.03</v>
       </c>
       <c r="P17" s="9" t="n">
-        <v>0.85924166998354</v>
+        <v>0.8592</v>
       </c>
       <c r="Q17" s="7" t="n">
-        <v>4879104.59</v>
+        <v>4879112.73</v>
       </c>
       <c r="R17" s="7" t="n">
         <v>0</v>
@@ -5627,10 +5627,10 @@
         <v>0</v>
       </c>
       <c r="O18" s="7" t="n">
-        <v>122778.19</v>
+        <v>7430869.32</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>0.01652272227013138</v>
+        <v>0.0165</v>
       </c>
       <c r="Q18" s="7" t="n">
         <v>7308091.13</v>
@@ -5910,10 +5910,10 @@
         <v>0</v>
       </c>
       <c r="O19" s="7" t="n">
-        <v>20145177.51</v>
+        <v>65678550.13</v>
       </c>
       <c r="P19" s="9" t="n">
-        <v>0.3067238462195937</v>
+        <v>0.3067</v>
       </c>
       <c r="Q19" s="7" t="n">
         <v>45533372.62</v>
@@ -6193,13 +6193,13 @@
         <v>0</v>
       </c>
       <c r="O20" s="7" t="n">
-        <v>22442987.52</v>
+        <v>58032411.71</v>
       </c>
       <c r="P20" s="9" t="n">
-        <v>0.3867319461433424</v>
+        <v>0.3867</v>
       </c>
       <c r="Q20" s="7" t="n">
-        <v>35589424.19</v>
+        <v>35589424.18</v>
       </c>
       <c r="R20" s="7" t="n">
         <v>0</v>
@@ -6476,10 +6476,10 @@
         <v>0</v>
       </c>
       <c r="O21" s="7" t="n">
-        <v>2045374.39</v>
+        <v>54283415</v>
       </c>
       <c r="P21" s="9" t="n">
-        <v>0.037679545216527</v>
+        <v>0.0377</v>
       </c>
       <c r="Q21" s="7" t="n">
         <v>52238040.61</v>
@@ -6759,13 +6759,13 @@
         <v>0</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>35796161.91</v>
+        <v>45862409.69</v>
       </c>
       <c r="P22" s="9" t="n">
-        <v>0.7805120174007151</v>
+        <v>0.7805</v>
       </c>
       <c r="Q22" s="7" t="n">
-        <v>10066247.78</v>
+        <v>10066247.71</v>
       </c>
       <c r="R22" s="7" t="n">
         <v>0</v>
@@ -7042,10 +7042,10 @@
         <v>0</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>3584685.32</v>
+        <v>6016602.48</v>
       </c>
       <c r="P23" s="9" t="n">
-        <v>0.5957989300300258</v>
+        <v>0.5958</v>
       </c>
       <c r="Q23" s="7" t="n">
         <v>2431917.16</v>
@@ -7325,13 +7325,13 @@
         <v>0</v>
       </c>
       <c r="O24" s="7" t="n">
-        <v>45451420.48</v>
+        <v>51414775.09</v>
       </c>
       <c r="P24" s="9" t="n">
-        <v>0.8840147681369541</v>
+        <v>0.8996</v>
       </c>
       <c r="Q24" s="7" t="n">
-        <v>5963354.61</v>
+        <v>5160639.5</v>
       </c>
       <c r="R24" s="7" t="n">
         <v>0</v>
@@ -7608,13 +7608,13 @@
         <v>0</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>2286082.54</v>
+        <v>2601911.32</v>
       </c>
       <c r="P25" s="9" t="n">
-        <v>0.8786166240285238</v>
+        <v>0.8786</v>
       </c>
       <c r="Q25" s="7" t="n">
-        <v>315828.78</v>
+        <v>315830.9</v>
       </c>
       <c r="R25" s="7" t="n">
         <v>0</v>
@@ -7891,10 +7891,10 @@
         <v>0</v>
       </c>
       <c r="O26" s="7" t="n">
-        <v>425261.4</v>
+        <v>544550.48</v>
       </c>
       <c r="P26" s="9" t="n">
-        <v>0.7809402720570552</v>
+        <v>0.7809</v>
       </c>
       <c r="Q26" s="7" t="n">
         <v>119289.08</v>
@@ -8174,13 +8174,13 @@
         <v>0</v>
       </c>
       <c r="O27" s="7" t="n">
-        <v>19844966.53</v>
+        <v>28459856.91</v>
       </c>
       <c r="P27" s="9" t="n">
-        <v>0.697296778151651</v>
+        <v>0.6973</v>
       </c>
       <c r="Q27" s="7" t="n">
-        <v>8614890.380000001</v>
+        <v>8614890.33</v>
       </c>
       <c r="R27" s="7" t="n">
         <v>0</v>
@@ -8457,10 +8457,10 @@
         <v>0</v>
       </c>
       <c r="O28" s="7" t="n">
-        <v>42048979.52</v>
+        <v>43796954.98</v>
       </c>
       <c r="P28" s="9" t="n">
-        <v>0.9600891098297082</v>
+        <v>0.9601000000000001</v>
       </c>
       <c r="Q28" s="7" t="n">
         <v>1747975.46</v>
@@ -8740,10 +8740,10 @@
         <v>499862.54</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>36377601.26</v>
+        <v>45726170.25</v>
       </c>
       <c r="P29" s="9" t="n">
-        <v>0.7955532042397536</v>
+        <v>0.7956</v>
       </c>
       <c r="Q29" s="7" t="n">
         <v>9348568.99</v>
@@ -9023,13 +9023,13 @@
         <v>0</v>
       </c>
       <c r="O30" s="7" t="n">
-        <v>13115141.03</v>
+        <v>22825141.32</v>
       </c>
       <c r="P30" s="9" t="n">
-        <v>0.574591887346089</v>
+        <v>0.5746</v>
       </c>
       <c r="Q30" s="7" t="n">
-        <v>9710000.289999999</v>
+        <v>9709999.51</v>
       </c>
       <c r="R30" s="7" t="n">
         <v>0</v>
@@ -9306,10 +9306,10 @@
         <v>0</v>
       </c>
       <c r="O31" s="7" t="n">
-        <v>14348711.09</v>
+        <v>26504288.68</v>
       </c>
       <c r="P31" s="9" t="n">
-        <v>0.5413731816476728</v>
+        <v>0.5414</v>
       </c>
       <c r="Q31" s="7" t="n">
         <v>12155577.59</v>
@@ -9589,10 +9589,10 @@
         <v>3545422.68</v>
       </c>
       <c r="O32" s="7" t="n">
-        <v>19434508.22</v>
+        <v>20106028.53</v>
       </c>
       <c r="P32" s="9" t="n">
-        <v>0.9666010465966449</v>
+        <v>0.9666</v>
       </c>
       <c r="Q32" s="7" t="n">
         <v>671520.3100000001</v>
@@ -9872,13 +9872,13 @@
         <v>0</v>
       </c>
       <c r="O33" s="7" t="n">
-        <v>7571952.28</v>
+        <v>7795660.46</v>
       </c>
       <c r="P33" s="9" t="n">
-        <v>0.971303498767313</v>
+        <v>0.9712999999999999</v>
       </c>
       <c r="Q33" s="7" t="n">
-        <v>223708.18</v>
+        <v>223708.17</v>
       </c>
       <c r="R33" s="7" t="n">
         <v>0</v>
@@ -10155,7 +10155,7 @@
         <v>0</v>
       </c>
       <c r="O34" s="7" t="n">
-        <v>0</v>
+        <v>41522873.42</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>0</v>
@@ -10438,10 +10438,10 @@
         <v>1285251.84</v>
       </c>
       <c r="O35" s="7" t="n">
-        <v>5666949.72</v>
+        <v>7066834.9</v>
       </c>
       <c r="P35" s="9" t="n">
-        <v>0.80190775646959</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="Q35" s="7" t="n">
         <v>1399885.18</v>
@@ -10721,10 +10721,10 @@
         <v>3055826.41</v>
       </c>
       <c r="O36" s="7" t="n">
-        <v>5476795.79</v>
+        <v>10349390.52</v>
       </c>
       <c r="P36" s="9" t="n">
-        <v>0.5291901759254515</v>
+        <v>0.5292</v>
       </c>
       <c r="Q36" s="7" t="n">
         <v>4872594.73</v>
@@ -11004,10 +11004,10 @@
         <v>7440875.08</v>
       </c>
       <c r="O37" s="7" t="n">
-        <v>21232327.94</v>
+        <v>27434724</v>
       </c>
       <c r="P37" s="9" t="n">
-        <v>0.7739216891702646</v>
+        <v>0.7739</v>
       </c>
       <c r="Q37" s="7" t="n">
         <v>6202396.06</v>
@@ -11287,10 +11287,10 @@
         <v>137056.25</v>
       </c>
       <c r="O38" s="7" t="n">
-        <v>685145.5600000001</v>
+        <v>763285.0699999999</v>
       </c>
       <c r="P38" s="9" t="n">
-        <v>0.8976273569716227</v>
+        <v>0.8976000000000001</v>
       </c>
       <c r="Q38" s="7" t="n">
         <v>78139.50999999999</v>
@@ -11570,10 +11570,10 @@
         <v>0</v>
       </c>
       <c r="O39" s="7" t="n">
-        <v>164482.69</v>
+        <v>256613.37</v>
       </c>
       <c r="P39" s="9" t="n">
-        <v>0.6409747473407174</v>
+        <v>0.6409999999999999</v>
       </c>
       <c r="Q39" s="7" t="n">
         <v>92130.67999999999</v>
@@ -11853,7 +11853,7 @@
         <v>0</v>
       </c>
       <c r="O40" s="7" t="n">
-        <v>0</v>
+        <v>2742607.66</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>0</v>
@@ -12136,13 +12136,13 @@
         <v>0</v>
       </c>
       <c r="O41" s="7" t="n">
-        <v>2301268.72</v>
+        <v>15203482.79</v>
       </c>
       <c r="P41" s="9" t="n">
-        <v>0.1513645755901172</v>
+        <v>0.15</v>
       </c>
       <c r="Q41" s="7" t="n">
-        <v>12902214.07</v>
+        <v>12923552.74</v>
       </c>
       <c r="R41" s="7" t="n">
         <v>0</v>
@@ -12419,13 +12419,13 @@
         <v>3468001.87</v>
       </c>
       <c r="O42" s="7" t="n">
-        <v>14615806.68</v>
+        <v>24187461.93</v>
       </c>
       <c r="P42" s="9" t="n">
-        <v>0.6042720283053692</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="Q42" s="7" t="n">
-        <v>9571655.25</v>
+        <v>9571655.24</v>
       </c>
       <c r="R42" s="7" t="n">
         <v>0</v>
@@ -12702,10 +12702,10 @@
         <v>0</v>
       </c>
       <c r="O43" s="7" t="n">
-        <v>10511270.47</v>
+        <v>12432476.25</v>
       </c>
       <c r="P43" s="9" t="n">
-        <v>0.8454687753777129</v>
+        <v>0.8454999999999999</v>
       </c>
       <c r="Q43" s="7" t="n">
         <v>1921205.78</v>
@@ -12985,10 +12985,10 @@
         <v>0</v>
       </c>
       <c r="O44" s="7" t="n">
-        <v>10301084.52</v>
+        <v>12100122.6</v>
       </c>
       <c r="P44" s="9" t="n">
-        <v>0.851320673395491</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="Q44" s="7" t="n">
         <v>1799038.08</v>
@@ -13268,13 +13268,13 @@
         <v>0</v>
       </c>
       <c r="O45" s="7" t="n">
-        <v>56075179.54</v>
+        <v>59148617.81</v>
       </c>
       <c r="P45" s="9" t="n">
-        <v>0.9480387136032045</v>
+        <v>0.948</v>
       </c>
       <c r="Q45" s="7" t="n">
-        <v>3073438.27</v>
+        <v>3073439.17</v>
       </c>
       <c r="R45" s="7" t="n">
         <v>0</v>
@@ -13551,10 +13551,10 @@
         <v>0</v>
       </c>
       <c r="O46" s="7" t="n">
-        <v>22022321.06</v>
+        <v>116500000</v>
       </c>
       <c r="P46" s="9" t="n">
-        <v>0.1890327987982832</v>
+        <v>0.189</v>
       </c>
       <c r="Q46" s="7" t="n">
         <v>94477678.94</v>
@@ -13834,10 +13834,10 @@
         <v>0</v>
       </c>
       <c r="O47" s="7" t="n">
-        <v>38738669.02</v>
+        <v>41651255.98</v>
       </c>
       <c r="P47" s="9" t="n">
-        <v>0.9300720496544316</v>
+        <v>0.9301</v>
       </c>
       <c r="Q47" s="7" t="n">
         <v>2912586.96</v>
@@ -14117,10 +14117,10 @@
         <v>0</v>
       </c>
       <c r="O48" s="7" t="n">
-        <v>54247297.54</v>
+        <v>104939756.55</v>
       </c>
       <c r="P48" s="9" t="n">
-        <v>0.5169375203777334</v>
+        <v>0.5169</v>
       </c>
       <c r="Q48" s="7" t="n">
         <v>50692459.01</v>
@@ -14400,10 +14400,10 @@
         <v>1537890.45</v>
       </c>
       <c r="O49" s="7" t="n">
-        <v>63449041.49</v>
+        <v>74609626.42</v>
       </c>
       <c r="P49" s="9" t="n">
-        <v>0.8504136065877919</v>
+        <v>0.8504</v>
       </c>
       <c r="Q49" s="7" t="n">
         <v>11160584.93</v>
@@ -15242,10 +15242,10 @@
         <v>0</v>
       </c>
       <c r="P2" s="7" t="n">
-        <v>1088826.01</v>
+        <v>1212482.21</v>
       </c>
       <c r="Q2" s="9" t="n">
-        <v>0.8980140087993539</v>
+        <v>0.898</v>
       </c>
       <c r="R2" s="7" t="n">
         <v>123656.2</v>
@@ -15522,13 +15522,13 @@
         <v>0</v>
       </c>
       <c r="P3" s="7" t="n">
-        <v>32682339.39</v>
+        <v>69450000</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>0.4705880401727862</v>
+        <v>0.4456</v>
       </c>
       <c r="R3" s="7" t="n">
-        <v>36767660.61</v>
+        <v>38500569.52</v>
       </c>
       <c r="S3" s="7" t="n">
         <v>0</v>
@@ -15802,13 +15802,13 @@
         <v>0</v>
       </c>
       <c r="P4" s="7" t="n">
-        <v>75957961.34</v>
+        <v>84484346.70999999</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>0.8990773356007883</v>
+        <v>0.4495</v>
       </c>
       <c r="R4" s="7" t="n">
-        <v>8526385.369999999</v>
+        <v>46505366.04</v>
       </c>
       <c r="S4" s="7" t="n">
         <v>0</v>
@@ -16090,13 +16090,13 @@
         <v>0</v>
       </c>
       <c r="P5" s="7" t="n">
-        <v>1127526.06</v>
+        <v>2069000</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>0.5449618463025616</v>
+        <v>0.545</v>
       </c>
       <c r="R5" s="7" t="n">
-        <v>941473.9399999999</v>
+        <v>941483.9399999999</v>
       </c>
       <c r="S5" s="7" t="n">
         <v>0</v>
@@ -16373,7 +16373,7 @@
         <v>6948720.19</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="R6" s="7" t="n">
         <v>0</v>
@@ -16930,10 +16930,10 @@
         <v>0</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>6743573.85</v>
+        <v>6743574.04</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>0.9999999718250295</v>
+        <v>1</v>
       </c>
       <c r="R8" s="7" t="n">
         <v>0.19</v>
@@ -17214,13 +17214,13 @@
         <v>0</v>
       </c>
       <c r="P9" s="7" t="n">
-        <v>8394719</v>
+        <v>8396309.76</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>0.9998105405772927</v>
+        <v>0.9998</v>
       </c>
       <c r="R9" s="7" t="n">
-        <v>1590.76</v>
+        <v>1540.74</v>
       </c>
       <c r="S9" s="7" t="n">
         <v>0</v>
@@ -17498,13 +17498,13 @@
         <v>0</v>
       </c>
       <c r="P10" s="7" t="n">
-        <v>4374443.73</v>
+        <v>4374443.78</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>0.9999999885699754</v>
+        <v>1</v>
       </c>
       <c r="R10" s="7" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="S10" s="7" t="n">
         <v>0</v>
@@ -17786,10 +17786,10 @@
         <v>0</v>
       </c>
       <c r="P11" s="7" t="n">
-        <v>1740561.74</v>
+        <v>1741703.69</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>0.9993443488656789</v>
+        <v>0.9993000000000001</v>
       </c>
       <c r="R11" s="7" t="n">
         <v>1141.95</v>
@@ -18070,10 +18070,10 @@
         <v>0</v>
       </c>
       <c r="P12" s="7" t="n">
-        <v>7104640.05</v>
+        <v>8811881.779999999</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>0.806256850395467</v>
+        <v>0.8062999999999999</v>
       </c>
       <c r="R12" s="7" t="n">
         <v>1707241.73</v>
@@ -18350,10 +18350,10 @@
         <v>0</v>
       </c>
       <c r="P13" s="7" t="n">
-        <v>1285178.36</v>
+        <v>1332580.86</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>0.9644280497920404</v>
+        <v>0.9643999999999999</v>
       </c>
       <c r="R13" s="7" t="n">
         <v>47402.5</v>
@@ -18634,13 +18634,13 @@
         <v>0</v>
       </c>
       <c r="P14" s="7" t="n">
-        <v>5132338.31</v>
+        <v>5272095.08</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>0.9734912273243751</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="R14" s="7" t="n">
-        <v>139756.77</v>
+        <v>401.87</v>
       </c>
       <c r="S14" s="7" t="n">
         <v>0</v>
@@ -18914,10 +18914,10 @@
         <v>0</v>
       </c>
       <c r="P15" s="7" t="n">
-        <v>3607318.65</v>
+        <v>3607367.42</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>0.999986480445621</v>
+        <v>1</v>
       </c>
       <c r="R15" s="7" t="n">
         <v>48.77</v>
@@ -19198,10 +19198,10 @@
         <v>0</v>
       </c>
       <c r="P16" s="7" t="n">
-        <v>4625557.49</v>
+        <v>4645152.25</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>0.9957816754014897</v>
+        <v>0.9958</v>
       </c>
       <c r="R16" s="7" t="n">
         <v>19594.76</v>
@@ -19482,13 +19482,13 @@
         <v>0</v>
       </c>
       <c r="P17" s="7" t="n">
-        <v>10939879.36</v>
+        <v>11046611.98</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>0.9903379769115415</v>
+        <v>0.9903</v>
       </c>
       <c r="R17" s="7" t="n">
-        <v>106732.62</v>
+        <v>106732.59</v>
       </c>
       <c r="S17" s="7" t="n">
         <v>0</v>
@@ -19762,7 +19762,7 @@
         <v>0</v>
       </c>
       <c r="P18" s="7" t="n">
-        <v>0</v>
+        <v>1305890.95</v>
       </c>
       <c r="Q18" s="9" t="n">
         <v>0</v>
@@ -20046,13 +20046,13 @@
         <v>0</v>
       </c>
       <c r="P19" s="7" t="n">
-        <v>6171355.17</v>
+        <v>30334596.91</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>0.2034427946515937</v>
+        <v>0.2034</v>
       </c>
       <c r="R19" s="7" t="n">
-        <v>24163241.74</v>
+        <v>24163359.13</v>
       </c>
       <c r="S19" s="7" t="n">
         <v>0</v>
@@ -20330,13 +20330,13 @@
         <v>0</v>
       </c>
       <c r="P20" s="7" t="n">
-        <v>10061305.06</v>
+        <v>10061005.41</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>1.000029783305722</v>
+        <v>1</v>
       </c>
       <c r="R20" s="7" t="n">
-        <v>-299.65</v>
+        <v>0.02</v>
       </c>
       <c r="S20" s="7" t="n">
         <v>0</v>
@@ -20618,10 +20618,10 @@
         <v>0</v>
       </c>
       <c r="P21" s="7" t="n">
-        <v>32314427.7</v>
+        <v>32464769.58</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>0.9953690760185584</v>
+        <v>0.9954000000000001</v>
       </c>
       <c r="R21" s="7" t="n">
         <v>150341.88</v>
@@ -20902,13 +20902,13 @@
         <v>0</v>
       </c>
       <c r="P22" s="7" t="n">
-        <v>17677149.64</v>
+        <v>17695067.23</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>0.9989874245874792</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="R22" s="7" t="n">
-        <v>17917.59</v>
+        <v>17917.39</v>
       </c>
       <c r="S22" s="7" t="n">
         <v>0</v>
@@ -21462,13 +21462,13 @@
         <v>0</v>
       </c>
       <c r="P24" s="7" t="n">
-        <v>30651574.56</v>
+        <v>68148567.14</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>0.4497757744052255</v>
+        <v>0.4476</v>
       </c>
       <c r="R24" s="7" t="n">
-        <v>37496992.58</v>
+        <v>37645831.73</v>
       </c>
       <c r="S24" s="7" t="n">
         <v>0</v>
@@ -21746,10 +21746,10 @@
         <v>0</v>
       </c>
       <c r="P25" s="7" t="n">
-        <v>133579.45</v>
+        <v>47996411.38</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>0.002783113281999709</v>
+        <v>0.0028</v>
       </c>
       <c r="R25" s="7" t="n">
         <v>47862831.93</v>
@@ -22034,10 +22034,10 @@
         <v>0</v>
       </c>
       <c r="P26" s="7" t="n">
-        <v>19406169.39</v>
+        <v>19451386.88</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>0.9976753590744477</v>
+        <v>0.9976999999999999</v>
       </c>
       <c r="R26" s="7" t="n">
         <v>45217.49</v>
@@ -22318,13 +22318,13 @@
         <v>0</v>
       </c>
       <c r="P27" s="7" t="n">
-        <v>28044628.65</v>
+        <v>30543662.31</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>0.9181815973920777</v>
+        <v>0.9181999999999999</v>
       </c>
       <c r="R27" s="7" t="n">
-        <v>2499033.66</v>
+        <v>2499033.71</v>
       </c>
       <c r="S27" s="7" t="n">
         <v>0</v>
@@ -22598,13 +22598,13 @@
         <v>0</v>
       </c>
       <c r="P28" s="7" t="n">
-        <v>5450476.84</v>
+        <v>5978542.15</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>0.9116732312408299</v>
+        <v>0.9117000000000001</v>
       </c>
       <c r="R28" s="7" t="n">
-        <v>528065.3100000001</v>
+        <v>528065.11</v>
       </c>
       <c r="S28" s="7" t="n">
         <v>0</v>
@@ -22872,7 +22872,7 @@
         <v>0</v>
       </c>
       <c r="P29" s="7" t="n">
-        <v>0</v>
+        <v>11620104.78</v>
       </c>
       <c r="Q29" s="9" t="n">
         <v>0</v>
@@ -23156,13 +23156,13 @@
         <v>0</v>
       </c>
       <c r="P30" s="7" t="n">
-        <v>4324004.79</v>
+        <v>4444784.22</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>0.9728267056347676</v>
+        <v>0.9728</v>
       </c>
       <c r="R30" s="7" t="n">
-        <v>120779.43</v>
+        <v>120779.41</v>
       </c>
       <c r="S30" s="7" t="n">
         <v>0</v>
@@ -23444,10 +23444,10 @@
         <v>0</v>
       </c>
       <c r="P31" s="7" t="n">
-        <v>2226331.45</v>
+        <v>2755604.93</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>0.8079283883412126</v>
+        <v>0.8079000000000001</v>
       </c>
       <c r="R31" s="7" t="n">
         <v>529273.48</v>
@@ -23724,7 +23724,7 @@
         <v>0</v>
       </c>
       <c r="P32" s="7" t="n">
-        <v>0</v>
+        <v>1712576.84</v>
       </c>
       <c r="Q32" s="9" t="n">
         <v>0</v>
@@ -24008,13 +24008,13 @@
         <v>0</v>
       </c>
       <c r="P33" s="7" t="n">
-        <v>56408430.85</v>
+        <v>58086688.76</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>0.971107702197759</v>
+        <v>0.9711</v>
       </c>
       <c r="R33" s="7" t="n">
-        <v>1678257.91</v>
+        <v>1678137.85</v>
       </c>
       <c r="S33" s="7" t="n">
         <v>0</v>
@@ -24282,10 +24282,10 @@
         <v>0</v>
       </c>
       <c r="P34" s="7" t="n">
-        <v>9021796.75</v>
+        <v>18996888.26</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>0.4749091865216877</v>
+        <v>0.4749</v>
       </c>
       <c r="R34" s="7" t="n">
         <v>9975091.51</v>
@@ -24562,13 +24562,13 @@
         <v>0</v>
       </c>
       <c r="P35" s="7" t="n">
-        <v>9986334.550000001</v>
+        <v>11942741.09</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>0.8361844634111548</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="R35" s="7" t="n">
-        <v>1956406.54</v>
+        <v>1956406.46</v>
       </c>
       <c r="S35" s="7" t="n">
         <v>0</v>
@@ -24842,10 +24842,10 @@
         <v>0</v>
       </c>
       <c r="P36" s="7" t="n">
-        <v>50454918.61</v>
+        <v>54913544.95</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>0.9188064375727395</v>
+        <v>0.9188</v>
       </c>
       <c r="R36" s="7" t="n">
         <v>4458626.34</v>
@@ -25406,10 +25406,10 @@
         <v>0</v>
       </c>
       <c r="P38" s="7" t="n">
-        <v>9661616.369999999</v>
+        <v>9751616.369999999</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>0.9907707608067029</v>
+        <v>0.9908</v>
       </c>
       <c r="R38" s="7" t="n">
         <v>90000</v>
@@ -25690,13 +25690,13 @@
         <v>0</v>
       </c>
       <c r="P39" s="7" t="n">
-        <v>13792679.65</v>
+        <v>13792679.79</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>0.9999999898496883</v>
+        <v>1</v>
       </c>
       <c r="R39" s="7" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="S39" s="7" t="n">
         <v>0</v>
@@ -25978,13 +25978,13 @@
         <v>0</v>
       </c>
       <c r="P40" s="7" t="n">
-        <v>6488132.93</v>
+        <v>7704834.91</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>0.8420859117408395</v>
+        <v>0.8421</v>
       </c>
       <c r="R40" s="7" t="n">
-        <v>1216701.98</v>
+        <v>1216701.97</v>
       </c>
       <c r="S40" s="7" t="n">
         <v>0</v>
@@ -26258,13 +26258,13 @@
         <v>0</v>
       </c>
       <c r="P41" s="7" t="n">
-        <v>74305044.28</v>
+        <v>80552394.92</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>0.9224436387496049</v>
+        <v>0.9224</v>
       </c>
       <c r="R41" s="7" t="n">
-        <v>6247350.64</v>
+        <v>6247349.45</v>
       </c>
       <c r="S41" s="7" t="n">
         <v>0</v>
@@ -26538,13 +26538,13 @@
         <v>0</v>
       </c>
       <c r="P42" s="7" t="n">
-        <v>6453162.33</v>
+        <v>6453162.72</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>0.9999999395645179</v>
+        <v>1</v>
       </c>
       <c r="R42" s="7" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="S42" s="7" t="n">
         <v>0</v>
@@ -26818,13 +26818,13 @@
         <v>0</v>
       </c>
       <c r="P43" s="7" t="n">
-        <v>25313733.13</v>
+        <v>37535912.65</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>0.6743870427778181</v>
+        <v>0.6744</v>
       </c>
       <c r="R43" s="7" t="n">
-        <v>12222179.52</v>
+        <v>12222179.43</v>
       </c>
       <c r="S43" s="7" t="n">
         <v>0</v>
@@ -27102,10 +27102,10 @@
         <v>0</v>
       </c>
       <c r="P44" s="7" t="n">
-        <v>3034704.58</v>
+        <v>3107538.75</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>0.9765621040123796</v>
+        <v>0.9765999999999999</v>
       </c>
       <c r="R44" s="7" t="n">
         <v>72834.17</v>
@@ -27386,10 +27386,10 @@
         <v>0</v>
       </c>
       <c r="P45" s="7" t="n">
-        <v>41562191.24</v>
+        <v>51359899.57</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>0.8092342778699091</v>
+        <v>0.8092</v>
       </c>
       <c r="R45" s="7" t="n">
         <v>9797708.33</v>
@@ -27670,10 +27670,10 @@
         <v>0</v>
       </c>
       <c r="P46" s="7" t="n">
-        <v>13242495.84</v>
+        <v>13242425.64</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>1.000005301143605</v>
+        <v>1</v>
       </c>
       <c r="R46" s="7" t="n">
         <v>-70.2</v>
@@ -27958,10 +27958,10 @@
         <v>0</v>
       </c>
       <c r="P47" s="7" t="n">
-        <v>6450491.31</v>
+        <v>7234583.77</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>0.8916188567403928</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="R47" s="7" t="n">
         <v>784092.46</v>
@@ -28242,13 +28242,13 @@
         <v>0</v>
       </c>
       <c r="P48" s="7" t="n">
-        <v>11566431.39</v>
+        <v>12560309.12</v>
       </c>
       <c r="Q48" s="9" t="n">
-        <v>0.9208715549510299</v>
+        <v>0.9209000000000001</v>
       </c>
       <c r="R48" s="7" t="n">
-        <v>993877.73</v>
+        <v>993876.73</v>
       </c>
       <c r="S48" s="7" t="n">
         <v>0</v>
@@ -28526,13 +28526,13 @@
         <v>0</v>
       </c>
       <c r="P49" s="7" t="n">
-        <v>20500685.69</v>
+        <v>22472818</v>
       </c>
       <c r="Q49" s="9" t="n">
-        <v>0.9122436576489871</v>
+        <v>0.9122</v>
       </c>
       <c r="R49" s="7" t="n">
-        <v>1972132.31</v>
+        <v>1972132.32</v>
       </c>
       <c r="S49" s="7" t="n">
         <v>0</v>
@@ -28810,13 +28810,13 @@
         <v>0</v>
       </c>
       <c r="P50" s="7" t="n">
-        <v>43785880.08</v>
+        <v>45237596.81</v>
       </c>
       <c r="Q50" s="9" t="n">
-        <v>0.9679090660784375</v>
+        <v>0.9865</v>
       </c>
       <c r="R50" s="7" t="n">
-        <v>1451716.73</v>
+        <v>610868.61</v>
       </c>
       <c r="S50" s="7" t="n">
         <v>0</v>
@@ -29090,10 +29090,10 @@
         <v>0</v>
       </c>
       <c r="P51" s="7" t="n">
-        <v>133236.58</v>
+        <v>12679339.18</v>
       </c>
       <c r="Q51" s="9" t="n">
-        <v>0.01050816435371989</v>
+        <v>0.0105</v>
       </c>
       <c r="R51" s="7" t="n">
         <v>12546102.6</v>
@@ -29374,10 +29374,10 @@
         <v>0</v>
       </c>
       <c r="P52" s="7" t="n">
-        <v>33048630.33</v>
+        <v>34508101.15</v>
       </c>
       <c r="Q52" s="9" t="n">
-        <v>0.9577064291756896</v>
+        <v>0.9577</v>
       </c>
       <c r="R52" s="7" t="n">
         <v>1459470.82</v>
@@ -29658,13 +29658,13 @@
         <v>0</v>
       </c>
       <c r="P53" s="7" t="n">
-        <v>151308</v>
+        <v>11494433.26</v>
       </c>
       <c r="Q53" s="9" t="n">
-        <v>0.01316358941562988</v>
+        <v>0.0132</v>
       </c>
       <c r="R53" s="7" t="n">
-        <v>11343125.26</v>
+        <v>11343147.64</v>
       </c>
       <c r="S53" s="7" t="n">
         <v>0</v>
@@ -29942,10 +29942,10 @@
         <v>0</v>
       </c>
       <c r="P54" s="7" t="n">
-        <v>13332401.6</v>
+        <v>20185137.81</v>
       </c>
       <c r="Q54" s="9" t="n">
-        <v>0.6605058496749495</v>
+        <v>0.6605</v>
       </c>
       <c r="R54" s="7" t="n">
         <v>6852736.21</v>
@@ -30226,10 +30226,10 @@
         <v>0</v>
       </c>
       <c r="P55" s="7" t="n">
-        <v>12534756.7</v>
+        <v>30477728.43</v>
       </c>
       <c r="Q55" s="9" t="n">
-        <v>0.4112759495442489</v>
+        <v>0.4113</v>
       </c>
       <c r="R55" s="7" t="n">
         <v>17942971.73</v>
@@ -30514,13 +30514,13 @@
         <v>0</v>
       </c>
       <c r="P56" s="7" t="n">
-        <v>6523029.66</v>
+        <v>6478069.43</v>
       </c>
       <c r="Q56" s="9" t="n">
-        <v>1.006940374827073</v>
+        <v>1</v>
       </c>
       <c r="R56" s="7" t="n">
-        <v>-44960.23</v>
+        <v>39.99</v>
       </c>
       <c r="S56" s="7" t="n">
         <v>0</v>
@@ -30802,10 +30802,10 @@
         <v>0</v>
       </c>
       <c r="P57" s="7" t="n">
-        <v>6007931.02</v>
+        <v>6055289.34</v>
       </c>
       <c r="Q57" s="9" t="n">
-        <v>0.9921790161723304</v>
+        <v>0.9922</v>
       </c>
       <c r="R57" s="7" t="n">
         <v>47358.32</v>
@@ -31086,10 +31086,10 @@
         <v>0</v>
       </c>
       <c r="P58" s="7" t="n">
-        <v>5551029.21</v>
+        <v>5722613.87</v>
       </c>
       <c r="Q58" s="9" t="n">
-        <v>0.9700163834398283</v>
+        <v>0.97</v>
       </c>
       <c r="R58" s="7" t="n">
         <v>171584.66</v>
@@ -31374,13 +31374,13 @@
         <v>0</v>
       </c>
       <c r="P59" s="7" t="n">
-        <v>5580983.94</v>
+        <v>5581731.3</v>
       </c>
       <c r="Q59" s="9" t="n">
-        <v>0.9998661060592436</v>
+        <v>1</v>
       </c>
       <c r="R59" s="7" t="n">
-        <v>747.36</v>
+        <v>1</v>
       </c>
       <c r="S59" s="7" t="n">
         <v>0</v>
@@ -31658,10 +31658,10 @@
         <v>0</v>
       </c>
       <c r="P60" s="7" t="n">
-        <v>12032786.93</v>
+        <v>13208831.36</v>
       </c>
       <c r="Q60" s="9" t="n">
-        <v>0.9109652929962155</v>
+        <v>0.9109999999999999</v>
       </c>
       <c r="R60" s="7" t="n">
         <v>1176044.43</v>
@@ -31946,13 +31946,13 @@
         <v>0</v>
       </c>
       <c r="P61" s="7" t="n">
-        <v>111124067.68</v>
+        <v>113557951.65</v>
       </c>
       <c r="Q61" s="9" t="n">
-        <v>0.9785670317698092</v>
+        <v>0.9786</v>
       </c>
       <c r="R61" s="7" t="n">
-        <v>2433883.97</v>
+        <v>2424755.97</v>
       </c>
       <c r="S61" s="7" t="n">
         <v>0</v>
@@ -32234,10 +32234,10 @@
         <v>0</v>
       </c>
       <c r="P62" s="7" t="n">
-        <v>8552770.91</v>
+        <v>12950372.72</v>
       </c>
       <c r="Q62" s="9" t="n">
-        <v>0.6604266220686813</v>
+        <v>0.6604000000000001</v>
       </c>
       <c r="R62" s="7" t="n">
         <v>4397601.81</v>
@@ -32518,13 +32518,13 @@
         <v>0</v>
       </c>
       <c r="P63" s="7" t="n">
-        <v>20859058.41</v>
+        <v>20859068.44</v>
       </c>
       <c r="Q63" s="9" t="n">
-        <v>0.9999995191539819</v>
+        <v>1</v>
       </c>
       <c r="R63" s="7" t="n">
-        <v>10.03</v>
+        <v>0</v>
       </c>
       <c r="S63" s="7" t="n">
         <v>0</v>
@@ -32806,13 +32806,13 @@
         <v>0</v>
       </c>
       <c r="P64" s="7" t="n">
-        <v>81959611</v>
+        <v>81950979.23</v>
       </c>
       <c r="Q64" s="9" t="n">
-        <v>1.000105328454658</v>
+        <v>1</v>
       </c>
       <c r="R64" s="7" t="n">
-        <v>-8631.77</v>
+        <v>0.23</v>
       </c>
       <c r="S64" s="7" t="n">
         <v>0</v>
@@ -33086,10 +33086,10 @@
         <v>0</v>
       </c>
       <c r="P65" s="7" t="n">
-        <v>2042159.29</v>
+        <v>8973983.869999999</v>
       </c>
       <c r="Q65" s="9" t="n">
-        <v>0.2275644039016977</v>
+        <v>0.2276</v>
       </c>
       <c r="R65" s="7" t="n">
         <v>6931824.58</v>
@@ -33366,13 +33366,13 @@
         <v>0</v>
       </c>
       <c r="P66" s="7" t="n">
-        <v>4852080.3</v>
+        <v>11928823.02</v>
       </c>
       <c r="Q66" s="9" t="n">
-        <v>0.4067526437323236</v>
+        <v>0.4067</v>
       </c>
       <c r="R66" s="7" t="n">
-        <v>7076742.72</v>
+        <v>7076780.22</v>
       </c>
       <c r="S66" s="7" t="n">
         <v>0</v>
@@ -33650,13 +33650,13 @@
         <v>0</v>
       </c>
       <c r="P67" s="7" t="n">
-        <v>11551184.42</v>
+        <v>11551184.44</v>
       </c>
       <c r="Q67" s="9" t="n">
-        <v>0.9999999982685759</v>
+        <v>1</v>
       </c>
       <c r="R67" s="7" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="S67" s="7" t="n">
         <v>0</v>
@@ -33934,13 +33934,13 @@
         <v>0</v>
       </c>
       <c r="P68" s="7" t="n">
-        <v>41516316.78</v>
+        <v>44149151.5</v>
       </c>
       <c r="Q68" s="9" t="n">
-        <v>0.940364998407727</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="R68" s="7" t="n">
-        <v>2632834.72</v>
+        <v>2648192.01</v>
       </c>
       <c r="S68" s="7" t="n">
         <v>0</v>
@@ -34214,10 +34214,10 @@
         <v>0</v>
       </c>
       <c r="P69" s="7" t="n">
-        <v>1496414.32</v>
+        <v>1498793.43</v>
       </c>
       <c r="Q69" s="9" t="n">
-        <v>0.9984126498339402</v>
+        <v>0.9984000000000001</v>
       </c>
       <c r="R69" s="7" t="n">
         <v>2379.11</v>
@@ -34498,10 +34498,10 @@
         <v>0</v>
       </c>
       <c r="P70" s="7" t="n">
-        <v>64026819.34</v>
+        <v>89008310.65000001</v>
       </c>
       <c r="Q70" s="9" t="n">
-        <v>0.7193352943386079</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="R70" s="7" t="n">
         <v>24981491.31</v>
@@ -34778,10 +34778,10 @@
         <v>0</v>
       </c>
       <c r="P71" s="7" t="n">
-        <v>266299.23</v>
+        <v>8995898.050000001</v>
       </c>
       <c r="Q71" s="9" t="n">
-        <v>0.02960229523721647</v>
+        <v>0</v>
       </c>
       <c r="R71" s="7" t="n">
         <v>8729598.82</v>
@@ -35069,7 +35069,7 @@
         <v>18264452.89</v>
       </c>
       <c r="Q72" s="9" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="R72" s="7" t="n">
         <v>0</v>
@@ -35350,10 +35350,10 @@
         <v>0</v>
       </c>
       <c r="P73" s="7" t="n">
-        <v>88995375.53</v>
+        <v>90986818.17</v>
       </c>
       <c r="Q73" s="9" t="n">
-        <v>0.9781128444751286</v>
+        <v>0.9781</v>
       </c>
       <c r="R73" s="7" t="n">
         <v>1991442.64</v>
@@ -35634,10 +35634,10 @@
         <v>0</v>
       </c>
       <c r="P74" s="7" t="n">
-        <v>35196032.93</v>
+        <v>36880209</v>
       </c>
       <c r="Q74" s="9" t="n">
-        <v>0.9543338794527981</v>
+        <v>0.9543</v>
       </c>
       <c r="R74" s="7" t="n">
         <v>1684176.07</v>
@@ -35918,13 +35918,13 @@
         <v>0</v>
       </c>
       <c r="P75" s="7" t="n">
-        <v>19910338.67</v>
+        <v>20229149.79</v>
       </c>
       <c r="Q75" s="9" t="n">
-        <v>0.9842400138755413</v>
+        <v>0.9842</v>
       </c>
       <c r="R75" s="7" t="n">
-        <v>318811.12</v>
+        <v>318751.42</v>
       </c>
       <c r="S75" s="7" t="n">
         <v>0</v>
@@ -36202,10 +36202,10 @@
         <v>0</v>
       </c>
       <c r="P76" s="7" t="n">
-        <v>56828.03</v>
+        <v>2317778.22</v>
       </c>
       <c r="Q76" s="9" t="n">
-        <v>0.02451832082536352</v>
+        <v>0.0245</v>
       </c>
       <c r="R76" s="7" t="n">
         <v>2260950.19</v>
@@ -36482,13 +36482,13 @@
         <v>0</v>
       </c>
       <c r="P77" s="7" t="n">
-        <v>3552073.1</v>
+        <v>3552093.82</v>
       </c>
       <c r="Q77" s="9" t="n">
-        <v>0.9999941668207402</v>
+        <v>1</v>
       </c>
       <c r="R77" s="7" t="n">
-        <v>20.72</v>
+        <v>20.69</v>
       </c>
       <c r="S77" s="7" t="n">
         <v>0</v>
@@ -36762,7 +36762,7 @@
         <v>0</v>
       </c>
       <c r="P78" s="7" t="n">
-        <v>0</v>
+        <v>10134014.66</v>
       </c>
       <c r="Q78" s="9" t="n">
         <v>0</v>
@@ -37052,7 +37052,7 @@
         <v>1</v>
       </c>
       <c r="R79" s="7" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="S79" s="7" t="n">
         <v>0</v>
@@ -37334,10 +37334,10 @@
         <v>0</v>
       </c>
       <c r="P80" s="7" t="n">
-        <v>147280622.62</v>
+        <v>148784461.49</v>
       </c>
       <c r="Q80" s="9" t="n">
-        <v>0.9898925005007927</v>
+        <v>0.9899</v>
       </c>
       <c r="R80" s="7" t="n">
         <v>1503838.87</v>
@@ -37614,10 +37614,10 @@
         <v>0</v>
       </c>
       <c r="P81" s="7" t="n">
-        <v>12576165.07</v>
+        <v>22759968.59</v>
       </c>
       <c r="Q81" s="9" t="n">
-        <v>0.5525563455973117</v>
+        <v>0.5526</v>
       </c>
       <c r="R81" s="7" t="n">
         <v>10183803.52</v>
@@ -37902,10 +37902,10 @@
         <v>0</v>
       </c>
       <c r="P82" s="7" t="n">
-        <v>1940441.71</v>
+        <v>27739392.32</v>
       </c>
       <c r="Q82" s="9" t="n">
-        <v>0.06995256736756085</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R82" s="7" t="n">
         <v>25798950.61</v>
@@ -38182,10 +38182,10 @@
         <v>0</v>
       </c>
       <c r="P83" s="7" t="n">
-        <v>5260332.26</v>
+        <v>5312585.57</v>
       </c>
       <c r="Q83" s="9" t="n">
-        <v>0.9901642412509883</v>
+        <v>0.9902</v>
       </c>
       <c r="R83" s="7" t="n">
         <v>52253.31</v>
@@ -38466,13 +38466,13 @@
         <v>0</v>
       </c>
       <c r="P84" s="7" t="n">
-        <v>5319860.7</v>
+        <v>5361446.28</v>
       </c>
       <c r="Q84" s="9" t="n">
-        <v>0.9922435891682567</v>
+        <v>0.9922</v>
       </c>
       <c r="R84" s="7" t="n">
-        <v>41585.58</v>
+        <v>41684.58</v>
       </c>
       <c r="S84" s="7" t="n">
         <v>0</v>
@@ -38746,13 +38746,13 @@
         <v>0</v>
       </c>
       <c r="P85" s="7" t="n">
-        <v>2867505.09</v>
+        <v>2994510.29</v>
       </c>
       <c r="Q85" s="9" t="n">
-        <v>0.9575873222329117</v>
+        <v>0.9577</v>
       </c>
       <c r="R85" s="7" t="n">
-        <v>127005.2</v>
+        <v>126804.97</v>
       </c>
       <c r="S85" s="7" t="n">
         <v>0</v>
@@ -39026,10 +39026,10 @@
         <v>0</v>
       </c>
       <c r="P86" s="7" t="n">
-        <v>8156656.13</v>
+        <v>8156656.19</v>
       </c>
       <c r="Q86" s="9" t="n">
-        <v>0.9999999926440444</v>
+        <v>1</v>
       </c>
       <c r="R86" s="7" t="n">
         <v>0.06</v>
@@ -39310,13 +39310,13 @@
         <v>0</v>
       </c>
       <c r="P87" s="7" t="n">
-        <v>7148655.62</v>
+        <v>7155724.39</v>
       </c>
       <c r="Q87" s="9" t="n">
-        <v>0.9990121517243065</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="R87" s="7" t="n">
-        <v>7068.77</v>
+        <v>7068.79</v>
       </c>
       <c r="S87" s="7" t="n">
         <v>0</v>
@@ -39598,13 +39598,13 @@
         <v>0</v>
       </c>
       <c r="P88" s="7" t="n">
-        <v>5991696.66</v>
+        <v>6765672.29</v>
       </c>
       <c r="Q88" s="9" t="n">
-        <v>0.8856025540663601</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="R88" s="7" t="n">
-        <v>773975.63</v>
+        <v>773975.71</v>
       </c>
       <c r="S88" s="7" t="n">
         <v>0</v>
@@ -39878,10 +39878,10 @@
         <v>0</v>
       </c>
       <c r="P89" s="7" t="n">
-        <v>137475.09</v>
+        <v>21672861.46</v>
       </c>
       <c r="Q89" s="9" t="n">
-        <v>0.006343190549790927</v>
+        <v>0.0063</v>
       </c>
       <c r="R89" s="7" t="n">
         <v>21535386.37</v>
@@ -40158,10 +40158,10 @@
         <v>0</v>
       </c>
       <c r="P90" s="7" t="n">
-        <v>31178236.21</v>
+        <v>32836774.76</v>
       </c>
       <c r="Q90" s="9" t="n">
-        <v>0.9494914295900844</v>
+        <v>0.9495</v>
       </c>
       <c r="R90" s="7" t="n">
         <v>1658538.55</v>
@@ -40438,7 +40438,7 @@
         <v>0</v>
       </c>
       <c r="P91" s="7" t="n">
-        <v>0</v>
+        <v>14144248.92</v>
       </c>
       <c r="Q91" s="9" t="n">
         <v>0</v>
@@ -40722,13 +40722,13 @@
         <v>0</v>
       </c>
       <c r="P92" s="7" t="n">
-        <v>1923627.24</v>
+        <v>1923627.23</v>
       </c>
       <c r="Q92" s="9" t="n">
-        <v>1.000000005198513</v>
+        <v>1</v>
       </c>
       <c r="R92" s="7" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="S92" s="7" t="n">
         <v>0</v>
@@ -41006,10 +41006,10 @@
         <v>0</v>
       </c>
       <c r="P93" s="7" t="n">
-        <v>127835.64</v>
+        <v>16774604.06</v>
       </c>
       <c r="Q93" s="9" t="n">
-        <v>0.007620784344164126</v>
+        <v>0.0076</v>
       </c>
       <c r="R93" s="7" t="n">
         <v>16646768.42</v>
@@ -41290,7 +41290,7 @@
         <v>0</v>
       </c>
       <c r="P94" s="7" t="n">
-        <v>0</v>
+        <v>6784130.44</v>
       </c>
       <c r="Q94" s="9" t="n">
         <v>0</v>
@@ -41574,10 +41574,10 @@
         <v>0</v>
       </c>
       <c r="P95" s="7" t="n">
-        <v>30456294.33</v>
+        <v>30599999.01</v>
       </c>
       <c r="Q95" s="9" t="n">
-        <v>0.9953037684755141</v>
+        <v>0.9953</v>
       </c>
       <c r="R95" s="7" t="n">
         <v>143704.68</v>
@@ -41854,10 +41854,10 @@
         <v>0</v>
       </c>
       <c r="P96" s="7" t="n">
-        <v>264324.6</v>
+        <v>2394811.95</v>
       </c>
       <c r="Q96" s="9" t="n">
-        <v>0.1103738437583794</v>
+        <v>0.1104</v>
       </c>
       <c r="R96" s="7" t="n">
         <v>2130487.35</v>
@@ -42138,13 +42138,13 @@
         <v>0</v>
       </c>
       <c r="P97" s="7" t="n">
-        <v>26930984.01</v>
+        <v>26946699.36</v>
       </c>
       <c r="Q97" s="9" t="n">
-        <v>0.9994167987036167</v>
+        <v>0.9994</v>
       </c>
       <c r="R97" s="7" t="n">
-        <v>15715.35</v>
+        <v>15715.34</v>
       </c>
       <c r="S97" s="7" t="n">
         <v>0</v>
@@ -42422,10 +42422,10 @@
         <v>0</v>
       </c>
       <c r="P98" s="7" t="n">
-        <v>5996889.68</v>
+        <v>6014775.77</v>
       </c>
       <c r="Q98" s="9" t="n">
-        <v>0.9970263080979328</v>
+        <v>0.997</v>
       </c>
       <c r="R98" s="7" t="n">
         <v>17886.09</v>
@@ -42706,10 +42706,10 @@
         <v>0</v>
       </c>
       <c r="P99" s="7" t="n">
-        <v>3538001.16</v>
+        <v>3569195.39</v>
       </c>
       <c r="Q99" s="9" t="n">
-        <v>0.9912601506526095</v>
+        <v>0.9913</v>
       </c>
       <c r="R99" s="7" t="n">
         <v>31194.23</v>
@@ -42986,10 +42986,10 @@
         <v>0</v>
       </c>
       <c r="P100" s="7" t="n">
-        <v>2975297.32</v>
+        <v>2975474.34</v>
       </c>
       <c r="Q100" s="9" t="n">
-        <v>0.9999405069646813</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="R100" s="7" t="n">
         <v>177.02</v>
@@ -43546,10 +43546,10 @@
         <v>0</v>
       </c>
       <c r="P102" s="7" t="n">
-        <v>1932548.63</v>
+        <v>1988555.07</v>
       </c>
       <c r="Q102" s="9" t="n">
-        <v>0.9718356102654981</v>
+        <v>0.9718000000000001</v>
       </c>
       <c r="R102" s="7" t="n">
         <v>56006.44</v>
@@ -43826,13 +43826,13 @@
         <v>0</v>
       </c>
       <c r="P103" s="7" t="n">
-        <v>1678310.19</v>
+        <v>1690234.37</v>
       </c>
       <c r="Q103" s="9" t="n">
-        <v>0.9929452505453428</v>
+        <v>0.9931</v>
       </c>
       <c r="R103" s="7" t="n">
-        <v>11924.18</v>
+        <v>11624.18</v>
       </c>
       <c r="S103" s="7" t="n">
         <v>0</v>
@@ -44110,13 +44110,13 @@
         <v>0</v>
       </c>
       <c r="P104" s="7" t="n">
-        <v>1612016.33</v>
+        <v>1612154.63</v>
       </c>
       <c r="Q104" s="9" t="n">
-        <v>0.9999142141842808</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="R104" s="7" t="n">
-        <v>138.3</v>
+        <v>129.78</v>
       </c>
       <c r="S104" s="7" t="n">
         <v>0</v>
@@ -44394,13 +44394,13 @@
         <v>0</v>
       </c>
       <c r="P105" s="7" t="n">
-        <v>25102277.93</v>
+        <v>25179808.67</v>
       </c>
       <c r="Q105" s="9" t="n">
-        <v>0.9969209162382409</v>
+        <v>0.9969</v>
       </c>
       <c r="R105" s="7" t="n">
-        <v>77530.74000000001</v>
+        <v>77530.64</v>
       </c>
       <c r="S105" s="7" t="n">
         <v>0</v>
@@ -44681,10 +44681,10 @@
         <v>666913.6800000001</v>
       </c>
       <c r="Q106" s="9" t="n">
-        <v>1</v>
+        <v>0.8991</v>
       </c>
       <c r="R106" s="7" t="n">
-        <v>0</v>
+        <v>67272.37</v>
       </c>
       <c r="S106" s="7" t="n">
         <v>0</v>
@@ -44962,10 +44962,10 @@
         <v>0</v>
       </c>
       <c r="P107" s="7" t="n">
-        <v>1006235.15</v>
+        <v>1052239.53</v>
       </c>
       <c r="Q107" s="9" t="n">
-        <v>0.9562795554734577</v>
+        <v>0.9562999999999999</v>
       </c>
       <c r="R107" s="7" t="n">
         <v>46004.38</v>
@@ -45246,10 +45246,10 @@
         <v>0</v>
       </c>
       <c r="P108" s="7" t="n">
-        <v>13180256.4</v>
+        <v>14782911.98</v>
       </c>
       <c r="Q108" s="9" t="n">
-        <v>0.8915872879329693</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="R108" s="7" t="n">
         <v>1602655.58</v>
@@ -45533,7 +45533,7 @@
         <v>62980000</v>
       </c>
       <c r="Q109" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R109" s="7" t="n">
         <v>0</v>
@@ -45814,13 +45814,13 @@
         <v>0</v>
       </c>
       <c r="P110" s="7" t="n">
-        <v>12888606.56</v>
+        <v>13554947.83</v>
       </c>
       <c r="Q110" s="9" t="n">
-        <v>0.9508414729177163</v>
+        <v>0.9508</v>
       </c>
       <c r="R110" s="7" t="n">
-        <v>666341.27</v>
+        <v>666441.27</v>
       </c>
       <c r="S110" s="7" t="n">
         <v>0</v>
@@ -46098,10 +46098,10 @@
         <v>0</v>
       </c>
       <c r="P111" s="7" t="n">
-        <v>296101.87</v>
+        <v>13677862.32</v>
       </c>
       <c r="Q111" s="9" t="n">
-        <v>0.02164825636291388</v>
+        <v>0.0216</v>
       </c>
       <c r="R111" s="7" t="n">
         <v>13381760.45</v>
@@ -46382,10 +46382,10 @@
         <v>0</v>
       </c>
       <c r="P112" s="7" t="n">
-        <v>54872063.4</v>
+        <v>56185153.92</v>
       </c>
       <c r="Q112" s="9" t="n">
-        <v>0.9766292262566429</v>
+        <v>0.9765999999999999</v>
       </c>
       <c r="R112" s="7" t="n">
         <v>1313090.52</v>
@@ -46666,10 +46666,10 @@
         <v>0</v>
       </c>
       <c r="P113" s="7" t="n">
-        <v>13048536.54</v>
+        <v>16880240</v>
       </c>
       <c r="Q113" s="9" t="n">
-        <v>0.7730065769207074</v>
+        <v>0.773</v>
       </c>
       <c r="R113" s="7" t="n">
         <v>3831703.46</v>
@@ -46950,13 +46950,13 @@
         <v>0</v>
       </c>
       <c r="P114" s="7" t="n">
-        <v>5728240.72</v>
+        <v>6519257.05</v>
       </c>
       <c r="Q114" s="9" t="n">
-        <v>0.8786646509052747</v>
+        <v>0.8787</v>
       </c>
       <c r="R114" s="7" t="n">
-        <v>791016.33</v>
+        <v>791016.1899999999</v>
       </c>
       <c r="S114" s="7" t="n">
         <v>0</v>
@@ -47234,13 +47234,13 @@
         <v>0</v>
       </c>
       <c r="P115" s="7" t="n">
-        <v>45858219.18</v>
+        <v>48302952.43</v>
       </c>
       <c r="Q115" s="9" t="n">
-        <v>0.9493874985479848</v>
+        <v>0.9493</v>
       </c>
       <c r="R115" s="7" t="n">
-        <v>2444733.25</v>
+        <v>2449729.13</v>
       </c>
       <c r="S115" s="7" t="n">
         <v>0</v>
@@ -47518,10 +47518,10 @@
         <v>0</v>
       </c>
       <c r="P116" s="7" t="n">
-        <v>255684.47</v>
+        <v>3615856.15</v>
       </c>
       <c r="Q116" s="9" t="n">
-        <v>0.07071201380619081</v>
+        <v>0.0707</v>
       </c>
       <c r="R116" s="7" t="n">
         <v>3360171.68</v>
@@ -47802,10 +47802,10 @@
         <v>0</v>
       </c>
       <c r="P117" s="7" t="n">
-        <v>8398407.23</v>
+        <v>24165422.12</v>
       </c>
       <c r="Q117" s="9" t="n">
-        <v>0.3475381968622528</v>
+        <v>0.3475</v>
       </c>
       <c r="R117" s="7" t="n">
         <v>15767014.89</v>
@@ -48086,13 +48086,13 @@
         <v>0</v>
       </c>
       <c r="P118" s="7" t="n">
-        <v>14985593.44</v>
+        <v>14995089.28</v>
       </c>
       <c r="Q118" s="9" t="n">
-        <v>0.9993667366814106</v>
+        <v>0.9994</v>
       </c>
       <c r="R118" s="7" t="n">
-        <v>9495.84</v>
+        <v>9530.83</v>
       </c>
       <c r="S118" s="7" t="n">
         <v>0</v>
@@ -48370,13 +48370,13 @@
         <v>0</v>
       </c>
       <c r="P119" s="7" t="n">
-        <v>14660281.99</v>
+        <v>15078640.21</v>
       </c>
       <c r="Q119" s="9" t="n">
-        <v>0.9722549106435638</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="R119" s="7" t="n">
-        <v>418358.22</v>
+        <v>418357.84</v>
       </c>
       <c r="S119" s="7" t="n">
         <v>0</v>
@@ -48654,10 +48654,10 @@
         <v>0</v>
       </c>
       <c r="P120" s="7" t="n">
-        <v>21925638.52</v>
+        <v>24590858.27</v>
       </c>
       <c r="Q120" s="9" t="n">
-        <v>0.8916174571567731</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="R120" s="7" t="n">
         <v>2665219.75</v>
@@ -48938,10 +48938,10 @@
         <v>0</v>
       </c>
       <c r="P121" s="7" t="n">
-        <v>9082408.67</v>
+        <v>16932981.45</v>
       </c>
       <c r="Q121" s="9" t="n">
-        <v>0.5363738628556755</v>
+        <v>0.5364</v>
       </c>
       <c r="R121" s="7" t="n">
         <v>7850572.78</v>

--- a/MEDIÇÕES_CONSOLIDADO.xlsx
+++ b/MEDIÇÕES_CONSOLIDADO.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CK51"/>
+  <dimension ref="A1:CK52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>330018/001109/2022</t>
+          <t>330018/001213/2022</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -9263,16 +9263,16 @@
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1174</v>
+        <v>664</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>45019</v>
+        <v>45398</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>46193</v>
+        <v>46062</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>22825141.32</v>
+        <v>6765672.29</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
@@ -9281,38 +9281,38 @@
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>JAQUELINE PASTÓRIO</t>
-        </is>
-      </c>
-      <c r="J31" s="8" t="inlineStr">
-        <is>
-          <t>SL</t>
+          <t>CARLOS FERNANDES</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>BX</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>Barra Mansa</t>
+          <t>Belford Roxo</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>STATLED</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="M31" s="7" t="n">
-        <v>2715707.77</v>
+        <v>4600873.35</v>
       </c>
       <c r="N31" s="7" t="n">
-        <v>0</v>
+        <v>615349.64</v>
       </c>
       <c r="O31" s="7" t="n">
-        <v>22825141.32</v>
+        <v>6765672.29</v>
       </c>
       <c r="P31" s="9" t="n">
-        <v>0.5746</v>
+        <v>0.9754</v>
       </c>
       <c r="Q31" s="7" t="n">
-        <v>9709999.51</v>
+        <v>166531.04</v>
       </c>
       <c r="R31" s="7" t="n">
         <v>0</v>
@@ -9396,16 +9396,16 @@
         <v>0</v>
       </c>
       <c r="AS31" s="7" t="n">
-        <v>332774.27</v>
+        <v>0</v>
       </c>
       <c r="AT31" s="7" t="n">
-        <v>104762.28</v>
+        <v>0</v>
       </c>
       <c r="AU31" s="7" t="n">
-        <v>50095.55</v>
+        <v>0</v>
       </c>
       <c r="AV31" s="7" t="n">
-        <v>42609.02</v>
+        <v>0</v>
       </c>
       <c r="AW31" s="7" t="n">
         <v>0</v>
@@ -9429,52 +9429,52 @@
         <v>0</v>
       </c>
       <c r="BD31" s="7" t="n">
-        <v>612019.51</v>
+        <v>0</v>
       </c>
       <c r="BE31" s="7" t="n">
-        <v>328829.71</v>
+        <v>0</v>
       </c>
       <c r="BF31" s="7" t="n">
-        <v>938469.6899999999</v>
+        <v>0</v>
       </c>
       <c r="BG31" s="7" t="n">
-        <v>1567024.51</v>
+        <v>0</v>
       </c>
       <c r="BH31" s="7" t="n">
-        <v>1590990.36</v>
+        <v>219698.04</v>
       </c>
       <c r="BI31" s="7" t="n">
-        <v>1038577.32</v>
+        <v>180625.15</v>
       </c>
       <c r="BJ31" s="7" t="n">
-        <v>1233190.83</v>
+        <v>470617.93</v>
       </c>
       <c r="BK31" s="7" t="n">
-        <v>1162514</v>
+        <v>519882.19</v>
       </c>
       <c r="BL31" s="7" t="n">
-        <v>1397576.21</v>
+        <v>0</v>
       </c>
       <c r="BM31" s="7" t="n">
         <v>0</v>
       </c>
       <c r="BN31" s="7" t="n">
-        <v>454942.58</v>
+        <v>0</v>
       </c>
       <c r="BO31" s="7" t="n">
-        <v>514718.89</v>
+        <v>0</v>
       </c>
       <c r="BP31" s="7" t="n">
-        <v>0</v>
+        <v>669692.84</v>
       </c>
       <c r="BQ31" s="7" t="n">
-        <v>0</v>
+        <v>1778629.34</v>
       </c>
       <c r="BR31" s="7" t="n">
-        <v>0</v>
+        <v>853473.6</v>
       </c>
       <c r="BS31" s="7" t="n">
-        <v>0</v>
+        <v>791806.64</v>
       </c>
       <c r="BT31" s="7" t="n">
         <v>0</v>
@@ -9483,19 +9483,19 @@
         <v>0</v>
       </c>
       <c r="BV31" s="7" t="n">
-        <v>712587.61</v>
+        <v>0</v>
       </c>
       <c r="BW31" s="7" t="n">
-        <v>273654.72</v>
+        <v>0</v>
       </c>
       <c r="BX31" s="7" t="n">
-        <v>367117.37</v>
+        <v>0</v>
       </c>
       <c r="BY31" s="7" t="n">
-        <v>392686.6</v>
+        <v>507270.93</v>
       </c>
       <c r="BZ31" s="7" t="n">
-        <v>0</v>
+        <v>615349.64</v>
       </c>
       <c r="CA31" s="7" t="n">
         <v>0</v>
@@ -9537,7 +9537,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>330018/001148/2022</t>
+          <t>330018/001109/2022</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -9546,16 +9546,16 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>963</v>
+        <v>1174</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>45190</v>
+        <v>45019</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>46153</v>
+        <v>46193</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>26504288.68</v>
+        <v>22825141.32</v>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
@@ -9564,17 +9564,17 @@
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>CARLOS FERNANDES</t>
-        </is>
-      </c>
-      <c r="J32" s="11" t="inlineStr">
-        <is>
-          <t>BX</t>
+          <t>JAQUELINE PASTÓRIO</t>
+        </is>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>SL</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>Duque de Caxias</t>
+          <t>Barra Mansa</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -9583,19 +9583,19 @@
         </is>
       </c>
       <c r="M32" s="7" t="n">
-        <v>3253833.79</v>
+        <v>2715707.77</v>
       </c>
       <c r="N32" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O32" s="7" t="n">
-        <v>26504288.68</v>
+        <v>22825141.32</v>
       </c>
       <c r="P32" s="9" t="n">
-        <v>0.5414</v>
+        <v>0.5746</v>
       </c>
       <c r="Q32" s="7" t="n">
-        <v>12155577.59</v>
+        <v>9709999.51</v>
       </c>
       <c r="R32" s="7" t="n">
         <v>0</v>
@@ -9679,16 +9679,16 @@
         <v>0</v>
       </c>
       <c r="AS32" s="7" t="n">
-        <v>0</v>
+        <v>332774.27</v>
       </c>
       <c r="AT32" s="7" t="n">
-        <v>0</v>
+        <v>104762.28</v>
       </c>
       <c r="AU32" s="7" t="n">
-        <v>0</v>
+        <v>50095.55</v>
       </c>
       <c r="AV32" s="7" t="n">
-        <v>0</v>
+        <v>42609.02</v>
       </c>
       <c r="AW32" s="7" t="n">
         <v>0</v>
@@ -9706,46 +9706,46 @@
         <v>0</v>
       </c>
       <c r="BB32" s="7" t="n">
-        <v>232321.18</v>
+        <v>0</v>
       </c>
       <c r="BC32" s="7" t="n">
-        <v>239771.55</v>
+        <v>0</v>
       </c>
       <c r="BD32" s="7" t="n">
-        <v>346035.44</v>
+        <v>612019.51</v>
       </c>
       <c r="BE32" s="7" t="n">
-        <v>226819.14</v>
+        <v>328829.71</v>
       </c>
       <c r="BF32" s="7" t="n">
-        <v>1450319</v>
+        <v>938469.6899999999</v>
       </c>
       <c r="BG32" s="7" t="n">
-        <v>1463559.22</v>
+        <v>1567024.51</v>
       </c>
       <c r="BH32" s="7" t="n">
-        <v>1790742.29</v>
+        <v>1590990.36</v>
       </c>
       <c r="BI32" s="7" t="n">
-        <v>1884899.62</v>
+        <v>1038577.32</v>
       </c>
       <c r="BJ32" s="7" t="n">
-        <v>1446453.72</v>
+        <v>1233190.83</v>
       </c>
       <c r="BK32" s="7" t="n">
-        <v>1093250.95</v>
+        <v>1162514</v>
       </c>
       <c r="BL32" s="7" t="n">
-        <v>920705.1899999999</v>
+        <v>1397576.21</v>
       </c>
       <c r="BM32" s="7" t="n">
         <v>0</v>
       </c>
       <c r="BN32" s="7" t="n">
-        <v>186904.1</v>
+        <v>454942.58</v>
       </c>
       <c r="BO32" s="7" t="n">
-        <v>1214701.27</v>
+        <v>514718.89</v>
       </c>
       <c r="BP32" s="7" t="n">
         <v>0</v>
@@ -9766,16 +9766,16 @@
         <v>0</v>
       </c>
       <c r="BV32" s="7" t="n">
-        <v>0</v>
+        <v>712587.61</v>
       </c>
       <c r="BW32" s="7" t="n">
-        <v>1403044.06</v>
+        <v>273654.72</v>
       </c>
       <c r="BX32" s="7" t="n">
-        <v>320057.75</v>
+        <v>367117.37</v>
       </c>
       <c r="BY32" s="7" t="n">
-        <v>129126.61</v>
+        <v>392686.6</v>
       </c>
       <c r="BZ32" s="7" t="n">
         <v>0</v>
@@ -9820,7 +9820,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>330018/000675/2022</t>
+          <t>330018/001148/2022</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -9829,16 +9829,16 @@
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1103</v>
+        <v>963</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>44991</v>
+        <v>45190</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>46094</v>
+        <v>46153</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>20106028.53</v>
+        <v>26504288.68</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>GISELLE G. FONSECA</t>
+          <t>CARLOS FERNANDES</t>
         </is>
       </c>
       <c r="J33" s="11" t="inlineStr">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>Nova Iguaçu</t>
+          <t>Duque de Caxias</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -9866,19 +9866,19 @@
         </is>
       </c>
       <c r="M33" s="7" t="n">
-        <v>6197590.26</v>
+        <v>3253833.79</v>
       </c>
       <c r="N33" s="7" t="n">
-        <v>3545422.68</v>
+        <v>0</v>
       </c>
       <c r="O33" s="7" t="n">
-        <v>20106028.53</v>
+        <v>26504288.68</v>
       </c>
       <c r="P33" s="9" t="n">
-        <v>0.9666</v>
+        <v>0.5414</v>
       </c>
       <c r="Q33" s="7" t="n">
-        <v>671520.3100000001</v>
+        <v>12155577.59</v>
       </c>
       <c r="R33" s="7" t="n">
         <v>0</v>
@@ -9962,19 +9962,19 @@
         <v>0</v>
       </c>
       <c r="AS33" s="7" t="n">
-        <v>1179761.28</v>
+        <v>0</v>
       </c>
       <c r="AT33" s="7" t="n">
-        <v>2326341.53</v>
+        <v>0</v>
       </c>
       <c r="AU33" s="7" t="n">
-        <v>1470005.02</v>
+        <v>0</v>
       </c>
       <c r="AV33" s="7" t="n">
-        <v>558932.58</v>
+        <v>0</v>
       </c>
       <c r="AW33" s="7" t="n">
-        <v>137039.92</v>
+        <v>0</v>
       </c>
       <c r="AX33" s="7" t="n">
         <v>0</v>
@@ -9989,46 +9989,46 @@
         <v>0</v>
       </c>
       <c r="BB33" s="7" t="n">
-        <v>0</v>
+        <v>232321.18</v>
       </c>
       <c r="BC33" s="7" t="n">
-        <v>0</v>
+        <v>239771.55</v>
       </c>
       <c r="BD33" s="7" t="n">
-        <v>0</v>
+        <v>346035.44</v>
       </c>
       <c r="BE33" s="7" t="n">
-        <v>531243.2</v>
+        <v>226819.14</v>
       </c>
       <c r="BF33" s="7" t="n">
-        <v>111606.91</v>
+        <v>1450319</v>
       </c>
       <c r="BG33" s="7" t="n">
-        <v>322341.36</v>
+        <v>1463559.22</v>
       </c>
       <c r="BH33" s="7" t="n">
-        <v>416849.42</v>
+        <v>1790742.29</v>
       </c>
       <c r="BI33" s="7" t="n">
-        <v>751552.98</v>
+        <v>1884899.62</v>
       </c>
       <c r="BJ33" s="7" t="n">
-        <v>805000</v>
+        <v>1446453.72</v>
       </c>
       <c r="BK33" s="7" t="n">
-        <v>630821.08</v>
+        <v>1093250.95</v>
       </c>
       <c r="BL33" s="7" t="n">
-        <v>450000</v>
+        <v>920705.1899999999</v>
       </c>
       <c r="BM33" s="7" t="n">
         <v>0</v>
       </c>
       <c r="BN33" s="7" t="n">
-        <v>689574.01</v>
+        <v>186904.1</v>
       </c>
       <c r="BO33" s="7" t="n">
-        <v>499375.75</v>
+        <v>1214701.27</v>
       </c>
       <c r="BP33" s="7" t="n">
         <v>0</v>
@@ -10052,19 +10052,19 @@
         <v>0</v>
       </c>
       <c r="BW33" s="7" t="n">
-        <v>0</v>
+        <v>1403044.06</v>
       </c>
       <c r="BX33" s="7" t="n">
-        <v>3480807.35</v>
+        <v>320057.75</v>
       </c>
       <c r="BY33" s="7" t="n">
-        <v>1527833.15</v>
+        <v>129126.61</v>
       </c>
       <c r="BZ33" s="7" t="n">
-        <v>537831.15</v>
+        <v>0</v>
       </c>
       <c r="CA33" s="7" t="n">
-        <v>3007591.53</v>
+        <v>0</v>
       </c>
       <c r="CB33" s="7" t="n">
         <v>0</v>
@@ -10103,7 +10103,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>330018/001062/2022</t>
+          <t>330018/000675/2022</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -10112,16 +10112,16 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1235</v>
+        <v>1103</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>44909</v>
+        <v>44991</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>46144</v>
+        <v>46094</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>7795660.46</v>
+        <v>20106028.53</v>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
@@ -10130,38 +10130,38 @@
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>JAQUELINE PASTÓRIO</t>
-        </is>
-      </c>
-      <c r="J34" s="8" t="inlineStr">
-        <is>
-          <t>SL</t>
+          <t>GISELLE G. FONSECA</t>
+        </is>
+      </c>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>BX</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>Barra Mansa</t>
+          <t>Nova Iguaçu</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>STATLED BRASIL</t>
+          <t>STATLED</t>
         </is>
       </c>
       <c r="M34" s="7" t="n">
-        <v>959686.41</v>
+        <v>6197590.26</v>
       </c>
       <c r="N34" s="7" t="n">
-        <v>0</v>
+        <v>3545422.68</v>
       </c>
       <c r="O34" s="7" t="n">
-        <v>7795660.46</v>
+        <v>20106028.53</v>
       </c>
       <c r="P34" s="9" t="n">
-        <v>0.9712999999999999</v>
+        <v>0.9666</v>
       </c>
       <c r="Q34" s="7" t="n">
-        <v>223708.17</v>
+        <v>671520.3100000001</v>
       </c>
       <c r="R34" s="7" t="n">
         <v>0</v>
@@ -10236,40 +10236,40 @@
         <v>0</v>
       </c>
       <c r="AP34" s="7" t="n">
-        <v>1055071.12</v>
+        <v>0</v>
       </c>
       <c r="AQ34" s="7" t="n">
-        <v>523066.3</v>
+        <v>0</v>
       </c>
       <c r="AR34" s="7" t="n">
-        <v>1069722.61</v>
+        <v>0</v>
       </c>
       <c r="AS34" s="7" t="n">
-        <v>268607.28</v>
+        <v>1179761.28</v>
       </c>
       <c r="AT34" s="7" t="n">
-        <v>245412.43</v>
+        <v>2326341.53</v>
       </c>
       <c r="AU34" s="7" t="n">
-        <v>5922.36</v>
+        <v>1470005.02</v>
       </c>
       <c r="AV34" s="7" t="n">
-        <v>94659.25</v>
+        <v>558932.58</v>
       </c>
       <c r="AW34" s="7" t="n">
-        <v>96942.14999999999</v>
+        <v>137039.92</v>
       </c>
       <c r="AX34" s="7" t="n">
-        <v>66869.32000000001</v>
+        <v>0</v>
       </c>
       <c r="AY34" s="7" t="n">
-        <v>83645.17</v>
+        <v>0</v>
       </c>
       <c r="AZ34" s="7" t="n">
-        <v>170056.31</v>
+        <v>0</v>
       </c>
       <c r="BA34" s="7" t="n">
-        <v>279264</v>
+        <v>0</v>
       </c>
       <c r="BB34" s="7" t="n">
         <v>0</v>
@@ -10281,37 +10281,37 @@
         <v>0</v>
       </c>
       <c r="BE34" s="7" t="n">
-        <v>212345.55</v>
+        <v>531243.2</v>
       </c>
       <c r="BF34" s="7" t="n">
-        <v>698367.6800000001</v>
+        <v>111606.91</v>
       </c>
       <c r="BG34" s="7" t="n">
-        <v>675950.2</v>
+        <v>322341.36</v>
       </c>
       <c r="BH34" s="7" t="n">
-        <v>354120.32</v>
+        <v>416849.42</v>
       </c>
       <c r="BI34" s="7" t="n">
-        <v>81917.5</v>
+        <v>751552.98</v>
       </c>
       <c r="BJ34" s="7" t="n">
-        <v>224576.79</v>
+        <v>805000</v>
       </c>
       <c r="BK34" s="7" t="n">
-        <v>175625.09</v>
+        <v>630821.08</v>
       </c>
       <c r="BL34" s="7" t="n">
-        <v>230124.44</v>
+        <v>450000</v>
       </c>
       <c r="BM34" s="7" t="n">
         <v>0</v>
       </c>
       <c r="BN34" s="7" t="n">
-        <v>241579.32</v>
+        <v>689574.01</v>
       </c>
       <c r="BO34" s="7" t="n">
-        <v>60530.37</v>
+        <v>499375.75</v>
       </c>
       <c r="BP34" s="7" t="n">
         <v>0</v>
@@ -10338,16 +10338,16 @@
         <v>0</v>
       </c>
       <c r="BX34" s="7" t="n">
-        <v>0</v>
+        <v>3480807.35</v>
       </c>
       <c r="BY34" s="7" t="n">
-        <v>657576.72</v>
+        <v>1527833.15</v>
       </c>
       <c r="BZ34" s="7" t="n">
-        <v>0</v>
+        <v>537831.15</v>
       </c>
       <c r="CA34" s="7" t="n">
-        <v>0</v>
+        <v>3007591.53</v>
       </c>
       <c r="CB34" s="7" t="n">
         <v>0</v>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>170026/001548/2021</t>
+          <t>330018/001062/2022</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -10395,16 +10395,16 @@
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>900</v>
+        <v>1235</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>45901</v>
+        <v>44909</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>46801</v>
+        <v>46144</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>41522873.42</v>
+        <v>7795660.46</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
@@ -10413,38 +10413,38 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>CARLOS FERNANDES</t>
-        </is>
-      </c>
-      <c r="J35" s="11" t="inlineStr">
-        <is>
-          <t>BX</t>
+          <t>JAQUELINE PASTÓRIO</t>
+        </is>
+      </c>
+      <c r="J35" s="8" t="inlineStr">
+        <is>
+          <t>SL</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>São João de Meriti</t>
+          <t>Barra Mansa</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>SÃO JOÃO</t>
+          <t>STATLED BRASIL</t>
         </is>
       </c>
       <c r="M35" s="7" t="n">
-        <v>0</v>
+        <v>959686.41</v>
       </c>
       <c r="N35" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O35" s="7" t="n">
-        <v>0</v>
+        <v>7795660.46</v>
       </c>
       <c r="P35" s="9" t="n">
-        <v>0</v>
+        <v>0.9712999999999999</v>
       </c>
       <c r="Q35" s="7" t="n">
-        <v>41522873.42</v>
+        <v>223708.17</v>
       </c>
       <c r="R35" s="7" t="n">
         <v>0</v>
@@ -10519,40 +10519,40 @@
         <v>0</v>
       </c>
       <c r="AP35" s="7" t="n">
-        <v>0</v>
+        <v>1055071.12</v>
       </c>
       <c r="AQ35" s="7" t="n">
-        <v>0</v>
+        <v>523066.3</v>
       </c>
       <c r="AR35" s="7" t="n">
-        <v>0</v>
+        <v>1069722.61</v>
       </c>
       <c r="AS35" s="7" t="n">
-        <v>0</v>
+        <v>268607.28</v>
       </c>
       <c r="AT35" s="7" t="n">
-        <v>0</v>
+        <v>245412.43</v>
       </c>
       <c r="AU35" s="7" t="n">
-        <v>0</v>
+        <v>5922.36</v>
       </c>
       <c r="AV35" s="7" t="n">
-        <v>0</v>
+        <v>94659.25</v>
       </c>
       <c r="AW35" s="7" t="n">
-        <v>0</v>
+        <v>96942.14999999999</v>
       </c>
       <c r="AX35" s="7" t="n">
-        <v>0</v>
+        <v>66869.32000000001</v>
       </c>
       <c r="AY35" s="7" t="n">
-        <v>0</v>
+        <v>83645.17</v>
       </c>
       <c r="AZ35" s="7" t="n">
-        <v>0</v>
+        <v>170056.31</v>
       </c>
       <c r="BA35" s="7" t="n">
-        <v>0</v>
+        <v>279264</v>
       </c>
       <c r="BB35" s="7" t="n">
         <v>0</v>
@@ -10564,37 +10564,37 @@
         <v>0</v>
       </c>
       <c r="BE35" s="7" t="n">
-        <v>0</v>
+        <v>212345.55</v>
       </c>
       <c r="BF35" s="7" t="n">
-        <v>0</v>
+        <v>698367.6800000001</v>
       </c>
       <c r="BG35" s="7" t="n">
-        <v>0</v>
+        <v>675950.2</v>
       </c>
       <c r="BH35" s="7" t="n">
-        <v>0</v>
+        <v>354120.32</v>
       </c>
       <c r="BI35" s="7" t="n">
-        <v>0</v>
+        <v>81917.5</v>
       </c>
       <c r="BJ35" s="7" t="n">
-        <v>0</v>
+        <v>224576.79</v>
       </c>
       <c r="BK35" s="7" t="n">
-        <v>0</v>
+        <v>175625.09</v>
       </c>
       <c r="BL35" s="7" t="n">
-        <v>0</v>
+        <v>230124.44</v>
       </c>
       <c r="BM35" s="7" t="n">
         <v>0</v>
       </c>
       <c r="BN35" s="7" t="n">
-        <v>0</v>
+        <v>241579.32</v>
       </c>
       <c r="BO35" s="7" t="n">
-        <v>0</v>
+        <v>60530.37</v>
       </c>
       <c r="BP35" s="7" t="n">
         <v>0</v>
@@ -10624,7 +10624,7 @@
         <v>0</v>
       </c>
       <c r="BY35" s="7" t="n">
-        <v>0</v>
+        <v>657576.72</v>
       </c>
       <c r="BZ35" s="7" t="n">
         <v>0</v>
@@ -10669,7 +10669,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>330001/000434/2026</t>
+          <t>170026/001548/2021</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -10677,31 +10677,41 @@
           <t>CIVIS</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr"/>
-      <c r="E36" s="4" t="inlineStr"/>
-      <c r="F36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="n">
+        <v>900</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>45901</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>46801</v>
+      </c>
       <c r="G36" s="7" t="n">
-        <v>31744937.05</v>
+        <v>41522873.42</v>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>ATA DE REGISTRO</t>
-        </is>
-      </c>
-      <c r="I36" s="4" t="inlineStr"/>
-      <c r="J36" s="12" t="inlineStr">
-        <is>
-          <t>MT</t>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>CARLOS FERNANDES</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>BX</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>São João de Meriti</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SÃO JOÃO</t>
         </is>
       </c>
       <c r="M36" s="7" t="n">
@@ -10717,7 +10727,7 @@
         <v>0</v>
       </c>
       <c r="Q36" s="7" t="n">
-        <v>31744937.05</v>
+        <v>41522873.42</v>
       </c>
       <c r="R36" s="7" t="n">
         <v>0</v>
@@ -10942,65 +10952,55 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>330018/000421/2023</t>
-        </is>
-      </c>
-      <c r="C37" s="13" t="inlineStr">
-        <is>
-          <t>CONTINGENCIA</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>374</v>
-      </c>
-      <c r="E37" s="6" t="n">
-        <v>45848</v>
-      </c>
-      <c r="F37" s="6" t="n">
-        <v>46222</v>
-      </c>
+          <t>330001/000434/2026</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>CIVIS</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="7" t="n">
-        <v>8684179.359999999</v>
+        <v>31744937.05</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>GISELLE G. FONSECA</t>
-        </is>
-      </c>
-      <c r="J37" s="10" t="inlineStr">
-        <is>
-          <t>NT</t>
+          <t>ATA DE REGISTRO</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr"/>
+      <c r="J37" s="12" t="inlineStr">
+        <is>
+          <t>MT</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>Petrópolis</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>ECONORTE</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="M37" s="7" t="n">
-        <v>4381697.88</v>
+        <v>0</v>
       </c>
       <c r="N37" s="7" t="n">
-        <v>1948573.31</v>
+        <v>0</v>
       </c>
       <c r="O37" s="7" t="n">
-        <v>8684179.359999999</v>
+        <v>0</v>
       </c>
       <c r="P37" s="9" t="n">
-        <v>0.7289</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="7" t="n">
-        <v>2353908.17</v>
+        <v>31744937.05</v>
       </c>
       <c r="R37" s="7" t="n">
         <v>0</v>
@@ -11171,22 +11171,22 @@
         <v>0</v>
       </c>
       <c r="BV37" s="7" t="n">
-        <v>78757.57000000001</v>
+        <v>0</v>
       </c>
       <c r="BW37" s="7" t="n">
-        <v>70767.05</v>
+        <v>0</v>
       </c>
       <c r="BX37" s="7" t="n">
-        <v>24903.47</v>
+        <v>0</v>
       </c>
       <c r="BY37" s="7" t="n">
-        <v>4207269.79</v>
+        <v>0</v>
       </c>
       <c r="BZ37" s="7" t="n">
-        <v>1285251.84</v>
+        <v>0</v>
       </c>
       <c r="CA37" s="7" t="n">
-        <v>663321.47</v>
+        <v>0</v>
       </c>
       <c r="CB37" s="7" t="n">
         <v>0</v>
@@ -11225,7 +11225,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>330001/001275/2024</t>
+          <t>330018/000421/2023</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
@@ -11234,16 +11234,16 @@
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>45867</v>
+        <v>45848</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>46227</v>
+        <v>46222</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>10349390.52</v>
+        <v>8684179.359999999</v>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
@@ -11255,35 +11255,35 @@
           <t>GISELLE G. FONSECA</t>
         </is>
       </c>
-      <c r="J38" s="11" t="inlineStr">
-        <is>
-          <t>BX</t>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>NT</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>Nilópolis</t>
+          <t>Petrópolis</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>MARENGE</t>
+          <t>ECONORTE</t>
         </is>
       </c>
       <c r="M38" s="7" t="n">
-        <v>2420969.38</v>
+        <v>4381697.88</v>
       </c>
       <c r="N38" s="7" t="n">
-        <v>3055826.41</v>
+        <v>1948573.31</v>
       </c>
       <c r="O38" s="7" t="n">
-        <v>10349390.52</v>
+        <v>8684179.359999999</v>
       </c>
       <c r="P38" s="9" t="n">
-        <v>0.5292</v>
+        <v>0.7289</v>
       </c>
       <c r="Q38" s="7" t="n">
-        <v>4872594.73</v>
+        <v>2353908.17</v>
       </c>
       <c r="R38" s="7" t="n">
         <v>0</v>
@@ -11454,22 +11454,22 @@
         <v>0</v>
       </c>
       <c r="BV38" s="7" t="n">
-        <v>0</v>
+        <v>78757.57000000001</v>
       </c>
       <c r="BW38" s="7" t="n">
-        <v>84288.92</v>
+        <v>70767.05</v>
       </c>
       <c r="BX38" s="7" t="n">
-        <v>272777.33</v>
+        <v>24903.47</v>
       </c>
       <c r="BY38" s="7" t="n">
-        <v>2063903.13</v>
+        <v>4207269.79</v>
       </c>
       <c r="BZ38" s="7" t="n">
-        <v>3055826.41</v>
+        <v>1285251.84</v>
       </c>
       <c r="CA38" s="7" t="n">
-        <v>0</v>
+        <v>663321.47</v>
       </c>
       <c r="CB38" s="7" t="n">
         <v>0</v>
@@ -11508,7 +11508,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>330001/001337/2025</t>
+          <t>330001/001275/2024</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
@@ -11517,16 +11517,16 @@
         </is>
       </c>
       <c r="D39" s="4" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>46002</v>
+        <v>45867</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>46242</v>
+        <v>46227</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>27434724</v>
+        <v>10349390.52</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
@@ -11538,35 +11538,35 @@
           <t>GISELLE G. FONSECA</t>
         </is>
       </c>
-      <c r="J39" s="10" t="inlineStr">
-        <is>
-          <t>NT</t>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>BX</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>Petrópolis</t>
+          <t>Nilópolis</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>QUITANDINHA - DRV</t>
+          <t>MARENGE</t>
         </is>
       </c>
       <c r="M39" s="7" t="n">
-        <v>13791452.86</v>
+        <v>2420969.38</v>
       </c>
       <c r="N39" s="7" t="n">
-        <v>7978998.2</v>
+        <v>3055826.41</v>
       </c>
       <c r="O39" s="7" t="n">
-        <v>27434724</v>
+        <v>10349390.52</v>
       </c>
       <c r="P39" s="9" t="n">
-        <v>0.7935</v>
+        <v>0.5292</v>
       </c>
       <c r="Q39" s="7" t="n">
-        <v>5664272.94</v>
+        <v>4872594.73</v>
       </c>
       <c r="R39" s="7" t="n">
         <v>0</v>
@@ -11740,19 +11740,19 @@
         <v>0</v>
       </c>
       <c r="BW39" s="7" t="n">
-        <v>0</v>
+        <v>84288.92</v>
       </c>
       <c r="BX39" s="7" t="n">
-        <v>0</v>
+        <v>272777.33</v>
       </c>
       <c r="BY39" s="7" t="n">
-        <v>13791452.86</v>
+        <v>2063903.13</v>
       </c>
       <c r="BZ39" s="7" t="n">
-        <v>7440875.08</v>
+        <v>3055826.41</v>
       </c>
       <c r="CA39" s="7" t="n">
-        <v>538123.12</v>
+        <v>0</v>
       </c>
       <c r="CB39" s="7" t="n">
         <v>0</v>
@@ -11791,7 +11791,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>330001/001280/2024</t>
+          <t>330001/001337/2025</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr">
@@ -11800,16 +11800,16 @@
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>332</v>
+        <v>240</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>45783</v>
+        <v>46002</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>46115</v>
+        <v>46242</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>763285.0699999999</v>
+        <v>27434724</v>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
@@ -11821,35 +11821,35 @@
           <t>GISELLE G. FONSECA</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr">
-        <is>
-          <t>BX</t>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>NT</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>Nilópolis</t>
+          <t>Petrópolis</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>SOLOTESTE</t>
+          <t>QUITANDINHA - DRV</t>
         </is>
       </c>
       <c r="M40" s="7" t="n">
-        <v>548089.3100000001</v>
+        <v>13791452.86</v>
       </c>
       <c r="N40" s="7" t="n">
-        <v>137056.25</v>
+        <v>7978998.2</v>
       </c>
       <c r="O40" s="7" t="n">
-        <v>763285.0699999999</v>
+        <v>27434724</v>
       </c>
       <c r="P40" s="9" t="n">
-        <v>0.8976000000000001</v>
+        <v>0.7935</v>
       </c>
       <c r="Q40" s="7" t="n">
-        <v>78139.50999999999</v>
+        <v>5664272.94</v>
       </c>
       <c r="R40" s="7" t="n">
         <v>0</v>
@@ -12008,7 +12008,7 @@
         <v>0</v>
       </c>
       <c r="BR40" s="7" t="n">
-        <v>21939.6</v>
+        <v>0</v>
       </c>
       <c r="BS40" s="7" t="n">
         <v>0</v>
@@ -12023,19 +12023,19 @@
         <v>0</v>
       </c>
       <c r="BW40" s="7" t="n">
-        <v>115052.84</v>
+        <v>0</v>
       </c>
       <c r="BX40" s="7" t="n">
-        <v>233489.27</v>
+        <v>0</v>
       </c>
       <c r="BY40" s="7" t="n">
-        <v>177607.6</v>
+        <v>13791452.86</v>
       </c>
       <c r="BZ40" s="7" t="n">
-        <v>137056.25</v>
+        <v>7440875.08</v>
       </c>
       <c r="CA40" s="7" t="n">
-        <v>0</v>
+        <v>538123.12</v>
       </c>
       <c r="CB40" s="7" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>330001/001081/2025</t>
+          <t>330001/001280/2024</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
@@ -12083,16 +12083,16 @@
         </is>
       </c>
       <c r="D41" s="4" t="n">
-        <v>90</v>
+        <v>332</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>45915</v>
+        <v>45783</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>46005</v>
+        <v>46115</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>256613.37</v>
+        <v>763285.0699999999</v>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
@@ -12101,38 +12101,38 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>CARLOS FERNANDES</t>
-        </is>
-      </c>
-      <c r="J41" s="12" t="inlineStr">
-        <is>
-          <t>MT</t>
+          <t>GISELLE G. FONSECA</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="inlineStr">
+        <is>
+          <t>BX</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>Nilópolis</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>SOLVE CONSULT.</t>
+          <t>SOLOTESTE</t>
         </is>
       </c>
       <c r="M41" s="7" t="n">
-        <v>164482.69</v>
+        <v>548089.3100000001</v>
       </c>
       <c r="N41" s="7" t="n">
-        <v>0</v>
+        <v>137056.25</v>
       </c>
       <c r="O41" s="7" t="n">
-        <v>256613.37</v>
+        <v>763285.0699999999</v>
       </c>
       <c r="P41" s="9" t="n">
-        <v>0.6409999999999999</v>
+        <v>0.8976000000000001</v>
       </c>
       <c r="Q41" s="7" t="n">
-        <v>92130.67999999999</v>
+        <v>78139.50999999999</v>
       </c>
       <c r="R41" s="7" t="n">
         <v>0</v>
@@ -12291,7 +12291,7 @@
         <v>0</v>
       </c>
       <c r="BR41" s="7" t="n">
-        <v>0</v>
+        <v>21939.6</v>
       </c>
       <c r="BS41" s="7" t="n">
         <v>0</v>
@@ -12303,19 +12303,19 @@
         <v>0</v>
       </c>
       <c r="BV41" s="7" t="n">
-        <v>32426.76</v>
+        <v>0</v>
       </c>
       <c r="BW41" s="7" t="n">
-        <v>52055.93</v>
+        <v>115052.84</v>
       </c>
       <c r="BX41" s="7" t="n">
-        <v>80000</v>
+        <v>233489.27</v>
       </c>
       <c r="BY41" s="7" t="n">
-        <v>0</v>
+        <v>177607.6</v>
       </c>
       <c r="BZ41" s="7" t="n">
-        <v>0</v>
+        <v>137056.25</v>
       </c>
       <c r="CA41" s="7" t="n">
         <v>0</v>
@@ -12357,7 +12357,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>E-17/001/219/2018</t>
+          <t>330001/001081/2025</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
@@ -12366,16 +12366,16 @@
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>45917</v>
+        <v>45915</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>46097</v>
+        <v>46005</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>2742607.66</v>
+        <v>256613.37</v>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
@@ -12384,38 +12384,38 @@
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>JEHNIFFER PIRES</t>
-        </is>
-      </c>
-      <c r="J42" s="10" t="inlineStr">
-        <is>
-          <t>NT</t>
+          <t>CARLOS FERNANDES</t>
+        </is>
+      </c>
+      <c r="J42" s="12" t="inlineStr">
+        <is>
+          <t>MT</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>Bom Jardim</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>SOPE ENG.</t>
+          <t>SOLVE CONSULT.</t>
         </is>
       </c>
       <c r="M42" s="7" t="n">
-        <v>0</v>
+        <v>164482.69</v>
       </c>
       <c r="N42" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O42" s="7" t="n">
-        <v>0</v>
+        <v>256613.37</v>
       </c>
       <c r="P42" s="9" t="n">
-        <v>0</v>
+        <v>0.6409999999999999</v>
       </c>
       <c r="Q42" s="7" t="n">
-        <v>2742607.66</v>
+        <v>92130.67999999999</v>
       </c>
       <c r="R42" s="7" t="n">
         <v>0</v>
@@ -12586,13 +12586,13 @@
         <v>0</v>
       </c>
       <c r="BV42" s="7" t="n">
-        <v>0</v>
+        <v>32426.76</v>
       </c>
       <c r="BW42" s="7" t="n">
-        <v>0</v>
+        <v>52055.93</v>
       </c>
       <c r="BX42" s="7" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="BY42" s="7" t="n">
         <v>0</v>
@@ -12640,25 +12640,25 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>170026/000277/2021</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="inlineStr">
-        <is>
-          <t>ESPECIAIS</t>
+          <t>E-17/001/219/2018</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>CONTINGENCIA</t>
         </is>
       </c>
       <c r="D43" s="4" t="n">
-        <v>1530</v>
+        <v>180</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>44757</v>
+        <v>45917</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>46287</v>
+        <v>46097</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>15203482.79</v>
+        <v>2742607.66</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
@@ -12667,38 +12667,38 @@
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>IGOR CARNEIRO</t>
-        </is>
-      </c>
-      <c r="J43" s="12" t="inlineStr">
-        <is>
-          <t>MT</t>
+          <t>JEHNIFFER PIRES</t>
+        </is>
+      </c>
+      <c r="J43" s="10" t="inlineStr">
+        <is>
+          <t>NT</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>Bom Jardim</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>CARLETTI</t>
+          <t>SOPE ENG.</t>
         </is>
       </c>
       <c r="M43" s="7" t="n">
-        <v>1367123.81</v>
+        <v>0</v>
       </c>
       <c r="N43" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O43" s="7" t="n">
-        <v>15203482.79</v>
+        <v>0</v>
       </c>
       <c r="P43" s="9" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="7" t="n">
-        <v>12923552.74</v>
+        <v>2742607.66</v>
       </c>
       <c r="R43" s="7" t="n">
         <v>0</v>
@@ -12758,13 +12758,13 @@
         <v>0</v>
       </c>
       <c r="AK43" s="7" t="n">
-        <v>251065.52</v>
+        <v>0</v>
       </c>
       <c r="AL43" s="7" t="n">
-        <v>228927.31</v>
+        <v>0</v>
       </c>
       <c r="AM43" s="7" t="n">
-        <v>169053.95</v>
+        <v>0</v>
       </c>
       <c r="AN43" s="7" t="n">
         <v>0</v>
@@ -12830,25 +12830,25 @@
         <v>0</v>
       </c>
       <c r="BI43" s="7" t="n">
-        <v>64140.14</v>
+        <v>0</v>
       </c>
       <c r="BJ43" s="7" t="n">
-        <v>30865</v>
+        <v>0</v>
       </c>
       <c r="BK43" s="7" t="n">
-        <v>53092.18</v>
+        <v>0</v>
       </c>
       <c r="BL43" s="7" t="n">
-        <v>115662.14</v>
+        <v>0</v>
       </c>
       <c r="BM43" s="7" t="n">
-        <v>21338.67</v>
+        <v>0</v>
       </c>
       <c r="BN43" s="7" t="n">
-        <v>35589.32</v>
+        <v>0</v>
       </c>
       <c r="BO43" s="7" t="n">
-        <v>98343.64</v>
+        <v>0</v>
       </c>
       <c r="BP43" s="7" t="n">
         <v>0</v>
@@ -12875,7 +12875,7 @@
         <v>0</v>
       </c>
       <c r="BX43" s="7" t="n">
-        <v>1233190.85</v>
+        <v>0</v>
       </c>
       <c r="BY43" s="7" t="n">
         <v>0</v>
@@ -12923,7 +12923,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>180007/000770/2022</t>
+          <t>170026/000277/2021</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
@@ -12932,16 +12932,16 @@
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>480</v>
+        <v>1530</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>45723</v>
+        <v>44757</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>46203</v>
+        <v>46287</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>24187461.93</v>
+        <v>15203482.79</v>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
@@ -12965,23 +12965,23 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>CONSTRUPOWER</t>
+          <t>CARLETTI</t>
         </is>
       </c>
       <c r="M44" s="7" t="n">
-        <v>11147804.81</v>
+        <v>1367123.81</v>
       </c>
       <c r="N44" s="7" t="n">
-        <v>3599595.33</v>
+        <v>0</v>
       </c>
       <c r="O44" s="7" t="n">
-        <v>24187461.93</v>
+        <v>15203482.79</v>
       </c>
       <c r="P44" s="9" t="n">
-        <v>0.6097</v>
+        <v>0.15</v>
       </c>
       <c r="Q44" s="7" t="n">
-        <v>9440061.779999999</v>
+        <v>12923552.74</v>
       </c>
       <c r="R44" s="7" t="n">
         <v>0</v>
@@ -13041,13 +13041,13 @@
         <v>0</v>
       </c>
       <c r="AK44" s="7" t="n">
-        <v>0</v>
+        <v>251065.52</v>
       </c>
       <c r="AL44" s="7" t="n">
-        <v>0</v>
+        <v>228927.31</v>
       </c>
       <c r="AM44" s="7" t="n">
-        <v>0</v>
+        <v>169053.95</v>
       </c>
       <c r="AN44" s="7" t="n">
         <v>0</v>
@@ -13113,61 +13113,61 @@
         <v>0</v>
       </c>
       <c r="BI44" s="7" t="n">
-        <v>0</v>
+        <v>64140.14</v>
       </c>
       <c r="BJ44" s="7" t="n">
-        <v>0</v>
+        <v>30865</v>
       </c>
       <c r="BK44" s="7" t="n">
-        <v>0</v>
+        <v>53092.18</v>
       </c>
       <c r="BL44" s="7" t="n">
-        <v>0</v>
+        <v>115662.14</v>
       </c>
       <c r="BM44" s="7" t="n">
-        <v>0</v>
+        <v>21338.67</v>
       </c>
       <c r="BN44" s="7" t="n">
-        <v>0</v>
+        <v>35589.32</v>
       </c>
       <c r="BO44" s="7" t="n">
-        <v>0</v>
+        <v>98343.64</v>
       </c>
       <c r="BP44" s="7" t="n">
-        <v>9209.35</v>
+        <v>0</v>
       </c>
       <c r="BQ44" s="7" t="n">
-        <v>93817.28</v>
+        <v>0</v>
       </c>
       <c r="BR44" s="7" t="n">
-        <v>302267.46</v>
+        <v>0</v>
       </c>
       <c r="BS44" s="7" t="n">
-        <v>1205629.77</v>
+        <v>0</v>
       </c>
       <c r="BT44" s="7" t="n">
-        <v>1125037.28</v>
+        <v>0</v>
       </c>
       <c r="BU44" s="7" t="n">
-        <v>2271367.75</v>
+        <v>0</v>
       </c>
       <c r="BV44" s="7" t="n">
-        <v>1358528.8</v>
+        <v>0</v>
       </c>
       <c r="BW44" s="7" t="n">
-        <v>1141457.9</v>
+        <v>0</v>
       </c>
       <c r="BX44" s="7" t="n">
-        <v>1199347.44</v>
+        <v>1233190.85</v>
       </c>
       <c r="BY44" s="7" t="n">
-        <v>2441141.78</v>
+        <v>0</v>
       </c>
       <c r="BZ44" s="7" t="n">
-        <v>1980228.97</v>
+        <v>0</v>
       </c>
       <c r="CA44" s="7" t="n">
-        <v>1619366.36</v>
+        <v>0</v>
       </c>
       <c r="CB44" s="7" t="n">
         <v>0</v>
@@ -13206,7 +13206,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>330001/000247/2025</t>
+          <t>180007/000770/2022</t>
         </is>
       </c>
       <c r="C45" s="14" t="inlineStr">
@@ -13215,16 +13215,16 @@
         </is>
       </c>
       <c r="D45" s="4" t="n">
-        <v>218</v>
+        <v>480</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>45894</v>
+        <v>45723</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>12432476.25</v>
+        <v>24187461.93</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>ERICK HYLARIO</t>
+          <t>IGOR CARNEIRO</t>
         </is>
       </c>
       <c r="J45" s="12" t="inlineStr">
@@ -13248,23 +13248,23 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>FAB MIX</t>
+          <t>CONSTRUPOWER</t>
         </is>
       </c>
       <c r="M45" s="7" t="n">
-        <v>10511270.47</v>
+        <v>11147804.81</v>
       </c>
       <c r="N45" s="7" t="n">
-        <v>206846.35</v>
+        <v>3599595.33</v>
       </c>
       <c r="O45" s="7" t="n">
-        <v>12432476.25</v>
+        <v>24187461.93</v>
       </c>
       <c r="P45" s="9" t="n">
-        <v>0.8621</v>
+        <v>0.6097</v>
       </c>
       <c r="Q45" s="7" t="n">
-        <v>1714359.43</v>
+        <v>9440061.779999999</v>
       </c>
       <c r="R45" s="7" t="n">
         <v>0</v>
@@ -13417,40 +13417,40 @@
         <v>0</v>
       </c>
       <c r="BP45" s="7" t="n">
-        <v>0</v>
+        <v>9209.35</v>
       </c>
       <c r="BQ45" s="7" t="n">
-        <v>0</v>
+        <v>93817.28</v>
       </c>
       <c r="BR45" s="7" t="n">
-        <v>0</v>
+        <v>302267.46</v>
       </c>
       <c r="BS45" s="7" t="n">
-        <v>0</v>
+        <v>1205629.77</v>
       </c>
       <c r="BT45" s="7" t="n">
-        <v>0</v>
+        <v>1125037.28</v>
       </c>
       <c r="BU45" s="7" t="n">
-        <v>0</v>
+        <v>2271367.75</v>
       </c>
       <c r="BV45" s="7" t="n">
-        <v>78962.34</v>
+        <v>1358528.8</v>
       </c>
       <c r="BW45" s="7" t="n">
-        <v>2207726.01</v>
+        <v>1141457.9</v>
       </c>
       <c r="BX45" s="7" t="n">
-        <v>4706493.48</v>
+        <v>1199347.44</v>
       </c>
       <c r="BY45" s="7" t="n">
-        <v>3518088.64</v>
+        <v>2441141.78</v>
       </c>
       <c r="BZ45" s="7" t="n">
-        <v>206846.35</v>
+        <v>1980228.97</v>
       </c>
       <c r="CA45" s="7" t="n">
-        <v>0</v>
+        <v>1619366.36</v>
       </c>
       <c r="CB45" s="7" t="n">
         <v>0</v>
@@ -13489,7 +13489,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>460001/001918/2023</t>
+          <t>330001/000247/2025</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
@@ -13498,16 +13498,16 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>365</v>
+        <v>218</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>45758</v>
+        <v>45894</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>46123</v>
+        <v>46112</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>12100122.6</v>
+        <v>12432476.25</v>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
@@ -13531,23 +13531,23 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>FACHADA MIS</t>
+          <t>FAB MIX</t>
         </is>
       </c>
       <c r="M46" s="7" t="n">
-        <v>10301084.52</v>
+        <v>10511270.47</v>
       </c>
       <c r="N46" s="7" t="n">
-        <v>185726.85</v>
+        <v>206846.35</v>
       </c>
       <c r="O46" s="7" t="n">
-        <v>12100122.6</v>
+        <v>12432476.25</v>
       </c>
       <c r="P46" s="9" t="n">
-        <v>0.8667</v>
+        <v>0.8621</v>
       </c>
       <c r="Q46" s="7" t="n">
-        <v>1613311.23</v>
+        <v>1714359.43</v>
       </c>
       <c r="R46" s="7" t="n">
         <v>0</v>
@@ -13709,28 +13709,28 @@
         <v>0</v>
       </c>
       <c r="BS46" s="7" t="n">
-        <v>106382.54</v>
+        <v>0</v>
       </c>
       <c r="BT46" s="7" t="n">
-        <v>413616.54</v>
+        <v>0</v>
       </c>
       <c r="BU46" s="7" t="n">
-        <v>192392.13</v>
+        <v>0</v>
       </c>
       <c r="BV46" s="7" t="n">
-        <v>165598.01</v>
+        <v>78962.34</v>
       </c>
       <c r="BW46" s="7" t="n">
-        <v>2318891.39</v>
+        <v>2207726.01</v>
       </c>
       <c r="BX46" s="7" t="n">
-        <v>3695146.28</v>
+        <v>4706493.48</v>
       </c>
       <c r="BY46" s="7" t="n">
-        <v>3409057.63</v>
+        <v>3518088.64</v>
       </c>
       <c r="BZ46" s="7" t="n">
-        <v>185726.85</v>
+        <v>206846.35</v>
       </c>
       <c r="CA46" s="7" t="n">
         <v>0</v>
@@ -13772,7 +13772,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>170026/000233/2022</t>
+          <t>460001/001918/2023</t>
         </is>
       </c>
       <c r="C47" s="14" t="inlineStr">
@@ -13781,16 +13781,16 @@
         </is>
       </c>
       <c r="D47" s="4" t="n">
-        <v>1280</v>
+        <v>365</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>44726</v>
+        <v>45758</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>46006</v>
+        <v>46123</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>59148617.81</v>
+        <v>12100122.6</v>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
@@ -13802,35 +13802,35 @@
           <t>ERICK HYLARIO</t>
         </is>
       </c>
-      <c r="J47" s="10" t="inlineStr">
-        <is>
-          <t>NT</t>
+      <c r="J47" s="12" t="inlineStr">
+        <is>
+          <t>MT</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>Nova Friburgo</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>MPE</t>
+          <t>FACHADA MIS</t>
         </is>
       </c>
       <c r="M47" s="7" t="n">
-        <v>9904470.27</v>
+        <v>10301084.52</v>
       </c>
       <c r="N47" s="7" t="n">
-        <v>0</v>
+        <v>185726.85</v>
       </c>
       <c r="O47" s="7" t="n">
-        <v>59148617.81</v>
+        <v>12100122.6</v>
       </c>
       <c r="P47" s="9" t="n">
-        <v>0.948</v>
+        <v>0.8667</v>
       </c>
       <c r="Q47" s="7" t="n">
-        <v>3073439.17</v>
+        <v>1613311.23</v>
       </c>
       <c r="R47" s="7" t="n">
         <v>0</v>
@@ -13884,136 +13884,136 @@
         <v>0</v>
       </c>
       <c r="AI47" s="7" t="n">
-        <v>2586476.21</v>
+        <v>0</v>
       </c>
       <c r="AJ47" s="7" t="n">
-        <v>2130349.36</v>
+        <v>0</v>
       </c>
       <c r="AK47" s="7" t="n">
-        <v>3069158.06</v>
+        <v>0</v>
       </c>
       <c r="AL47" s="7" t="n">
-        <v>3940056.94</v>
+        <v>0</v>
       </c>
       <c r="AM47" s="7" t="n">
-        <v>7368617.47</v>
+        <v>0</v>
       </c>
       <c r="AN47" s="7" t="n">
-        <v>4520360.22</v>
+        <v>0</v>
       </c>
       <c r="AO47" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AP47" s="7" t="n">
-        <v>1699998.95</v>
+        <v>0</v>
       </c>
       <c r="AQ47" s="7" t="n">
-        <v>1991371.45</v>
+        <v>0</v>
       </c>
       <c r="AR47" s="7" t="n">
-        <v>1700389.28</v>
+        <v>0</v>
       </c>
       <c r="AS47" s="7" t="n">
-        <v>1501741.01</v>
+        <v>0</v>
       </c>
       <c r="AT47" s="7" t="n">
-        <v>155555.61</v>
+        <v>0</v>
       </c>
       <c r="AU47" s="7" t="n">
-        <v>82140.75</v>
+        <v>0</v>
       </c>
       <c r="AV47" s="7" t="n">
-        <v>114352.08</v>
+        <v>0</v>
       </c>
       <c r="AW47" s="7" t="n">
-        <v>100040.41</v>
+        <v>0</v>
       </c>
       <c r="AX47" s="7" t="n">
-        <v>166813.86</v>
+        <v>0</v>
       </c>
       <c r="AY47" s="7" t="n">
-        <v>239298.44</v>
+        <v>0</v>
       </c>
       <c r="AZ47" s="7" t="n">
-        <v>223175.17</v>
+        <v>0</v>
       </c>
       <c r="BA47" s="7" t="n">
-        <v>182734.82</v>
+        <v>0</v>
       </c>
       <c r="BB47" s="7" t="n">
-        <v>224993.06</v>
+        <v>0</v>
       </c>
       <c r="BC47" s="7" t="n">
-        <v>108342.85</v>
+        <v>0</v>
       </c>
       <c r="BD47" s="7" t="n">
-        <v>187923.63</v>
+        <v>0</v>
       </c>
       <c r="BE47" s="7" t="n">
-        <v>515128.1</v>
+        <v>0</v>
       </c>
       <c r="BF47" s="7" t="n">
-        <v>142691.86</v>
+        <v>0</v>
       </c>
       <c r="BG47" s="7" t="n">
-        <v>2198591.1</v>
+        <v>0</v>
       </c>
       <c r="BH47" s="7" t="n">
-        <v>2441391.26</v>
+        <v>0</v>
       </c>
       <c r="BI47" s="7" t="n">
-        <v>2533116.01</v>
+        <v>0</v>
       </c>
       <c r="BJ47" s="7" t="n">
-        <v>2055983.33</v>
+        <v>0</v>
       </c>
       <c r="BK47" s="7" t="n">
-        <v>2527771.87</v>
+        <v>0</v>
       </c>
       <c r="BL47" s="7" t="n">
-        <v>1021876.31</v>
+        <v>0</v>
       </c>
       <c r="BM47" s="7" t="n">
-        <v>440269.8</v>
+        <v>0</v>
       </c>
       <c r="BN47" s="7" t="n">
-        <v>1729073.23</v>
+        <v>0</v>
       </c>
       <c r="BO47" s="7" t="n">
-        <v>1040307.02</v>
+        <v>0</v>
       </c>
       <c r="BP47" s="7" t="n">
-        <v>1067421.56</v>
+        <v>0</v>
       </c>
       <c r="BQ47" s="7" t="n">
-        <v>4750815.75</v>
+        <v>0</v>
       </c>
       <c r="BR47" s="7" t="n">
-        <v>102607.96</v>
+        <v>0</v>
       </c>
       <c r="BS47" s="7" t="n">
-        <v>487664.76</v>
+        <v>106382.54</v>
       </c>
       <c r="BT47" s="7" t="n">
-        <v>0</v>
+        <v>413616.54</v>
       </c>
       <c r="BU47" s="7" t="n">
-        <v>0</v>
+        <v>192392.13</v>
       </c>
       <c r="BV47" s="7" t="n">
-        <v>0</v>
+        <v>165598.01</v>
       </c>
       <c r="BW47" s="7" t="n">
-        <v>0</v>
+        <v>2318891.39</v>
       </c>
       <c r="BX47" s="7" t="n">
-        <v>726579.99</v>
+        <v>3695146.28</v>
       </c>
       <c r="BY47" s="7" t="n">
-        <v>0</v>
+        <v>3409057.63</v>
       </c>
       <c r="BZ47" s="7" t="n">
-        <v>0</v>
+        <v>185726.85</v>
       </c>
       <c r="CA47" s="7" t="n">
         <v>0</v>
@@ -14055,7 +14055,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>330001/000414/2024</t>
+          <t>170026/000233/2022</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
@@ -14064,16 +14064,16 @@
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>210</v>
+        <v>1280</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>45897</v>
+        <v>44726</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>46107</v>
+        <v>46006</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>116500000</v>
+        <v>59148617.81</v>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
@@ -14085,14 +14085,14 @@
           <t>ERICK HYLARIO</t>
         </is>
       </c>
-      <c r="J48" s="12" t="inlineStr">
-        <is>
-          <t>MT</t>
+      <c r="J48" s="10" t="inlineStr">
+        <is>
+          <t>NT</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>Nova Friburgo</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
@@ -14101,19 +14101,19 @@
         </is>
       </c>
       <c r="M48" s="7" t="n">
-        <v>22022321.06</v>
+        <v>9904470.27</v>
       </c>
       <c r="N48" s="7" t="n">
-        <v>4823492.73</v>
+        <v>0</v>
       </c>
       <c r="O48" s="7" t="n">
-        <v>116500000</v>
+        <v>59148617.81</v>
       </c>
       <c r="P48" s="9" t="n">
-        <v>0.2304</v>
+        <v>0.948</v>
       </c>
       <c r="Q48" s="7" t="n">
-        <v>89654186.20999999</v>
+        <v>3073439.17</v>
       </c>
       <c r="R48" s="7" t="n">
         <v>0</v>
@@ -14167,115 +14167,115 @@
         <v>0</v>
       </c>
       <c r="AI48" s="7" t="n">
-        <v>0</v>
+        <v>2586476.21</v>
       </c>
       <c r="AJ48" s="7" t="n">
-        <v>0</v>
+        <v>2130349.36</v>
       </c>
       <c r="AK48" s="7" t="n">
-        <v>0</v>
+        <v>3069158.06</v>
       </c>
       <c r="AL48" s="7" t="n">
-        <v>0</v>
+        <v>3940056.94</v>
       </c>
       <c r="AM48" s="7" t="n">
-        <v>0</v>
+        <v>7368617.47</v>
       </c>
       <c r="AN48" s="7" t="n">
-        <v>0</v>
+        <v>4520360.22</v>
       </c>
       <c r="AO48" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AP48" s="7" t="n">
-        <v>0</v>
+        <v>1699998.95</v>
       </c>
       <c r="AQ48" s="7" t="n">
-        <v>0</v>
+        <v>1991371.45</v>
       </c>
       <c r="AR48" s="7" t="n">
-        <v>0</v>
+        <v>1700389.28</v>
       </c>
       <c r="AS48" s="7" t="n">
-        <v>0</v>
+        <v>1501741.01</v>
       </c>
       <c r="AT48" s="7" t="n">
-        <v>0</v>
+        <v>155555.61</v>
       </c>
       <c r="AU48" s="7" t="n">
-        <v>0</v>
+        <v>82140.75</v>
       </c>
       <c r="AV48" s="7" t="n">
-        <v>0</v>
+        <v>114352.08</v>
       </c>
       <c r="AW48" s="7" t="n">
-        <v>0</v>
+        <v>100040.41</v>
       </c>
       <c r="AX48" s="7" t="n">
-        <v>0</v>
+        <v>166813.86</v>
       </c>
       <c r="AY48" s="7" t="n">
-        <v>0</v>
+        <v>239298.44</v>
       </c>
       <c r="AZ48" s="7" t="n">
-        <v>0</v>
+        <v>223175.17</v>
       </c>
       <c r="BA48" s="7" t="n">
-        <v>0</v>
+        <v>182734.82</v>
       </c>
       <c r="BB48" s="7" t="n">
-        <v>0</v>
+        <v>224993.06</v>
       </c>
       <c r="BC48" s="7" t="n">
-        <v>0</v>
+        <v>108342.85</v>
       </c>
       <c r="BD48" s="7" t="n">
-        <v>0</v>
+        <v>187923.63</v>
       </c>
       <c r="BE48" s="7" t="n">
-        <v>0</v>
+        <v>515128.1</v>
       </c>
       <c r="BF48" s="7" t="n">
-        <v>0</v>
+        <v>142691.86</v>
       </c>
       <c r="BG48" s="7" t="n">
-        <v>0</v>
+        <v>2198591.1</v>
       </c>
       <c r="BH48" s="7" t="n">
-        <v>0</v>
+        <v>2441391.26</v>
       </c>
       <c r="BI48" s="7" t="n">
-        <v>0</v>
+        <v>2533116.01</v>
       </c>
       <c r="BJ48" s="7" t="n">
-        <v>0</v>
+        <v>2055983.33</v>
       </c>
       <c r="BK48" s="7" t="n">
-        <v>0</v>
+        <v>2527771.87</v>
       </c>
       <c r="BL48" s="7" t="n">
-        <v>0</v>
+        <v>1021876.31</v>
       </c>
       <c r="BM48" s="7" t="n">
-        <v>0</v>
+        <v>440269.8</v>
       </c>
       <c r="BN48" s="7" t="n">
-        <v>0</v>
+        <v>1729073.23</v>
       </c>
       <c r="BO48" s="7" t="n">
-        <v>0</v>
+        <v>1040307.02</v>
       </c>
       <c r="BP48" s="7" t="n">
-        <v>0</v>
+        <v>1067421.56</v>
       </c>
       <c r="BQ48" s="7" t="n">
-        <v>0</v>
+        <v>4750815.75</v>
       </c>
       <c r="BR48" s="7" t="n">
-        <v>0</v>
+        <v>102607.96</v>
       </c>
       <c r="BS48" s="7" t="n">
-        <v>0</v>
+        <v>487664.76</v>
       </c>
       <c r="BT48" s="7" t="n">
         <v>0</v>
@@ -14284,19 +14284,19 @@
         <v>0</v>
       </c>
       <c r="BV48" s="7" t="n">
-        <v>3852905.57</v>
+        <v>0</v>
       </c>
       <c r="BW48" s="7" t="n">
-        <v>7526416.37</v>
+        <v>0</v>
       </c>
       <c r="BX48" s="7" t="n">
-        <v>4336364.05</v>
+        <v>726579.99</v>
       </c>
       <c r="BY48" s="7" t="n">
-        <v>6306635.07</v>
+        <v>0</v>
       </c>
       <c r="BZ48" s="7" t="n">
-        <v>4823492.73</v>
+        <v>0</v>
       </c>
       <c r="CA48" s="7" t="n">
         <v>0</v>
@@ -14338,7 +14338,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>460001/000416/2023</t>
+          <t>330001/000414/2024</t>
         </is>
       </c>
       <c r="C49" s="14" t="inlineStr">
@@ -14347,16 +14347,16 @@
         </is>
       </c>
       <c r="D49" s="4" t="n">
-        <v>666</v>
+        <v>210</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>45391</v>
+        <v>45897</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>46057</v>
+        <v>46107</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>41651255.98</v>
+        <v>116500000</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
@@ -14365,38 +14365,38 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>IGOR CARNEIRO</t>
-        </is>
-      </c>
-      <c r="J49" s="11" t="inlineStr">
-        <is>
-          <t>BX</t>
+          <t>ERICK HYLARIO</t>
+        </is>
+      </c>
+      <c r="J49" s="12" t="inlineStr">
+        <is>
+          <t>MT</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>Duque de Caxias</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>OMEGA</t>
+          <t>MPE</t>
         </is>
       </c>
       <c r="M49" s="7" t="n">
-        <v>12334165.09</v>
+        <v>22022321.06</v>
       </c>
       <c r="N49" s="7" t="n">
-        <v>0</v>
+        <v>4823492.73</v>
       </c>
       <c r="O49" s="7" t="n">
-        <v>41651255.98</v>
+        <v>116500000</v>
       </c>
       <c r="P49" s="9" t="n">
-        <v>0.9301</v>
+        <v>0.2304</v>
       </c>
       <c r="Q49" s="7" t="n">
-        <v>2912586.96</v>
+        <v>89654186.20999999</v>
       </c>
       <c r="R49" s="7" t="n">
         <v>0</v>
@@ -14516,70 +14516,70 @@
         <v>0</v>
       </c>
       <c r="BE49" s="7" t="n">
-        <v>66647</v>
+        <v>0</v>
       </c>
       <c r="BF49" s="7" t="n">
-        <v>7823810.81</v>
+        <v>0</v>
       </c>
       <c r="BG49" s="7" t="n">
-        <v>3945943.45</v>
+        <v>0</v>
       </c>
       <c r="BH49" s="7" t="n">
-        <v>8782118.74</v>
+        <v>0</v>
       </c>
       <c r="BI49" s="7" t="n">
-        <v>4935599.9</v>
+        <v>0</v>
       </c>
       <c r="BJ49" s="7" t="n">
-        <v>362750.13</v>
+        <v>0</v>
       </c>
       <c r="BK49" s="7" t="n">
-        <v>298756.33</v>
+        <v>0</v>
       </c>
       <c r="BL49" s="7" t="n">
-        <v>188877.57</v>
+        <v>0</v>
       </c>
       <c r="BM49" s="7" t="n">
         <v>0</v>
       </c>
       <c r="BN49" s="7" t="n">
-        <v>908147.84</v>
+        <v>0</v>
       </c>
       <c r="BO49" s="7" t="n">
-        <v>4200442.63</v>
+        <v>0</v>
       </c>
       <c r="BP49" s="7" t="n">
-        <v>458086.93</v>
+        <v>0</v>
       </c>
       <c r="BQ49" s="7" t="n">
-        <v>4837971.15</v>
+        <v>0</v>
       </c>
       <c r="BR49" s="7" t="n">
-        <v>179856.91</v>
+        <v>0</v>
       </c>
       <c r="BS49" s="7" t="n">
-        <v>112986.28</v>
+        <v>0</v>
       </c>
       <c r="BT49" s="7" t="n">
-        <v>125094.83</v>
+        <v>0</v>
       </c>
       <c r="BU49" s="7" t="n">
-        <v>152137.68</v>
+        <v>0</v>
       </c>
       <c r="BV49" s="7" t="n">
-        <v>120408.81</v>
+        <v>3852905.57</v>
       </c>
       <c r="BW49" s="7" t="n">
-        <v>130614.89</v>
+        <v>7526416.37</v>
       </c>
       <c r="BX49" s="7" t="n">
-        <v>1108417.14</v>
+        <v>4336364.05</v>
       </c>
       <c r="BY49" s="7" t="n">
-        <v>0</v>
+        <v>6306635.07</v>
       </c>
       <c r="BZ49" s="7" t="n">
-        <v>0</v>
+        <v>4823492.73</v>
       </c>
       <c r="CA49" s="7" t="n">
         <v>0</v>
@@ -14621,7 +14621,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>170026/000214/2022</t>
+          <t>460001/000416/2023</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
@@ -14630,16 +14630,16 @@
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>450</v>
+        <v>666</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>45624</v>
+        <v>45391</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>46074</v>
+        <v>46057</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>104939756.55</v>
+        <v>41651255.98</v>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
@@ -14648,38 +14648,38 @@
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>ERICK HYLARIO</t>
-        </is>
-      </c>
-      <c r="J50" s="12" t="inlineStr">
-        <is>
-          <t>MT</t>
+          <t>IGOR CARNEIRO</t>
+        </is>
+      </c>
+      <c r="J50" s="11" t="inlineStr">
+        <is>
+          <t>BX</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>Duque de Caxias</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>POMA</t>
+          <t>OMEGA</t>
         </is>
       </c>
       <c r="M50" s="7" t="n">
-        <v>54247297.54</v>
+        <v>12334165.09</v>
       </c>
       <c r="N50" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O50" s="7" t="n">
-        <v>104939756.55</v>
+        <v>41651255.98</v>
       </c>
       <c r="P50" s="9" t="n">
-        <v>0.5169</v>
+        <v>0.9301</v>
       </c>
       <c r="Q50" s="7" t="n">
-        <v>50692459.01</v>
+        <v>2912586.96</v>
       </c>
       <c r="R50" s="7" t="n">
         <v>0</v>
@@ -14799,64 +14799,64 @@
         <v>0</v>
       </c>
       <c r="BE50" s="7" t="n">
-        <v>0</v>
+        <v>66647</v>
       </c>
       <c r="BF50" s="7" t="n">
-        <v>0</v>
+        <v>7823810.81</v>
       </c>
       <c r="BG50" s="7" t="n">
-        <v>0</v>
+        <v>3945943.45</v>
       </c>
       <c r="BH50" s="7" t="n">
-        <v>0</v>
+        <v>8782118.74</v>
       </c>
       <c r="BI50" s="7" t="n">
-        <v>0</v>
+        <v>4935599.9</v>
       </c>
       <c r="BJ50" s="7" t="n">
-        <v>0</v>
+        <v>362750.13</v>
       </c>
       <c r="BK50" s="7" t="n">
-        <v>0</v>
+        <v>298756.33</v>
       </c>
       <c r="BL50" s="7" t="n">
-        <v>0</v>
+        <v>188877.57</v>
       </c>
       <c r="BM50" s="7" t="n">
         <v>0</v>
       </c>
       <c r="BN50" s="7" t="n">
-        <v>0</v>
+        <v>908147.84</v>
       </c>
       <c r="BO50" s="7" t="n">
-        <v>4377658.21</v>
+        <v>4200442.63</v>
       </c>
       <c r="BP50" s="7" t="n">
-        <v>0</v>
+        <v>458086.93</v>
       </c>
       <c r="BQ50" s="7" t="n">
-        <v>0</v>
+        <v>4837971.15</v>
       </c>
       <c r="BR50" s="7" t="n">
-        <v>0</v>
+        <v>179856.91</v>
       </c>
       <c r="BS50" s="7" t="n">
-        <v>21982596.03</v>
+        <v>112986.28</v>
       </c>
       <c r="BT50" s="7" t="n">
-        <v>0</v>
+        <v>125094.83</v>
       </c>
       <c r="BU50" s="7" t="n">
-        <v>27887043.3</v>
+        <v>152137.68</v>
       </c>
       <c r="BV50" s="7" t="n">
-        <v>0</v>
+        <v>120408.81</v>
       </c>
       <c r="BW50" s="7" t="n">
-        <v>0</v>
+        <v>130614.89</v>
       </c>
       <c r="BX50" s="7" t="n">
-        <v>0</v>
+        <v>1108417.14</v>
       </c>
       <c r="BY50" s="7" t="n">
         <v>0</v>
@@ -14904,280 +14904,563 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
+          <t>170026/000214/2022</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>ESPECIAIS</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>450</v>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>45624</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>46074</v>
+      </c>
+      <c r="G51" s="7" t="n">
+        <v>104939756.55</v>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>ERICK HYLARIO</t>
+        </is>
+      </c>
+      <c r="J51" s="12" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>POMA</t>
+        </is>
+      </c>
+      <c r="M51" s="7" t="n">
+        <v>54247297.54</v>
+      </c>
+      <c r="N51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="7" t="n">
+        <v>104939756.55</v>
+      </c>
+      <c r="P51" s="9" t="n">
+        <v>0.5169</v>
+      </c>
+      <c r="Q51" s="7" t="n">
+        <v>50692459.01</v>
+      </c>
+      <c r="R51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO51" s="7" t="n">
+        <v>4377658.21</v>
+      </c>
+      <c r="BP51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS51" s="7" t="n">
+        <v>21982596.03</v>
+      </c>
+      <c r="BT51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU51" s="7" t="n">
+        <v>27887043.3</v>
+      </c>
+      <c r="BV51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK51" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
           <t>330001/000097/2024</t>
         </is>
       </c>
-      <c r="C51" s="14" t="inlineStr">
+      <c r="C52" s="14" t="inlineStr">
         <is>
           <t>ESPECIAIS</t>
         </is>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="D52" s="4" t="n">
         <v>557</v>
       </c>
-      <c r="E51" s="6" t="n">
+      <c r="E52" s="6" t="n">
         <v>45555</v>
       </c>
-      <c r="F51" s="6" t="n">
+      <c r="F52" s="6" t="n">
         <v>46112</v>
       </c>
-      <c r="G51" s="7" t="n">
+      <c r="G52" s="7" t="n">
         <v>74609626.42</v>
       </c>
-      <c r="H51" s="4" t="inlineStr">
+      <c r="H52" s="4" t="inlineStr">
         <is>
           <t>EXECUÇÃO</t>
         </is>
       </c>
-      <c r="I51" s="4" t="inlineStr">
+      <c r="I52" s="4" t="inlineStr">
         <is>
           <t>ERICK HYLARIO</t>
         </is>
       </c>
-      <c r="J51" s="12" t="inlineStr">
+      <c r="J52" s="12" t="inlineStr">
         <is>
           <t>MT</t>
         </is>
       </c>
-      <c r="K51" s="4" t="inlineStr">
+      <c r="K52" s="4" t="inlineStr">
         <is>
           <t>Rio de Janeiro</t>
         </is>
       </c>
-      <c r="L51" s="4" t="inlineStr">
+      <c r="L52" s="4" t="inlineStr">
         <is>
           <t>TANGRAN ENGENHARIA</t>
         </is>
       </c>
-      <c r="M51" s="7" t="n">
+      <c r="M52" s="7" t="n">
         <v>55173009.47</v>
       </c>
-      <c r="N51" s="7" t="n">
+      <c r="N52" s="7" t="n">
         <v>1537890.45</v>
       </c>
-      <c r="O51" s="7" t="n">
+      <c r="O52" s="7" t="n">
         <v>74609626.42</v>
       </c>
-      <c r="P51" s="9" t="n">
+      <c r="P52" s="9" t="n">
         <v>0.8504</v>
       </c>
-      <c r="Q51" s="7" t="n">
+      <c r="Q52" s="7" t="n">
         <v>11160584.93</v>
       </c>
-      <c r="R51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK51" s="7" t="n">
+      <c r="R52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK52" s="7" t="n">
         <v>992254.67</v>
       </c>
-      <c r="BL51" s="7" t="n">
+      <c r="BL52" s="7" t="n">
         <v>1415945.29</v>
       </c>
-      <c r="BM51" s="7" t="n">
+      <c r="BM52" s="7" t="n">
         <v>4329941.61</v>
       </c>
-      <c r="BN51" s="7" t="n">
+      <c r="BN52" s="7" t="n">
         <v>1690670</v>
       </c>
-      <c r="BO51" s="7" t="n">
+      <c r="BO52" s="7" t="n">
         <v>380731.29</v>
       </c>
-      <c r="BP51" s="7" t="n">
+      <c r="BP52" s="7" t="n">
         <v>941725.7</v>
       </c>
-      <c r="BQ51" s="7" t="n">
+      <c r="BQ52" s="7" t="n">
         <v>7173927.79</v>
       </c>
-      <c r="BR51" s="7" t="n">
+      <c r="BR52" s="7" t="n">
         <v>4408318.83</v>
       </c>
-      <c r="BS51" s="7" t="n">
+      <c r="BS52" s="7" t="n">
         <v>911822.65</v>
       </c>
-      <c r="BT51" s="7" t="n">
+      <c r="BT52" s="7" t="n">
         <v>797460</v>
       </c>
-      <c r="BU51" s="7" t="n">
+      <c r="BU52" s="7" t="n">
         <v>4046951.13</v>
       </c>
-      <c r="BV51" s="7" t="n">
+      <c r="BV52" s="7" t="n">
         <v>1934090.63</v>
       </c>
-      <c r="BW51" s="7" t="n">
+      <c r="BW52" s="7" t="n">
         <v>4527612.82</v>
       </c>
-      <c r="BX51" s="7" t="n">
+      <c r="BX52" s="7" t="n">
         <v>10087226.35</v>
       </c>
-      <c r="BY51" s="7" t="n">
+      <c r="BY52" s="7" t="n">
         <v>18272472.28</v>
       </c>
-      <c r="BZ51" s="7" t="n">
+      <c r="BZ52" s="7" t="n">
         <v>1537890.45</v>
       </c>
-      <c r="CA51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK51" s="7" t="n">
+      <c r="CA52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK52" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15192,7 +15475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CL121"/>
+  <dimension ref="A1:CL120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -40083,7 +40366,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>330018/001213/2022</t>
+          <t>330018/001077/2021</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
@@ -40092,32 +40375,24 @@
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>664</v>
+        <v>215</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>45398</v>
+        <v>44783</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>46062</v>
+        <v>44998</v>
       </c>
       <c r="G88" s="7" t="n">
-        <v>6765672.29</v>
+        <v>21672861.46</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>CONCLUÍDA</t>
-        </is>
-      </c>
-      <c r="I88" s="4" t="inlineStr">
-        <is>
-          <t>CARLOS FERNANDES</t>
-        </is>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>NICHOLAS TAVARES / OTAVIO FEITOSA</t>
-        </is>
-      </c>
+          <t>NÃO CONCLUÍDA</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr"/>
+      <c r="J88" s="4" t="inlineStr"/>
       <c r="K88" s="11" t="inlineStr">
         <is>
           <t>BX</t>
@@ -40125,7 +40400,7 @@
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>Belford Roxo</t>
+          <t>Duque de Caxias</t>
         </is>
       </c>
       <c r="M88" s="4" t="inlineStr">
@@ -40134,19 +40409,19 @@
         </is>
       </c>
       <c r="N88" s="7" t="n">
-        <v>4600873.35</v>
+        <v>0</v>
       </c>
       <c r="O88" s="7" t="n">
-        <v>615349.64</v>
+        <v>0</v>
       </c>
       <c r="P88" s="7" t="n">
-        <v>6765672.29</v>
+        <v>21672861.46</v>
       </c>
       <c r="Q88" s="9" t="n">
-        <v>0.9754</v>
+        <v>0.0063</v>
       </c>
       <c r="R88" s="7" t="n">
-        <v>166531.04</v>
+        <v>21535386.37</v>
       </c>
       <c r="S88" s="7" t="n">
         <v>0</v>
@@ -40206,7 +40481,7 @@
         <v>0</v>
       </c>
       <c r="AL88" s="7" t="n">
-        <v>0</v>
+        <v>137475.09</v>
       </c>
       <c r="AM88" s="7" t="n">
         <v>0</v>
@@ -40275,16 +40550,16 @@
         <v>0</v>
       </c>
       <c r="BI88" s="7" t="n">
-        <v>219698.04</v>
+        <v>0</v>
       </c>
       <c r="BJ88" s="7" t="n">
-        <v>180625.15</v>
+        <v>0</v>
       </c>
       <c r="BK88" s="7" t="n">
-        <v>470617.93</v>
+        <v>0</v>
       </c>
       <c r="BL88" s="7" t="n">
-        <v>519882.19</v>
+        <v>0</v>
       </c>
       <c r="BM88" s="7" t="n">
         <v>0</v>
@@ -40299,16 +40574,16 @@
         <v>0</v>
       </c>
       <c r="BQ88" s="7" t="n">
-        <v>669692.84</v>
+        <v>0</v>
       </c>
       <c r="BR88" s="7" t="n">
-        <v>1778629.34</v>
+        <v>0</v>
       </c>
       <c r="BS88" s="7" t="n">
-        <v>853473.6</v>
+        <v>0</v>
       </c>
       <c r="BT88" s="7" t="n">
-        <v>791806.64</v>
+        <v>0</v>
       </c>
       <c r="BU88" s="7" t="n">
         <v>0</v>
@@ -40326,10 +40601,10 @@
         <v>0</v>
       </c>
       <c r="BZ88" s="7" t="n">
-        <v>507270.93</v>
+        <v>0</v>
       </c>
       <c r="CA88" s="7" t="n">
-        <v>615349.64</v>
+        <v>0</v>
       </c>
       <c r="CB88" s="7" t="n">
         <v>0</v>
@@ -40371,7 +40646,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>330018/001077/2021</t>
+          <t>330018/000712/2021</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
@@ -40380,20 +40655,20 @@
         </is>
       </c>
       <c r="D89" s="4" t="n">
-        <v>215</v>
+        <v>380</v>
       </c>
       <c r="E89" s="6" t="n">
-        <v>44783</v>
+        <v>44564</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>44998</v>
+        <v>44944</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>21672861.46</v>
+        <v>32836774.76</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>NÃO CONCLUÍDA</t>
+          <t>CONCLUÍDA</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr"/>
@@ -40405,7 +40680,7 @@
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>Duque de Caxias</t>
+          <t>Nilópolis</t>
         </is>
       </c>
       <c r="M89" s="4" t="inlineStr">
@@ -40420,13 +40695,13 @@
         <v>0</v>
       </c>
       <c r="P89" s="7" t="n">
-        <v>21672861.46</v>
+        <v>32836774.76</v>
       </c>
       <c r="Q89" s="9" t="n">
-        <v>0.0063</v>
+        <v>0.9495</v>
       </c>
       <c r="R89" s="7" t="n">
-        <v>21535386.37</v>
+        <v>1658538.55</v>
       </c>
       <c r="S89" s="7" t="n">
         <v>0</v>
@@ -40465,40 +40740,40 @@
         <v>0</v>
       </c>
       <c r="AE89" s="7" t="n">
-        <v>0</v>
+        <v>1252183.89</v>
       </c>
       <c r="AF89" s="7" t="n">
-        <v>0</v>
+        <v>2696269.1</v>
       </c>
       <c r="AG89" s="7" t="n">
-        <v>0</v>
+        <v>4871474.25</v>
       </c>
       <c r="AH89" s="7" t="n">
-        <v>0</v>
+        <v>4497352.58</v>
       </c>
       <c r="AI89" s="7" t="n">
-        <v>0</v>
+        <v>3228080.73</v>
       </c>
       <c r="AJ89" s="7" t="n">
-        <v>0</v>
+        <v>3793877.75</v>
       </c>
       <c r="AK89" s="7" t="n">
-        <v>0</v>
+        <v>2375732.68</v>
       </c>
       <c r="AL89" s="7" t="n">
-        <v>137475.09</v>
+        <v>1212320.58</v>
       </c>
       <c r="AM89" s="7" t="n">
-        <v>0</v>
+        <v>4888556.81</v>
       </c>
       <c r="AN89" s="7" t="n">
-        <v>0</v>
+        <v>1660361.27</v>
       </c>
       <c r="AO89" s="7" t="n">
-        <v>0</v>
+        <v>426548.56</v>
       </c>
       <c r="AP89" s="7" t="n">
-        <v>0</v>
+        <v>275478.01</v>
       </c>
       <c r="AQ89" s="7" t="n">
         <v>0</v>
@@ -40651,7 +40926,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>330018/000712/2021</t>
+          <t>E-17/001/81/2013</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
@@ -40660,37 +40935,37 @@
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>380</v>
+        <v>2569</v>
       </c>
       <c r="E90" s="6" t="n">
-        <v>44564</v>
+        <v>41443</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>44944</v>
+        <v>44012</v>
       </c>
       <c r="G90" s="7" t="n">
-        <v>32836774.76</v>
+        <v>14144248.92</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>CONCLUÍDA</t>
+          <t>NÃO CONCLUÍDA</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr"/>
       <c r="J90" s="4" t="inlineStr"/>
-      <c r="K90" s="11" t="inlineStr">
-        <is>
-          <t>BX</t>
+      <c r="K90" s="12" t="inlineStr">
+        <is>
+          <t>MT</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>Nilópolis</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="M90" s="4" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>SEVEME</t>
         </is>
       </c>
       <c r="N90" s="7" t="n">
@@ -40700,13 +40975,13 @@
         <v>0</v>
       </c>
       <c r="P90" s="7" t="n">
-        <v>32836774.76</v>
+        <v>0</v>
       </c>
       <c r="Q90" s="9" t="n">
-        <v>0.9495</v>
+        <v>0</v>
       </c>
       <c r="R90" s="7" t="n">
-        <v>1658538.55</v>
+        <v>14144248.92</v>
       </c>
       <c r="S90" s="7" t="n">
         <v>0</v>
@@ -40745,40 +41020,40 @@
         <v>0</v>
       </c>
       <c r="AE90" s="7" t="n">
-        <v>1252183.89</v>
+        <v>0</v>
       </c>
       <c r="AF90" s="7" t="n">
-        <v>2696269.1</v>
+        <v>0</v>
       </c>
       <c r="AG90" s="7" t="n">
-        <v>4871474.25</v>
+        <v>0</v>
       </c>
       <c r="AH90" s="7" t="n">
-        <v>4497352.58</v>
+        <v>0</v>
       </c>
       <c r="AI90" s="7" t="n">
-        <v>3228080.73</v>
+        <v>0</v>
       </c>
       <c r="AJ90" s="7" t="n">
-        <v>3793877.75</v>
+        <v>0</v>
       </c>
       <c r="AK90" s="7" t="n">
-        <v>2375732.68</v>
+        <v>0</v>
       </c>
       <c r="AL90" s="7" t="n">
-        <v>1212320.58</v>
+        <v>0</v>
       </c>
       <c r="AM90" s="7" t="n">
-        <v>4888556.81</v>
+        <v>0</v>
       </c>
       <c r="AN90" s="7" t="n">
-        <v>1660361.27</v>
+        <v>0</v>
       </c>
       <c r="AO90" s="7" t="n">
-        <v>426548.56</v>
+        <v>0</v>
       </c>
       <c r="AP90" s="7" t="n">
-        <v>275478.01</v>
+        <v>0</v>
       </c>
       <c r="AQ90" s="7" t="n">
         <v>0</v>
@@ -40931,7 +41206,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>E-17/001/81/2013</t>
+          <t>330018/000982/2021</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
@@ -40940,37 +41215,41 @@
         </is>
       </c>
       <c r="D91" s="4" t="n">
-        <v>2569</v>
+        <v>932</v>
       </c>
       <c r="E91" s="6" t="n">
-        <v>41443</v>
+        <v>44708</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>44012</v>
+        <v>45640</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>14144248.92</v>
+        <v>1923627.23</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>NÃO CONCLUÍDA</t>
-        </is>
-      </c>
-      <c r="I91" s="4" t="inlineStr"/>
+          <t>CONCLUÍDA</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>CARLOS FERNANDES</t>
+        </is>
+      </c>
       <c r="J91" s="4" t="inlineStr"/>
-      <c r="K91" s="12" t="inlineStr">
-        <is>
-          <t>MT</t>
+      <c r="K91" s="10" t="inlineStr">
+        <is>
+          <t>NT</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>Nova Friburgo</t>
         </is>
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>SEVEME</t>
+          <t>SOLOTESTE</t>
         </is>
       </c>
       <c r="N91" s="7" t="n">
@@ -40980,13 +41259,13 @@
         <v>0</v>
       </c>
       <c r="P91" s="7" t="n">
-        <v>0</v>
+        <v>1923627.23</v>
       </c>
       <c r="Q91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R91" s="7" t="n">
-        <v>14144248.92</v>
+        <v>-0.03</v>
       </c>
       <c r="S91" s="7" t="n">
         <v>0</v>
@@ -41040,28 +41319,28 @@
         <v>0</v>
       </c>
       <c r="AJ91" s="7" t="n">
-        <v>0</v>
+        <v>49621.01</v>
       </c>
       <c r="AK91" s="7" t="n">
-        <v>0</v>
+        <v>124085.56</v>
       </c>
       <c r="AL91" s="7" t="n">
-        <v>0</v>
+        <v>256348.22</v>
       </c>
       <c r="AM91" s="7" t="n">
-        <v>0</v>
+        <v>243547.65</v>
       </c>
       <c r="AN91" s="7" t="n">
-        <v>0</v>
+        <v>102567.02</v>
       </c>
       <c r="AO91" s="7" t="n">
-        <v>0</v>
+        <v>86297.64</v>
       </c>
       <c r="AP91" s="7" t="n">
-        <v>0</v>
+        <v>88959.88</v>
       </c>
       <c r="AQ91" s="7" t="n">
-        <v>0</v>
+        <v>21991.88</v>
       </c>
       <c r="AR91" s="7" t="n">
         <v>0</v>
@@ -41070,19 +41349,19 @@
         <v>0</v>
       </c>
       <c r="AT91" s="7" t="n">
-        <v>0</v>
+        <v>132786.18</v>
       </c>
       <c r="AU91" s="7" t="n">
-        <v>0</v>
+        <v>170182.8</v>
       </c>
       <c r="AV91" s="7" t="n">
-        <v>0</v>
+        <v>136974.88</v>
       </c>
       <c r="AW91" s="7" t="n">
-        <v>0</v>
+        <v>55704.54</v>
       </c>
       <c r="AX91" s="7" t="n">
-        <v>0</v>
+        <v>103693.23</v>
       </c>
       <c r="AY91" s="7" t="n">
         <v>0</v>
@@ -41115,19 +41394,19 @@
         <v>0</v>
       </c>
       <c r="BI91" s="7" t="n">
-        <v>0</v>
+        <v>79200.21000000001</v>
       </c>
       <c r="BJ91" s="7" t="n">
-        <v>0</v>
+        <v>82637.3</v>
       </c>
       <c r="BK91" s="7" t="n">
-        <v>0</v>
+        <v>113915.66</v>
       </c>
       <c r="BL91" s="7" t="n">
-        <v>0</v>
+        <v>49286.75</v>
       </c>
       <c r="BM91" s="7" t="n">
-        <v>0</v>
+        <v>25826.83</v>
       </c>
       <c r="BN91" s="7" t="n">
         <v>0</v>
@@ -41211,7 +41490,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>330018/000982/2021</t>
+          <t>330018/000748/2022</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
@@ -41220,41 +41499,41 @@
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>932</v>
+        <v>360</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>44708</v>
+        <v>45100</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>45640</v>
+        <v>45460</v>
       </c>
       <c r="G92" s="7" t="n">
-        <v>1923627.23</v>
+        <v>16774604.06</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>CONCLUÍDA</t>
+          <t>NÃO CONCLUÍDA</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>CARLOS FERNANDES</t>
+          <t>LUIZ FILHO</t>
         </is>
       </c>
       <c r="J92" s="4" t="inlineStr"/>
-      <c r="K92" s="10" t="inlineStr">
-        <is>
-          <t>NT</t>
+      <c r="K92" s="8" t="inlineStr">
+        <is>
+          <t>SL</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>Nova Friburgo</t>
+          <t>Barra do Piraí</t>
         </is>
       </c>
       <c r="M92" s="4" t="inlineStr">
         <is>
-          <t>SOLOTESTE</t>
+          <t>STATLED</t>
         </is>
       </c>
       <c r="N92" s="7" t="n">
@@ -41264,13 +41543,13 @@
         <v>0</v>
       </c>
       <c r="P92" s="7" t="n">
-        <v>1923627.23</v>
+        <v>16774604.06</v>
       </c>
       <c r="Q92" s="9" t="n">
-        <v>1</v>
+        <v>0.0076</v>
       </c>
       <c r="R92" s="7" t="n">
-        <v>-0.03</v>
+        <v>16646768.42</v>
       </c>
       <c r="S92" s="7" t="n">
         <v>0</v>
@@ -41324,28 +41603,28 @@
         <v>0</v>
       </c>
       <c r="AJ92" s="7" t="n">
-        <v>49621.01</v>
+        <v>0</v>
       </c>
       <c r="AK92" s="7" t="n">
-        <v>124085.56</v>
+        <v>0</v>
       </c>
       <c r="AL92" s="7" t="n">
-        <v>256348.22</v>
+        <v>0</v>
       </c>
       <c r="AM92" s="7" t="n">
-        <v>243547.65</v>
+        <v>0</v>
       </c>
       <c r="AN92" s="7" t="n">
-        <v>102567.02</v>
+        <v>0</v>
       </c>
       <c r="AO92" s="7" t="n">
-        <v>86297.64</v>
+        <v>0</v>
       </c>
       <c r="AP92" s="7" t="n">
-        <v>88959.88</v>
+        <v>0</v>
       </c>
       <c r="AQ92" s="7" t="n">
-        <v>21991.88</v>
+        <v>0</v>
       </c>
       <c r="AR92" s="7" t="n">
         <v>0</v>
@@ -41354,19 +41633,19 @@
         <v>0</v>
       </c>
       <c r="AT92" s="7" t="n">
-        <v>132786.18</v>
+        <v>0</v>
       </c>
       <c r="AU92" s="7" t="n">
-        <v>170182.8</v>
+        <v>127835.64</v>
       </c>
       <c r="AV92" s="7" t="n">
-        <v>136974.88</v>
+        <v>0</v>
       </c>
       <c r="AW92" s="7" t="n">
-        <v>55704.54</v>
+        <v>0</v>
       </c>
       <c r="AX92" s="7" t="n">
-        <v>103693.23</v>
+        <v>0</v>
       </c>
       <c r="AY92" s="7" t="n">
         <v>0</v>
@@ -41399,19 +41678,19 @@
         <v>0</v>
       </c>
       <c r="BI92" s="7" t="n">
-        <v>79200.21000000001</v>
+        <v>0</v>
       </c>
       <c r="BJ92" s="7" t="n">
-        <v>82637.3</v>
+        <v>0</v>
       </c>
       <c r="BK92" s="7" t="n">
-        <v>113915.66</v>
+        <v>0</v>
       </c>
       <c r="BL92" s="7" t="n">
-        <v>49286.75</v>
+        <v>0</v>
       </c>
       <c r="BM92" s="7" t="n">
-        <v>25826.83</v>
+        <v>0</v>
       </c>
       <c r="BN92" s="7" t="n">
         <v>0</v>
@@ -41495,7 +41774,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>330018/000748/2022</t>
+          <t>330018/001159/2022</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
@@ -41504,16 +41783,16 @@
         </is>
       </c>
       <c r="D93" s="4" t="n">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="E93" s="6" t="n">
         <v>45100</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>45460</v>
+        <v>45400</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>16774604.06</v>
+        <v>6784130.44</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
@@ -41522,18 +41801,18 @@
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>LUIZ FILHO</t>
+          <t>CARLOS FERNANDES</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr"/>
-      <c r="K93" s="8" t="inlineStr">
-        <is>
-          <t>SL</t>
+      <c r="K93" s="11" t="inlineStr">
+        <is>
+          <t>BX</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>Barra do Piraí</t>
+          <t>Queimados</t>
         </is>
       </c>
       <c r="M93" s="4" t="inlineStr">
@@ -41548,13 +41827,13 @@
         <v>0</v>
       </c>
       <c r="P93" s="7" t="n">
-        <v>16774604.06</v>
+        <v>0</v>
       </c>
       <c r="Q93" s="9" t="n">
-        <v>0.0076</v>
+        <v>0</v>
       </c>
       <c r="R93" s="7" t="n">
-        <v>16646768.42</v>
+        <v>6784130.44</v>
       </c>
       <c r="S93" s="7" t="n">
         <v>0</v>
@@ -41641,7 +41920,7 @@
         <v>0</v>
       </c>
       <c r="AU93" s="7" t="n">
-        <v>127835.64</v>
+        <v>0</v>
       </c>
       <c r="AV93" s="7" t="n">
         <v>0</v>
@@ -41779,7 +42058,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>330018/001159/2022</t>
+          <t>330018/001392/2022</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
@@ -41788,36 +42067,36 @@
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>300</v>
+        <v>724</v>
       </c>
       <c r="E94" s="6" t="n">
-        <v>45100</v>
+        <v>45019</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>45400</v>
+        <v>45743</v>
       </c>
       <c r="G94" s="7" t="n">
-        <v>6784130.44</v>
+        <v>30599999.01</v>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>NÃO CONCLUÍDA</t>
+          <t>CONCLUÍDA</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>CARLOS FERNANDES</t>
+          <t>ISADORA ROSALINO</t>
         </is>
       </c>
       <c r="J94" s="4" t="inlineStr"/>
-      <c r="K94" s="11" t="inlineStr">
-        <is>
-          <t>BX</t>
+      <c r="K94" s="8" t="inlineStr">
+        <is>
+          <t>SL</t>
         </is>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>Queimados</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="M94" s="4" t="inlineStr">
@@ -41832,13 +42111,13 @@
         <v>0</v>
       </c>
       <c r="P94" s="7" t="n">
-        <v>0</v>
+        <v>30599999.01</v>
       </c>
       <c r="Q94" s="9" t="n">
-        <v>0</v>
+        <v>0.9953</v>
       </c>
       <c r="R94" s="7" t="n">
-        <v>6784130.44</v>
+        <v>143704.68</v>
       </c>
       <c r="S94" s="7" t="n">
         <v>0</v>
@@ -41922,31 +42201,31 @@
         <v>0</v>
       </c>
       <c r="AT94" s="7" t="n">
-        <v>0</v>
+        <v>2345932.87</v>
       </c>
       <c r="AU94" s="7" t="n">
-        <v>0</v>
+        <v>1414040.86</v>
       </c>
       <c r="AV94" s="7" t="n">
-        <v>0</v>
+        <v>914901.4</v>
       </c>
       <c r="AW94" s="7" t="n">
-        <v>0</v>
+        <v>118615.88</v>
       </c>
       <c r="AX94" s="7" t="n">
-        <v>0</v>
+        <v>25544.46</v>
       </c>
       <c r="AY94" s="7" t="n">
-        <v>0</v>
+        <v>205134.66</v>
       </c>
       <c r="AZ94" s="7" t="n">
-        <v>0</v>
+        <v>1222905.88</v>
       </c>
       <c r="BA94" s="7" t="n">
-        <v>0</v>
+        <v>1094079.72</v>
       </c>
       <c r="BB94" s="7" t="n">
-        <v>0</v>
+        <v>2386262.51</v>
       </c>
       <c r="BC94" s="7" t="n">
         <v>0</v>
@@ -41958,22 +42237,22 @@
         <v>0</v>
       </c>
       <c r="BF94" s="7" t="n">
-        <v>0</v>
+        <v>1951646.51</v>
       </c>
       <c r="BG94" s="7" t="n">
-        <v>0</v>
+        <v>3941943.7</v>
       </c>
       <c r="BH94" s="7" t="n">
-        <v>0</v>
+        <v>3466477.58</v>
       </c>
       <c r="BI94" s="7" t="n">
-        <v>0</v>
+        <v>5469516.6</v>
       </c>
       <c r="BJ94" s="7" t="n">
-        <v>0</v>
+        <v>2906940.33</v>
       </c>
       <c r="BK94" s="7" t="n">
-        <v>0</v>
+        <v>2992351.37</v>
       </c>
       <c r="BL94" s="7" t="n">
         <v>0</v>
@@ -42063,7 +42342,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>330018/001392/2022</t>
+          <t>330018/001042/2021</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
@@ -42072,41 +42351,37 @@
         </is>
       </c>
       <c r="D95" s="4" t="n">
-        <v>724</v>
+        <v>550</v>
       </c>
       <c r="E95" s="6" t="n">
-        <v>45019</v>
+        <v>44840</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>45743</v>
+        <v>45390</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>30599999.01</v>
+        <v>2394811.95</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>CONCLUÍDA</t>
-        </is>
-      </c>
-      <c r="I95" s="4" t="inlineStr">
-        <is>
-          <t>ISADORA ROSALINO</t>
-        </is>
-      </c>
+          <t>NÃO CONCLUÍDA</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr"/>
       <c r="J95" s="4" t="inlineStr"/>
-      <c r="K95" s="8" t="inlineStr">
-        <is>
-          <t>SL</t>
+      <c r="K95" s="10" t="inlineStr">
+        <is>
+          <t>NT</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Cardoso Moreira</t>
         </is>
       </c>
       <c r="M95" s="4" t="inlineStr">
         <is>
-          <t>STATLED</t>
+          <t>TOTAL CONST.</t>
         </is>
       </c>
       <c r="N95" s="7" t="n">
@@ -42116,13 +42391,13 @@
         <v>0</v>
       </c>
       <c r="P95" s="7" t="n">
-        <v>30599999.01</v>
+        <v>2394811.95</v>
       </c>
       <c r="Q95" s="9" t="n">
-        <v>0.9953</v>
+        <v>0.1104</v>
       </c>
       <c r="R95" s="7" t="n">
-        <v>143704.68</v>
+        <v>2130487.35</v>
       </c>
       <c r="S95" s="7" t="n">
         <v>0</v>
@@ -42188,10 +42463,10 @@
         <v>0</v>
       </c>
       <c r="AN95" s="7" t="n">
-        <v>0</v>
+        <v>195454.51</v>
       </c>
       <c r="AO95" s="7" t="n">
-        <v>0</v>
+        <v>68870.09</v>
       </c>
       <c r="AP95" s="7" t="n">
         <v>0</v>
@@ -42206,31 +42481,31 @@
         <v>0</v>
       </c>
       <c r="AT95" s="7" t="n">
-        <v>2345932.87</v>
+        <v>0</v>
       </c>
       <c r="AU95" s="7" t="n">
-        <v>1414040.86</v>
+        <v>0</v>
       </c>
       <c r="AV95" s="7" t="n">
-        <v>914901.4</v>
+        <v>0</v>
       </c>
       <c r="AW95" s="7" t="n">
-        <v>118615.88</v>
+        <v>0</v>
       </c>
       <c r="AX95" s="7" t="n">
-        <v>25544.46</v>
+        <v>0</v>
       </c>
       <c r="AY95" s="7" t="n">
-        <v>205134.66</v>
+        <v>0</v>
       </c>
       <c r="AZ95" s="7" t="n">
-        <v>1222905.88</v>
+        <v>0</v>
       </c>
       <c r="BA95" s="7" t="n">
-        <v>1094079.72</v>
+        <v>0</v>
       </c>
       <c r="BB95" s="7" t="n">
-        <v>2386262.51</v>
+        <v>0</v>
       </c>
       <c r="BC95" s="7" t="n">
         <v>0</v>
@@ -42242,22 +42517,22 @@
         <v>0</v>
       </c>
       <c r="BF95" s="7" t="n">
-        <v>1951646.51</v>
+        <v>0</v>
       </c>
       <c r="BG95" s="7" t="n">
-        <v>3941943.7</v>
+        <v>0</v>
       </c>
       <c r="BH95" s="7" t="n">
-        <v>3466477.58</v>
+        <v>0</v>
       </c>
       <c r="BI95" s="7" t="n">
-        <v>5469516.6</v>
+        <v>0</v>
       </c>
       <c r="BJ95" s="7" t="n">
-        <v>2906940.33</v>
+        <v>0</v>
       </c>
       <c r="BK95" s="7" t="n">
-        <v>2992351.37</v>
+        <v>0</v>
       </c>
       <c r="BL95" s="7" t="n">
         <v>0</v>
@@ -42347,7 +42622,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>330018/001042/2021</t>
+          <t>330018/000960/2021</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
@@ -42356,37 +42631,41 @@
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>550</v>
+        <v>993</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>44840</v>
+        <v>44823</v>
       </c>
       <c r="F96" s="6" t="n">
-        <v>45390</v>
+        <v>45816</v>
       </c>
       <c r="G96" s="7" t="n">
-        <v>2394811.95</v>
+        <v>26946699.36</v>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>NÃO CONCLUÍDA</t>
-        </is>
-      </c>
-      <c r="I96" s="4" t="inlineStr"/>
+          <t>CONCLUÍDA</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>GISELLE G. FONSECA</t>
+        </is>
+      </c>
       <c r="J96" s="4" t="inlineStr"/>
-      <c r="K96" s="10" t="inlineStr">
-        <is>
-          <t>NT</t>
+      <c r="K96" s="8" t="inlineStr">
+        <is>
+          <t>SL</t>
         </is>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>Cardoso Moreira</t>
+          <t>Porto Real</t>
         </is>
       </c>
       <c r="M96" s="4" t="inlineStr">
         <is>
-          <t>TOTAL CONST.</t>
+          <t>VALLE SUL</t>
         </is>
       </c>
       <c r="N96" s="7" t="n">
@@ -42396,13 +42675,13 @@
         <v>0</v>
       </c>
       <c r="P96" s="7" t="n">
-        <v>2394811.95</v>
+        <v>26946699.36</v>
       </c>
       <c r="Q96" s="9" t="n">
-        <v>0.1104</v>
+        <v>0.9994</v>
       </c>
       <c r="R96" s="7" t="n">
-        <v>2130487.35</v>
+        <v>15715.34</v>
       </c>
       <c r="S96" s="7" t="n">
         <v>0</v>
@@ -42465,49 +42744,49 @@
         <v>0</v>
       </c>
       <c r="AM96" s="7" t="n">
-        <v>0</v>
+        <v>40320.53</v>
       </c>
       <c r="AN96" s="7" t="n">
-        <v>195454.51</v>
+        <v>1376375.53</v>
       </c>
       <c r="AO96" s="7" t="n">
-        <v>68870.09</v>
+        <v>2736866.39</v>
       </c>
       <c r="AP96" s="7" t="n">
-        <v>0</v>
+        <v>1501922.59</v>
       </c>
       <c r="AQ96" s="7" t="n">
-        <v>0</v>
+        <v>1119770.09</v>
       </c>
       <c r="AR96" s="7" t="n">
-        <v>0</v>
+        <v>2735309.9</v>
       </c>
       <c r="AS96" s="7" t="n">
-        <v>0</v>
+        <v>2661273.96</v>
       </c>
       <c r="AT96" s="7" t="n">
-        <v>0</v>
+        <v>2250842.93</v>
       </c>
       <c r="AU96" s="7" t="n">
-        <v>0</v>
+        <v>2531089.81</v>
       </c>
       <c r="AV96" s="7" t="n">
-        <v>0</v>
+        <v>1991366.09</v>
       </c>
       <c r="AW96" s="7" t="n">
-        <v>0</v>
+        <v>2020437.14</v>
       </c>
       <c r="AX96" s="7" t="n">
-        <v>0</v>
+        <v>890788.2</v>
       </c>
       <c r="AY96" s="7" t="n">
-        <v>0</v>
+        <v>274255.72</v>
       </c>
       <c r="AZ96" s="7" t="n">
-        <v>0</v>
+        <v>10829.52</v>
       </c>
       <c r="BA96" s="7" t="n">
-        <v>0</v>
+        <v>17808.95</v>
       </c>
       <c r="BB96" s="7" t="n">
         <v>0</v>
@@ -42528,22 +42807,22 @@
         <v>0</v>
       </c>
       <c r="BH96" s="7" t="n">
-        <v>0</v>
+        <v>1445406.25</v>
       </c>
       <c r="BI96" s="7" t="n">
-        <v>0</v>
+        <v>986014.6</v>
       </c>
       <c r="BJ96" s="7" t="n">
-        <v>0</v>
+        <v>1196482.33</v>
       </c>
       <c r="BK96" s="7" t="n">
         <v>0</v>
       </c>
       <c r="BL96" s="7" t="n">
-        <v>0</v>
+        <v>797186.25</v>
       </c>
       <c r="BM96" s="7" t="n">
-        <v>0</v>
+        <v>346637.23</v>
       </c>
       <c r="BN96" s="7" t="n">
         <v>0</v>
@@ -42627,7 +42906,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>330018/000960/2021</t>
+          <t>330018/001069/2021</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
@@ -42636,16 +42915,16 @@
         </is>
       </c>
       <c r="D97" s="4" t="n">
-        <v>993</v>
+        <v>759</v>
       </c>
       <c r="E97" s="6" t="n">
-        <v>44823</v>
+        <v>44708</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>45816</v>
+        <v>45467</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>26946699.36</v>
+        <v>6014775.77</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
@@ -42658,14 +42937,14 @@
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr"/>
-      <c r="K97" s="8" t="inlineStr">
-        <is>
-          <t>SL</t>
+      <c r="K97" s="11" t="inlineStr">
+        <is>
+          <t>BX</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t>Porto Real</t>
+          <t>Rio Claro</t>
         </is>
       </c>
       <c r="M97" s="4" t="inlineStr">
@@ -42680,13 +42959,13 @@
         <v>0</v>
       </c>
       <c r="P97" s="7" t="n">
-        <v>26946699.36</v>
+        <v>6014775.77</v>
       </c>
       <c r="Q97" s="9" t="n">
-        <v>0.9994</v>
+        <v>0.997</v>
       </c>
       <c r="R97" s="7" t="n">
-        <v>15715.34</v>
+        <v>17886.09</v>
       </c>
       <c r="S97" s="7" t="n">
         <v>0</v>
@@ -42740,67 +43019,67 @@
         <v>0</v>
       </c>
       <c r="AJ97" s="7" t="n">
-        <v>0</v>
+        <v>1770722.09</v>
       </c>
       <c r="AK97" s="7" t="n">
-        <v>0</v>
+        <v>897418.65</v>
       </c>
       <c r="AL97" s="7" t="n">
-        <v>0</v>
+        <v>1574691.95</v>
       </c>
       <c r="AM97" s="7" t="n">
-        <v>40320.53</v>
+        <v>203315.88</v>
       </c>
       <c r="AN97" s="7" t="n">
-        <v>1376375.53</v>
+        <v>83181.07000000001</v>
       </c>
       <c r="AO97" s="7" t="n">
-        <v>2736866.39</v>
+        <v>0</v>
       </c>
       <c r="AP97" s="7" t="n">
-        <v>1501922.59</v>
+        <v>0</v>
       </c>
       <c r="AQ97" s="7" t="n">
-        <v>1119770.09</v>
+        <v>0</v>
       </c>
       <c r="AR97" s="7" t="n">
-        <v>2735309.9</v>
+        <v>0</v>
       </c>
       <c r="AS97" s="7" t="n">
-        <v>2661273.96</v>
+        <v>0</v>
       </c>
       <c r="AT97" s="7" t="n">
-        <v>2250842.93</v>
+        <v>0</v>
       </c>
       <c r="AU97" s="7" t="n">
-        <v>2531089.81</v>
+        <v>0</v>
       </c>
       <c r="AV97" s="7" t="n">
-        <v>1991366.09</v>
+        <v>0</v>
       </c>
       <c r="AW97" s="7" t="n">
-        <v>2020437.14</v>
+        <v>0</v>
       </c>
       <c r="AX97" s="7" t="n">
-        <v>890788.2</v>
+        <v>0</v>
       </c>
       <c r="AY97" s="7" t="n">
-        <v>274255.72</v>
+        <v>0</v>
       </c>
       <c r="AZ97" s="7" t="n">
-        <v>10829.52</v>
+        <v>871587.5600000001</v>
       </c>
       <c r="BA97" s="7" t="n">
-        <v>17808.95</v>
+        <v>311020.27</v>
       </c>
       <c r="BB97" s="7" t="n">
         <v>0</v>
       </c>
       <c r="BC97" s="7" t="n">
-        <v>0</v>
+        <v>99502.36</v>
       </c>
       <c r="BD97" s="7" t="n">
-        <v>0</v>
+        <v>185449.85</v>
       </c>
       <c r="BE97" s="7" t="n">
         <v>0</v>
@@ -42812,22 +43091,22 @@
         <v>0</v>
       </c>
       <c r="BH97" s="7" t="n">
-        <v>1445406.25</v>
+        <v>0</v>
       </c>
       <c r="BI97" s="7" t="n">
-        <v>986014.6</v>
+        <v>0</v>
       </c>
       <c r="BJ97" s="7" t="n">
-        <v>1196482.33</v>
+        <v>0</v>
       </c>
       <c r="BK97" s="7" t="n">
         <v>0</v>
       </c>
       <c r="BL97" s="7" t="n">
-        <v>797186.25</v>
+        <v>0</v>
       </c>
       <c r="BM97" s="7" t="n">
-        <v>346637.23</v>
+        <v>0</v>
       </c>
       <c r="BN97" s="7" t="n">
         <v>0</v>
@@ -42911,7 +43190,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>330018/001069/2021</t>
+          <t>330018/000698/2021</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
@@ -42920,20 +43199,20 @@
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>759</v>
+        <v>768</v>
       </c>
       <c r="E98" s="6" t="n">
-        <v>44708</v>
+        <v>44658</v>
       </c>
       <c r="F98" s="6" t="n">
-        <v>45467</v>
+        <v>45426</v>
       </c>
       <c r="G98" s="7" t="n">
-        <v>6014775.77</v>
+        <v>3569195.39</v>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>CONCLUÍDA</t>
+          <t>NÃO CONCLUÍDA</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr">
@@ -42964,13 +43243,13 @@
         <v>0</v>
       </c>
       <c r="P98" s="7" t="n">
-        <v>6014775.77</v>
+        <v>3569195.39</v>
       </c>
       <c r="Q98" s="9" t="n">
-        <v>0.997</v>
+        <v>0.9913</v>
       </c>
       <c r="R98" s="7" t="n">
-        <v>17886.09</v>
+        <v>31194.23</v>
       </c>
       <c r="S98" s="7" t="n">
         <v>0</v>
@@ -43018,25 +43297,25 @@
         <v>0</v>
       </c>
       <c r="AH98" s="7" t="n">
-        <v>0</v>
+        <v>347400.67</v>
       </c>
       <c r="AI98" s="7" t="n">
-        <v>0</v>
+        <v>645282.2</v>
       </c>
       <c r="AJ98" s="7" t="n">
-        <v>1770722.09</v>
+        <v>510653.43</v>
       </c>
       <c r="AK98" s="7" t="n">
-        <v>897418.65</v>
+        <v>670047.79</v>
       </c>
       <c r="AL98" s="7" t="n">
-        <v>1574691.95</v>
+        <v>421649.51</v>
       </c>
       <c r="AM98" s="7" t="n">
-        <v>203315.88</v>
+        <v>903704.0600000001</v>
       </c>
       <c r="AN98" s="7" t="n">
-        <v>83181.07000000001</v>
+        <v>39263.5</v>
       </c>
       <c r="AO98" s="7" t="n">
         <v>0</v>
@@ -43072,19 +43351,19 @@
         <v>0</v>
       </c>
       <c r="AZ98" s="7" t="n">
-        <v>871587.5600000001</v>
+        <v>0</v>
       </c>
       <c r="BA98" s="7" t="n">
-        <v>311020.27</v>
+        <v>0</v>
       </c>
       <c r="BB98" s="7" t="n">
         <v>0</v>
       </c>
       <c r="BC98" s="7" t="n">
-        <v>99502.36</v>
+        <v>0</v>
       </c>
       <c r="BD98" s="7" t="n">
-        <v>185449.85</v>
+        <v>0</v>
       </c>
       <c r="BE98" s="7" t="n">
         <v>0</v>
@@ -43195,7 +43474,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>330018/000698/2021</t>
+          <t>170026/003834/2021</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
@@ -43204,41 +43483,37 @@
         </is>
       </c>
       <c r="D99" s="4" t="n">
-        <v>768</v>
+        <v>528</v>
       </c>
       <c r="E99" s="6" t="n">
-        <v>44658</v>
+        <v>44883</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>45426</v>
+        <v>45411</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>3569195.39</v>
+        <v>2975474.34</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>NÃO CONCLUÍDA</t>
-        </is>
-      </c>
-      <c r="I99" s="4" t="inlineStr">
-        <is>
-          <t>GISELLE G. FONSECA</t>
-        </is>
-      </c>
+          <t>CONCLUÍDA</t>
+        </is>
+      </c>
+      <c r="I99" s="4" t="inlineStr"/>
       <c r="J99" s="4" t="inlineStr"/>
-      <c r="K99" s="11" t="inlineStr">
-        <is>
-          <t>BX</t>
+      <c r="K99" s="10" t="inlineStr">
+        <is>
+          <t>NT</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>Rio Claro</t>
+          <t>Carmo</t>
         </is>
       </c>
       <c r="M99" s="4" t="inlineStr">
         <is>
-          <t>VALLE SUL</t>
+          <t>VISION RIO</t>
         </is>
       </c>
       <c r="N99" s="7" t="n">
@@ -43248,13 +43523,13 @@
         <v>0</v>
       </c>
       <c r="P99" s="7" t="n">
-        <v>3569195.39</v>
+        <v>2975474.34</v>
       </c>
       <c r="Q99" s="9" t="n">
-        <v>0.9913</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="R99" s="7" t="n">
-        <v>31194.23</v>
+        <v>177.02</v>
       </c>
       <c r="S99" s="7" t="n">
         <v>0</v>
@@ -43302,28 +43577,28 @@
         <v>0</v>
       </c>
       <c r="AH99" s="7" t="n">
-        <v>347400.67</v>
+        <v>0</v>
       </c>
       <c r="AI99" s="7" t="n">
-        <v>645282.2</v>
+        <v>0</v>
       </c>
       <c r="AJ99" s="7" t="n">
-        <v>510653.43</v>
+        <v>0</v>
       </c>
       <c r="AK99" s="7" t="n">
-        <v>670047.79</v>
+        <v>0</v>
       </c>
       <c r="AL99" s="7" t="n">
-        <v>421649.51</v>
+        <v>0</v>
       </c>
       <c r="AM99" s="7" t="n">
-        <v>903704.0600000001</v>
+        <v>0</v>
       </c>
       <c r="AN99" s="7" t="n">
-        <v>39263.5</v>
+        <v>0</v>
       </c>
       <c r="AO99" s="7" t="n">
-        <v>0</v>
+        <v>1723298</v>
       </c>
       <c r="AP99" s="7" t="n">
         <v>0</v>
@@ -43332,10 +43607,10 @@
         <v>0</v>
       </c>
       <c r="AR99" s="7" t="n">
-        <v>0</v>
+        <v>1196572.32</v>
       </c>
       <c r="AS99" s="7" t="n">
-        <v>0</v>
+        <v>55427</v>
       </c>
       <c r="AT99" s="7" t="n">
         <v>0</v>
@@ -43479,7 +43754,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>170026/003834/2021</t>
+          <t>170026/002388/2021</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
@@ -43488,16 +43763,16 @@
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>528</v>
+        <v>271</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>44883</v>
+        <v>44911</v>
       </c>
       <c r="F100" s="6" t="n">
-        <v>45411</v>
+        <v>45182</v>
       </c>
       <c r="G100" s="7" t="n">
-        <v>2975474.34</v>
+        <v>724764.22</v>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
@@ -43506,19 +43781,19 @@
       </c>
       <c r="I100" s="4" t="inlineStr"/>
       <c r="J100" s="4" t="inlineStr"/>
-      <c r="K100" s="10" t="inlineStr">
-        <is>
-          <t>NT</t>
+      <c r="K100" s="8" t="inlineStr">
+        <is>
+          <t>SL</t>
         </is>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>Carmo</t>
+          <t>Miguel Pereira</t>
         </is>
       </c>
       <c r="M100" s="4" t="inlineStr">
         <is>
-          <t>VISION RIO</t>
+          <t>WTE ENGENHARIA EIRELI</t>
         </is>
       </c>
       <c r="N100" s="7" t="n">
@@ -43528,13 +43803,13 @@
         <v>0</v>
       </c>
       <c r="P100" s="7" t="n">
-        <v>2975474.34</v>
+        <v>724764.22</v>
       </c>
       <c r="Q100" s="9" t="n">
-        <v>0.9998999999999999</v>
+        <v>1</v>
       </c>
       <c r="R100" s="7" t="n">
-        <v>177.02</v>
+        <v>0</v>
       </c>
       <c r="S100" s="7" t="n">
         <v>0</v>
@@ -43603,7 +43878,7 @@
         <v>0</v>
       </c>
       <c r="AO100" s="7" t="n">
-        <v>1723298</v>
+        <v>0</v>
       </c>
       <c r="AP100" s="7" t="n">
         <v>0</v>
@@ -43612,19 +43887,19 @@
         <v>0</v>
       </c>
       <c r="AR100" s="7" t="n">
-        <v>1196572.32</v>
+        <v>0</v>
       </c>
       <c r="AS100" s="7" t="n">
-        <v>55427</v>
+        <v>364158.55</v>
       </c>
       <c r="AT100" s="7" t="n">
-        <v>0</v>
+        <v>144181.31</v>
       </c>
       <c r="AU100" s="7" t="n">
-        <v>0</v>
+        <v>114920.76</v>
       </c>
       <c r="AV100" s="7" t="n">
-        <v>0</v>
+        <v>101503.6</v>
       </c>
       <c r="AW100" s="7" t="n">
         <v>0</v>
@@ -43759,7 +44034,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>170026/002388/2021</t>
+          <t>170026/001303/2020</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
@@ -43768,16 +44043,16 @@
         </is>
       </c>
       <c r="D101" s="4" t="n">
-        <v>271</v>
+        <v>670</v>
       </c>
       <c r="E101" s="6" t="n">
-        <v>44911</v>
+        <v>44742</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>45182</v>
+        <v>45412</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>724764.22</v>
+        <v>1988555.07</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
@@ -43793,7 +44068,7 @@
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
-          <t>Miguel Pereira</t>
+          <t>Pinheiral</t>
         </is>
       </c>
       <c r="M101" s="4" t="inlineStr">
@@ -43808,13 +44083,13 @@
         <v>0</v>
       </c>
       <c r="P101" s="7" t="n">
-        <v>724764.22</v>
+        <v>1988555.07</v>
       </c>
       <c r="Q101" s="9" t="n">
-        <v>1</v>
+        <v>0.9718000000000001</v>
       </c>
       <c r="R101" s="7" t="n">
-        <v>0</v>
+        <v>56006.44</v>
       </c>
       <c r="S101" s="7" t="n">
         <v>0</v>
@@ -43871,22 +44146,22 @@
         <v>0</v>
       </c>
       <c r="AK101" s="7" t="n">
-        <v>0</v>
+        <v>167615.99</v>
       </c>
       <c r="AL101" s="7" t="n">
-        <v>0</v>
+        <v>349263.45</v>
       </c>
       <c r="AM101" s="7" t="n">
-        <v>0</v>
+        <v>601788.92</v>
       </c>
       <c r="AN101" s="7" t="n">
-        <v>0</v>
+        <v>275710.63</v>
       </c>
       <c r="AO101" s="7" t="n">
-        <v>0</v>
+        <v>210741.28</v>
       </c>
       <c r="AP101" s="7" t="n">
-        <v>0</v>
+        <v>327428.36</v>
       </c>
       <c r="AQ101" s="7" t="n">
         <v>0</v>
@@ -43895,16 +44170,16 @@
         <v>0</v>
       </c>
       <c r="AS101" s="7" t="n">
-        <v>364158.55</v>
+        <v>0</v>
       </c>
       <c r="AT101" s="7" t="n">
-        <v>144181.31</v>
+        <v>0</v>
       </c>
       <c r="AU101" s="7" t="n">
-        <v>114920.76</v>
+        <v>0</v>
       </c>
       <c r="AV101" s="7" t="n">
-        <v>101503.6</v>
+        <v>0</v>
       </c>
       <c r="AW101" s="7" t="n">
         <v>0</v>
@@ -44039,7 +44314,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>170026/001303/2020</t>
+          <t>170026/001868/2021</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
@@ -44048,16 +44323,16 @@
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>670</v>
+        <v>544</v>
       </c>
       <c r="E102" s="6" t="n">
-        <v>44742</v>
+        <v>44772</v>
       </c>
       <c r="F102" s="6" t="n">
-        <v>45412</v>
+        <v>45316</v>
       </c>
       <c r="G102" s="7" t="n">
-        <v>1988555.07</v>
+        <v>1690234.37</v>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
@@ -44073,7 +44348,7 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>Pinheiral</t>
+          <t>Porto Real</t>
         </is>
       </c>
       <c r="M102" s="4" t="inlineStr">
@@ -44088,13 +44363,13 @@
         <v>0</v>
       </c>
       <c r="P102" s="7" t="n">
-        <v>1988555.07</v>
+        <v>1690234.37</v>
       </c>
       <c r="Q102" s="9" t="n">
-        <v>0.9718000000000001</v>
+        <v>0.9931</v>
       </c>
       <c r="R102" s="7" t="n">
-        <v>56006.44</v>
+        <v>11624.18</v>
       </c>
       <c r="S102" s="7" t="n">
         <v>0</v>
@@ -44151,25 +44426,25 @@
         <v>0</v>
       </c>
       <c r="AK102" s="7" t="n">
-        <v>167615.99</v>
+        <v>214289.72</v>
       </c>
       <c r="AL102" s="7" t="n">
-        <v>349263.45</v>
+        <v>213540.59</v>
       </c>
       <c r="AM102" s="7" t="n">
-        <v>601788.92</v>
+        <v>407765.72</v>
       </c>
       <c r="AN102" s="7" t="n">
-        <v>275710.63</v>
+        <v>288110.94</v>
       </c>
       <c r="AO102" s="7" t="n">
-        <v>210741.28</v>
+        <v>329339.67</v>
       </c>
       <c r="AP102" s="7" t="n">
-        <v>327428.36</v>
+        <v>127565.39</v>
       </c>
       <c r="AQ102" s="7" t="n">
-        <v>0</v>
+        <v>97698.16</v>
       </c>
       <c r="AR102" s="7" t="n">
         <v>0</v>
@@ -44319,62 +44594,66 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>170026/001868/2021</t>
-        </is>
-      </c>
-      <c r="C103" s="5" t="inlineStr">
-        <is>
-          <t>CIVIS</t>
+          <t>330018/000245/2022</t>
+        </is>
+      </c>
+      <c r="C103" s="13" t="inlineStr">
+        <is>
+          <t>CONTINGENCIA</t>
         </is>
       </c>
       <c r="D103" s="4" t="n">
-        <v>544</v>
+        <v>210</v>
       </c>
       <c r="E103" s="6" t="n">
-        <v>44772</v>
+        <v>45776</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>45316</v>
+        <v>45986</v>
       </c>
       <c r="G103" s="7" t="n">
-        <v>1690234.37</v>
+        <v>1612154.63</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
           <t>CONCLUÍDA</t>
         </is>
       </c>
-      <c r="I103" s="4" t="inlineStr"/>
+      <c r="I103" s="4" t="inlineStr">
+        <is>
+          <t>GISELLE G. FONSECA</t>
+        </is>
+      </c>
       <c r="J103" s="4" t="inlineStr"/>
-      <c r="K103" s="8" t="inlineStr">
-        <is>
-          <t>SL</t>
+      <c r="K103" s="12" t="inlineStr">
+        <is>
+          <t>MT</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
-          <t>Porto Real</t>
+          <t>Rio Bonito</t>
         </is>
       </c>
       <c r="M103" s="4" t="inlineStr">
         <is>
-          <t>WTE ENGENHARIA EIRELI</t>
+          <t>ENEX</t>
         </is>
       </c>
       <c r="N103" s="7" t="n">
-        <v>0</v>
+        <v>1612016.33</v>
       </c>
       <c r="O103" s="7" t="n">
         <v>0</v>
       </c>
       <c r="P103" s="7" t="n">
-        <v>1690234.37</v>
+        <v>1612154.63</v>
       </c>
       <c r="Q103" s="9" t="n">
-        <v>0.9931</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="R103" s="7" t="n">
-        <v>11624.18</v>
+        <v>129.78</v>
       </c>
       <c r="S103" s="7" t="n">
         <v>0</v>
@@ -44431,25 +44710,25 @@
         <v>0</v>
       </c>
       <c r="AK103" s="7" t="n">
-        <v>214289.72</v>
+        <v>0</v>
       </c>
       <c r="AL103" s="7" t="n">
-        <v>213540.59</v>
+        <v>0</v>
       </c>
       <c r="AM103" s="7" t="n">
-        <v>407765.72</v>
+        <v>0</v>
       </c>
       <c r="AN103" s="7" t="n">
-        <v>288110.94</v>
+        <v>0</v>
       </c>
       <c r="AO103" s="7" t="n">
-        <v>329339.67</v>
+        <v>0</v>
       </c>
       <c r="AP103" s="7" t="n">
-        <v>127565.39</v>
+        <v>0</v>
       </c>
       <c r="AQ103" s="7" t="n">
-        <v>97698.16</v>
+        <v>0</v>
       </c>
       <c r="AR103" s="7" t="n">
         <v>0</v>
@@ -44530,28 +44809,28 @@
         <v>0</v>
       </c>
       <c r="BR103" s="7" t="n">
-        <v>0</v>
+        <v>54154.23</v>
       </c>
       <c r="BS103" s="7" t="n">
-        <v>0</v>
+        <v>100801.91</v>
       </c>
       <c r="BT103" s="7" t="n">
-        <v>0</v>
+        <v>293372.72</v>
       </c>
       <c r="BU103" s="7" t="n">
-        <v>0</v>
+        <v>343266.53</v>
       </c>
       <c r="BV103" s="7" t="n">
-        <v>0</v>
+        <v>233380.03</v>
       </c>
       <c r="BW103" s="7" t="n">
-        <v>0</v>
+        <v>374191.54</v>
       </c>
       <c r="BX103" s="7" t="n">
-        <v>0</v>
+        <v>51750.66</v>
       </c>
       <c r="BY103" s="7" t="n">
-        <v>0</v>
+        <v>161098.71</v>
       </c>
       <c r="BZ103" s="7" t="n">
         <v>0</v>
@@ -44599,7 +44878,7 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>330018/000245/2022</t>
+          <t>330001/001217/2024</t>
         </is>
       </c>
       <c r="C104" s="13" t="inlineStr">
@@ -44608,16 +44887,16 @@
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>210</v>
+        <v>359</v>
       </c>
       <c r="E104" s="6" t="n">
-        <v>45776</v>
+        <v>45646</v>
       </c>
       <c r="F104" s="6" t="n">
-        <v>45986</v>
+        <v>46005</v>
       </c>
       <c r="G104" s="7" t="n">
-        <v>1612154.63</v>
+        <v>25179808.67</v>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
@@ -44630,35 +44909,35 @@
         </is>
       </c>
       <c r="J104" s="4" t="inlineStr"/>
-      <c r="K104" s="12" t="inlineStr">
-        <is>
-          <t>MT</t>
+      <c r="K104" s="8" t="inlineStr">
+        <is>
+          <t>SL</t>
         </is>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>Rio Bonito</t>
+          <t>Mendes</t>
         </is>
       </c>
       <c r="M104" s="4" t="inlineStr">
         <is>
-          <t>ENEX</t>
+          <t>MENDES KLABIN</t>
         </is>
       </c>
       <c r="N104" s="7" t="n">
-        <v>1612016.33</v>
+        <v>21884193.46</v>
       </c>
       <c r="O104" s="7" t="n">
         <v>0</v>
       </c>
       <c r="P104" s="7" t="n">
-        <v>1612154.63</v>
+        <v>25179808.67</v>
       </c>
       <c r="Q104" s="9" t="n">
-        <v>0.9998999999999999</v>
+        <v>0.9969</v>
       </c>
       <c r="R104" s="7" t="n">
-        <v>129.78</v>
+        <v>77530.64</v>
       </c>
       <c r="S104" s="7" t="n">
         <v>0</v>
@@ -44802,40 +45081,40 @@
         <v>0</v>
       </c>
       <c r="BN104" s="7" t="n">
-        <v>0</v>
+        <v>3218084.47</v>
       </c>
       <c r="BO104" s="7" t="n">
-        <v>0</v>
+        <v>1708705.48</v>
       </c>
       <c r="BP104" s="7" t="n">
-        <v>0</v>
+        <v>3195820.11</v>
       </c>
       <c r="BQ104" s="7" t="n">
-        <v>0</v>
+        <v>3082384.72</v>
       </c>
       <c r="BR104" s="7" t="n">
-        <v>54154.23</v>
+        <v>3081583.5</v>
       </c>
       <c r="BS104" s="7" t="n">
-        <v>100801.91</v>
+        <v>4440676.6</v>
       </c>
       <c r="BT104" s="7" t="n">
-        <v>293372.72</v>
+        <v>0</v>
       </c>
       <c r="BU104" s="7" t="n">
-        <v>343266.53</v>
+        <v>3472953.84</v>
       </c>
       <c r="BV104" s="7" t="n">
-        <v>233380.03</v>
+        <v>461617.82</v>
       </c>
       <c r="BW104" s="7" t="n">
-        <v>374191.54</v>
+        <v>2440451.39</v>
       </c>
       <c r="BX104" s="7" t="n">
-        <v>51750.66</v>
+        <v>0</v>
       </c>
       <c r="BY104" s="7" t="n">
-        <v>161098.71</v>
+        <v>0</v>
       </c>
       <c r="BZ104" s="7" t="n">
         <v>0</v>
@@ -44883,7 +45162,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>330001/001217/2024</t>
+          <t>330001/001278/2024</t>
         </is>
       </c>
       <c r="C105" s="13" t="inlineStr">
@@ -44892,16 +45171,16 @@
         </is>
       </c>
       <c r="D105" s="4" t="n">
-        <v>359</v>
+        <v>181</v>
       </c>
       <c r="E105" s="6" t="n">
-        <v>45646</v>
+        <v>45783</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>46005</v>
+        <v>45964</v>
       </c>
       <c r="G105" s="7" t="n">
-        <v>25179808.67</v>
+        <v>666913.6800000001</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
@@ -44914,35 +45193,35 @@
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr"/>
-      <c r="K105" s="8" t="inlineStr">
-        <is>
-          <t>SL</t>
+      <c r="K105" s="11" t="inlineStr">
+        <is>
+          <t>BX</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
-          <t>Mendes</t>
+          <t>Nilópolis</t>
         </is>
       </c>
       <c r="M105" s="4" t="inlineStr">
         <is>
-          <t>MENDES KLABIN</t>
+          <t>SOLOTESTE</t>
         </is>
       </c>
       <c r="N105" s="7" t="n">
-        <v>21884193.46</v>
+        <v>666913.6800000001</v>
       </c>
       <c r="O105" s="7" t="n">
         <v>0</v>
       </c>
       <c r="P105" s="7" t="n">
-        <v>25179808.67</v>
+        <v>666913.6800000001</v>
       </c>
       <c r="Q105" s="9" t="n">
-        <v>0.9969</v>
+        <v>0.8991</v>
       </c>
       <c r="R105" s="7" t="n">
-        <v>77530.64</v>
+        <v>67272.37</v>
       </c>
       <c r="S105" s="7" t="n">
         <v>0</v>
@@ -45086,40 +45365,40 @@
         <v>0</v>
       </c>
       <c r="BN105" s="7" t="n">
-        <v>3218084.47</v>
+        <v>0</v>
       </c>
       <c r="BO105" s="7" t="n">
-        <v>1708705.48</v>
+        <v>0</v>
       </c>
       <c r="BP105" s="7" t="n">
-        <v>3195820.11</v>
+        <v>0</v>
       </c>
       <c r="BQ105" s="7" t="n">
-        <v>3082384.72</v>
+        <v>0</v>
       </c>
       <c r="BR105" s="7" t="n">
-        <v>3081583.5</v>
+        <v>0</v>
       </c>
       <c r="BS105" s="7" t="n">
-        <v>4440676.6</v>
+        <v>54982.84</v>
       </c>
       <c r="BT105" s="7" t="n">
         <v>0</v>
       </c>
       <c r="BU105" s="7" t="n">
-        <v>3472953.84</v>
+        <v>331805.71</v>
       </c>
       <c r="BV105" s="7" t="n">
-        <v>461617.82</v>
+        <v>0</v>
       </c>
       <c r="BW105" s="7" t="n">
-        <v>2440451.39</v>
+        <v>93982.96000000001</v>
       </c>
       <c r="BX105" s="7" t="n">
-        <v>0</v>
+        <v>118869.68</v>
       </c>
       <c r="BY105" s="7" t="n">
-        <v>0</v>
+        <v>67272.49000000001</v>
       </c>
       <c r="BZ105" s="7" t="n">
         <v>0</v>
@@ -45167,25 +45446,25 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>330001/001278/2024</t>
-        </is>
-      </c>
-      <c r="C106" s="13" t="inlineStr">
-        <is>
-          <t>CONTINGENCIA</t>
+          <t>390005/000096/2021</t>
+        </is>
+      </c>
+      <c r="C106" s="14" t="inlineStr">
+        <is>
+          <t>ESPECIAIS</t>
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>181</v>
+        <v>570</v>
       </c>
       <c r="E106" s="6" t="n">
-        <v>45783</v>
+        <v>44613</v>
       </c>
       <c r="F106" s="6" t="n">
-        <v>45964</v>
+        <v>45183</v>
       </c>
       <c r="G106" s="7" t="n">
-        <v>666913.6800000001</v>
+        <v>1052239.53</v>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
@@ -45194,39 +45473,39 @@
       </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>GISELLE G. FONSECA</t>
+          <t>MARCUS PAULO</t>
         </is>
       </c>
       <c r="J106" s="4" t="inlineStr"/>
-      <c r="K106" s="11" t="inlineStr">
-        <is>
-          <t>BX</t>
+      <c r="K106" s="12" t="inlineStr">
+        <is>
+          <t>MT</t>
         </is>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>Nilópolis</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="M106" s="4" t="inlineStr">
         <is>
-          <t>SOLOTESTE</t>
+          <t>ABBM BRAGA</t>
         </is>
       </c>
       <c r="N106" s="7" t="n">
-        <v>666913.6800000001</v>
+        <v>0</v>
       </c>
       <c r="O106" s="7" t="n">
         <v>0</v>
       </c>
       <c r="P106" s="7" t="n">
-        <v>666913.6800000001</v>
+        <v>1052239.53</v>
       </c>
       <c r="Q106" s="9" t="n">
-        <v>0.8991</v>
+        <v>0.9562999999999999</v>
       </c>
       <c r="R106" s="7" t="n">
-        <v>67272.37</v>
+        <v>46004.38</v>
       </c>
       <c r="S106" s="7" t="n">
         <v>0</v>
@@ -45271,10 +45550,10 @@
         <v>0</v>
       </c>
       <c r="AG106" s="7" t="n">
-        <v>0</v>
+        <v>480649.82</v>
       </c>
       <c r="AH106" s="7" t="n">
-        <v>0</v>
+        <v>150863.84</v>
       </c>
       <c r="AI106" s="7" t="n">
         <v>0</v>
@@ -45313,7 +45592,7 @@
         <v>0</v>
       </c>
       <c r="AU106" s="7" t="n">
-        <v>0</v>
+        <v>374721.49</v>
       </c>
       <c r="AV106" s="7" t="n">
         <v>0</v>
@@ -45385,25 +45664,25 @@
         <v>0</v>
       </c>
       <c r="BS106" s="7" t="n">
-        <v>54982.84</v>
+        <v>0</v>
       </c>
       <c r="BT106" s="7" t="n">
         <v>0</v>
       </c>
       <c r="BU106" s="7" t="n">
-        <v>331805.71</v>
+        <v>0</v>
       </c>
       <c r="BV106" s="7" t="n">
         <v>0</v>
       </c>
       <c r="BW106" s="7" t="n">
-        <v>93982.96000000001</v>
+        <v>0</v>
       </c>
       <c r="BX106" s="7" t="n">
-        <v>118869.68</v>
+        <v>0</v>
       </c>
       <c r="BY106" s="7" t="n">
-        <v>67272.49000000001</v>
+        <v>0</v>
       </c>
       <c r="BZ106" s="7" t="n">
         <v>0</v>
@@ -45451,7 +45730,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>390005/000096/2021</t>
+          <t>170026/001374/2022</t>
         </is>
       </c>
       <c r="C107" s="14" t="inlineStr">
@@ -45460,16 +45739,16 @@
         </is>
       </c>
       <c r="D107" s="4" t="n">
-        <v>570</v>
+        <v>596</v>
       </c>
       <c r="E107" s="6" t="n">
-        <v>44613</v>
+        <v>44917</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>45183</v>
+        <v>45513</v>
       </c>
       <c r="G107" s="7" t="n">
-        <v>1052239.53</v>
+        <v>14782911.98</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
@@ -45478,23 +45757,23 @@
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>MARCUS PAULO</t>
+          <t>JAQUELINE PASTÓRIO</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr"/>
-      <c r="K107" s="12" t="inlineStr">
-        <is>
-          <t>MT</t>
+      <c r="K107" s="11" t="inlineStr">
+        <is>
+          <t>BX</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>Angra dos Reis</t>
         </is>
       </c>
       <c r="M107" s="4" t="inlineStr">
         <is>
-          <t>ABBM BRAGA</t>
+          <t>BARRA NOVA</t>
         </is>
       </c>
       <c r="N107" s="7" t="n">
@@ -45504,13 +45783,13 @@
         <v>0</v>
       </c>
       <c r="P107" s="7" t="n">
-        <v>1052239.53</v>
+        <v>14782911.98</v>
       </c>
       <c r="Q107" s="9" t="n">
-        <v>0.9562999999999999</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="R107" s="7" t="n">
-        <v>46004.38</v>
+        <v>1602655.58</v>
       </c>
       <c r="S107" s="7" t="n">
         <v>0</v>
@@ -45555,10 +45834,10 @@
         <v>0</v>
       </c>
       <c r="AG107" s="7" t="n">
-        <v>480649.82</v>
+        <v>0</v>
       </c>
       <c r="AH107" s="7" t="n">
-        <v>150863.84</v>
+        <v>0</v>
       </c>
       <c r="AI107" s="7" t="n">
         <v>0</v>
@@ -45588,19 +45867,19 @@
         <v>0</v>
       </c>
       <c r="AR107" s="7" t="n">
-        <v>0</v>
+        <v>499163.85</v>
       </c>
       <c r="AS107" s="7" t="n">
-        <v>0</v>
+        <v>1483218.6</v>
       </c>
       <c r="AT107" s="7" t="n">
-        <v>0</v>
+        <v>4482740.67</v>
       </c>
       <c r="AU107" s="7" t="n">
-        <v>374721.49</v>
+        <v>5107295.89</v>
       </c>
       <c r="AV107" s="7" t="n">
-        <v>0</v>
+        <v>1607837.39</v>
       </c>
       <c r="AW107" s="7" t="n">
         <v>0</v>
@@ -45735,7 +46014,7 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>170026/001374/2022</t>
+          <t>E-17/026/0056/2020</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
@@ -45744,16 +46023,16 @@
         </is>
       </c>
       <c r="D108" s="4" t="n">
-        <v>596</v>
+        <v>81</v>
       </c>
       <c r="E108" s="6" t="n">
-        <v>44917</v>
+        <v>43930</v>
       </c>
       <c r="F108" s="6" t="n">
-        <v>45513</v>
+        <v>44011</v>
       </c>
       <c r="G108" s="7" t="n">
-        <v>14782911.98</v>
+        <v>62980000</v>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
@@ -45762,7 +46041,7 @@
       </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
-          <t>JAQUELINE PASTÓRIO</t>
+          <t>ERICK HYLARIO</t>
         </is>
       </c>
       <c r="J108" s="4" t="inlineStr"/>
@@ -45773,12 +46052,12 @@
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>Angra dos Reis</t>
+          <t>Nova Iguaçu</t>
         </is>
       </c>
       <c r="M108" s="4" t="inlineStr">
         <is>
-          <t>BARRA NOVA</t>
+          <t>BIG FARM</t>
         </is>
       </c>
       <c r="N108" s="7" t="n">
@@ -45788,31 +46067,31 @@
         <v>0</v>
       </c>
       <c r="P108" s="7" t="n">
-        <v>14782911.98</v>
+        <v>0</v>
       </c>
       <c r="Q108" s="9" t="n">
-        <v>0.8915999999999999</v>
+        <v>0</v>
       </c>
       <c r="R108" s="7" t="n">
-        <v>1602655.58</v>
+        <v>0</v>
       </c>
       <c r="S108" s="7" t="n">
-        <v>0</v>
+        <v>27179207.94</v>
       </c>
       <c r="T108" s="7" t="n">
-        <v>0</v>
+        <v>6238798.8</v>
       </c>
       <c r="U108" s="7" t="n">
-        <v>0</v>
+        <v>9623973.800000001</v>
       </c>
       <c r="V108" s="7" t="n">
-        <v>0</v>
+        <v>6699374.99</v>
       </c>
       <c r="W108" s="7" t="n">
-        <v>0</v>
+        <v>9772059.779999999</v>
       </c>
       <c r="X108" s="7" t="n">
-        <v>0</v>
+        <v>3466584.69</v>
       </c>
       <c r="Y108" s="7" t="n">
         <v>0</v>
@@ -45872,19 +46151,19 @@
         <v>0</v>
       </c>
       <c r="AR108" s="7" t="n">
-        <v>499163.85</v>
+        <v>0</v>
       </c>
       <c r="AS108" s="7" t="n">
-        <v>1483218.6</v>
+        <v>0</v>
       </c>
       <c r="AT108" s="7" t="n">
-        <v>4482740.67</v>
+        <v>0</v>
       </c>
       <c r="AU108" s="7" t="n">
-        <v>5107295.89</v>
+        <v>0</v>
       </c>
       <c r="AV108" s="7" t="n">
-        <v>1607837.39</v>
+        <v>0</v>
       </c>
       <c r="AW108" s="7" t="n">
         <v>0</v>
@@ -46019,7 +46298,7 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>E-17/026/0056/2020</t>
+          <t>170026/000821/2021</t>
         </is>
       </c>
       <c r="C109" s="14" t="inlineStr">
@@ -46028,16 +46307,16 @@
         </is>
       </c>
       <c r="D109" s="4" t="n">
-        <v>81</v>
+        <v>1538</v>
       </c>
       <c r="E109" s="6" t="n">
-        <v>43930</v>
+        <v>44537</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>44011</v>
+        <v>46075</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>62980000</v>
+        <v>13554947.83</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
@@ -46046,57 +46325,57 @@
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>ERICK HYLARIO</t>
+          <t>IGOR CARNEIRO</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr"/>
-      <c r="K109" s="11" t="inlineStr">
-        <is>
-          <t>BX</t>
+      <c r="K109" s="12" t="inlineStr">
+        <is>
+          <t>MT</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
-          <t>Nova Iguaçu</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="M109" s="4" t="inlineStr">
         <is>
-          <t>BIG FARM</t>
+          <t>CARLETTI</t>
         </is>
       </c>
       <c r="N109" s="7" t="n">
-        <v>0</v>
+        <v>710964.03</v>
       </c>
       <c r="O109" s="7" t="n">
         <v>0</v>
       </c>
       <c r="P109" s="7" t="n">
-        <v>0</v>
+        <v>13554947.83</v>
       </c>
       <c r="Q109" s="9" t="n">
-        <v>0</v>
+        <v>0.9508</v>
       </c>
       <c r="R109" s="7" t="n">
-        <v>0</v>
+        <v>666441.27</v>
       </c>
       <c r="S109" s="7" t="n">
-        <v>27179207.94</v>
+        <v>0</v>
       </c>
       <c r="T109" s="7" t="n">
-        <v>6238798.8</v>
+        <v>0</v>
       </c>
       <c r="U109" s="7" t="n">
-        <v>9623973.800000001</v>
+        <v>0</v>
       </c>
       <c r="V109" s="7" t="n">
-        <v>6699374.99</v>
+        <v>0</v>
       </c>
       <c r="W109" s="7" t="n">
-        <v>9772059.779999999</v>
+        <v>0</v>
       </c>
       <c r="X109" s="7" t="n">
-        <v>3466584.69</v>
+        <v>0</v>
       </c>
       <c r="Y109" s="7" t="n">
         <v>0</v>
@@ -46114,37 +46393,37 @@
         <v>0</v>
       </c>
       <c r="AD109" s="7" t="n">
-        <v>0</v>
+        <v>7225.75</v>
       </c>
       <c r="AE109" s="7" t="n">
-        <v>0</v>
+        <v>1206875.16</v>
       </c>
       <c r="AF109" s="7" t="n">
-        <v>0</v>
+        <v>551463.38</v>
       </c>
       <c r="AG109" s="7" t="n">
-        <v>0</v>
+        <v>794160.66</v>
       </c>
       <c r="AH109" s="7" t="n">
-        <v>0</v>
+        <v>521754.01</v>
       </c>
       <c r="AI109" s="7" t="n">
-        <v>0</v>
+        <v>521159.55</v>
       </c>
       <c r="AJ109" s="7" t="n">
-        <v>0</v>
+        <v>969635.98</v>
       </c>
       <c r="AK109" s="7" t="n">
-        <v>0</v>
+        <v>433388.22</v>
       </c>
       <c r="AL109" s="7" t="n">
-        <v>0</v>
+        <v>428416.77</v>
       </c>
       <c r="AM109" s="7" t="n">
-        <v>0</v>
+        <v>676602.5600000001</v>
       </c>
       <c r="AN109" s="7" t="n">
-        <v>0</v>
+        <v>1351593.11</v>
       </c>
       <c r="AO109" s="7" t="n">
         <v>0</v>
@@ -46156,85 +46435,85 @@
         <v>0</v>
       </c>
       <c r="AR109" s="7" t="n">
-        <v>0</v>
+        <v>116253.42</v>
       </c>
       <c r="AS109" s="7" t="n">
-        <v>0</v>
+        <v>25420.39</v>
       </c>
       <c r="AT109" s="7" t="n">
-        <v>0</v>
+        <v>25029.21</v>
       </c>
       <c r="AU109" s="7" t="n">
-        <v>0</v>
+        <v>21733.94</v>
       </c>
       <c r="AV109" s="7" t="n">
-        <v>0</v>
+        <v>15071.37</v>
       </c>
       <c r="AW109" s="7" t="n">
-        <v>0</v>
+        <v>16492.16</v>
       </c>
       <c r="AX109" s="7" t="n">
-        <v>0</v>
+        <v>12502.02</v>
       </c>
       <c r="AY109" s="7" t="n">
-        <v>0</v>
+        <v>19489.13</v>
       </c>
       <c r="AZ109" s="7" t="n">
-        <v>0</v>
+        <v>329676.62</v>
       </c>
       <c r="BA109" s="7" t="n">
-        <v>0</v>
+        <v>783668.37</v>
       </c>
       <c r="BB109" s="7" t="n">
-        <v>0</v>
+        <v>27164.33</v>
       </c>
       <c r="BC109" s="7" t="n">
-        <v>0</v>
+        <v>24944.07</v>
       </c>
       <c r="BD109" s="7" t="n">
-        <v>0</v>
+        <v>14039.67</v>
       </c>
       <c r="BE109" s="7" t="n">
-        <v>0</v>
+        <v>252684.52</v>
       </c>
       <c r="BF109" s="7" t="n">
-        <v>0</v>
+        <v>119159.34</v>
       </c>
       <c r="BG109" s="7" t="n">
-        <v>0</v>
+        <v>370897.39</v>
       </c>
       <c r="BH109" s="7" t="n">
-        <v>0</v>
+        <v>712517.77</v>
       </c>
       <c r="BI109" s="7" t="n">
-        <v>0</v>
+        <v>528677.09</v>
       </c>
       <c r="BJ109" s="7" t="n">
-        <v>0</v>
+        <v>598849.04</v>
       </c>
       <c r="BK109" s="7" t="n">
-        <v>0</v>
+        <v>430454.97</v>
       </c>
       <c r="BL109" s="7" t="n">
-        <v>0</v>
+        <v>260173.15</v>
       </c>
       <c r="BM109" s="7" t="n">
-        <v>0</v>
+        <v>10469.41</v>
       </c>
       <c r="BN109" s="7" t="n">
         <v>0</v>
       </c>
       <c r="BO109" s="7" t="n">
-        <v>0</v>
+        <v>21239.88</v>
       </c>
       <c r="BP109" s="7" t="n">
-        <v>0</v>
+        <v>95373.96000000001</v>
       </c>
       <c r="BQ109" s="7" t="n">
-        <v>0</v>
+        <v>37461.02</v>
       </c>
       <c r="BR109" s="7" t="n">
-        <v>0</v>
+        <v>556889.17</v>
       </c>
       <c r="BS109" s="7" t="n">
         <v>0</v>
@@ -46303,7 +46582,7 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>170026/000821/2021</t>
+          <t>E-17/026/903/2019</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
@@ -46312,25 +46591,25 @@
         </is>
       </c>
       <c r="D110" s="4" t="n">
-        <v>1538</v>
+        <v>980</v>
       </c>
       <c r="E110" s="6" t="n">
-        <v>44537</v>
+        <v>44581</v>
       </c>
       <c r="F110" s="6" t="n">
-        <v>46075</v>
+        <v>45561</v>
       </c>
       <c r="G110" s="7" t="n">
-        <v>13554947.83</v>
+        <v>13677862.32</v>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>CONCLUÍDA</t>
+          <t>NÃO CONCLUÍDA</t>
         </is>
       </c>
       <c r="I110" s="4" t="inlineStr">
         <is>
-          <t>IGOR CARNEIRO</t>
+          <t>JAQUELINE PASTÓRIO</t>
         </is>
       </c>
       <c r="J110" s="4" t="inlineStr"/>
@@ -46350,19 +46629,19 @@
         </is>
       </c>
       <c r="N110" s="7" t="n">
-        <v>710964.03</v>
+        <v>0</v>
       </c>
       <c r="O110" s="7" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="7" t="n">
-        <v>13554947.83</v>
+        <v>13677862.32</v>
       </c>
       <c r="Q110" s="9" t="n">
-        <v>0.9508</v>
+        <v>0.0216</v>
       </c>
       <c r="R110" s="7" t="n">
-        <v>666441.27</v>
+        <v>13381760.45</v>
       </c>
       <c r="S110" s="7" t="n">
         <v>0</v>
@@ -46398,37 +46677,37 @@
         <v>0</v>
       </c>
       <c r="AD110" s="7" t="n">
-        <v>7225.75</v>
+        <v>0</v>
       </c>
       <c r="AE110" s="7" t="n">
-        <v>1206875.16</v>
+        <v>296101.87</v>
       </c>
       <c r="AF110" s="7" t="n">
-        <v>551463.38</v>
+        <v>0</v>
       </c>
       <c r="AG110" s="7" t="n">
-        <v>794160.66</v>
+        <v>0</v>
       </c>
       <c r="AH110" s="7" t="n">
-        <v>521754.01</v>
+        <v>0</v>
       </c>
       <c r="AI110" s="7" t="n">
-        <v>521159.55</v>
+        <v>0</v>
       </c>
       <c r="AJ110" s="7" t="n">
-        <v>969635.98</v>
+        <v>0</v>
       </c>
       <c r="AK110" s="7" t="n">
-        <v>433388.22</v>
+        <v>0</v>
       </c>
       <c r="AL110" s="7" t="n">
-        <v>428416.77</v>
+        <v>0</v>
       </c>
       <c r="AM110" s="7" t="n">
-        <v>676602.5600000001</v>
+        <v>0</v>
       </c>
       <c r="AN110" s="7" t="n">
-        <v>1351593.11</v>
+        <v>0</v>
       </c>
       <c r="AO110" s="7" t="n">
         <v>0</v>
@@ -46440,85 +46719,85 @@
         <v>0</v>
       </c>
       <c r="AR110" s="7" t="n">
-        <v>116253.42</v>
+        <v>0</v>
       </c>
       <c r="AS110" s="7" t="n">
-        <v>25420.39</v>
+        <v>0</v>
       </c>
       <c r="AT110" s="7" t="n">
-        <v>25029.21</v>
+        <v>0</v>
       </c>
       <c r="AU110" s="7" t="n">
-        <v>21733.94</v>
+        <v>0</v>
       </c>
       <c r="AV110" s="7" t="n">
-        <v>15071.37</v>
+        <v>0</v>
       </c>
       <c r="AW110" s="7" t="n">
-        <v>16492.16</v>
+        <v>0</v>
       </c>
       <c r="AX110" s="7" t="n">
-        <v>12502.02</v>
+        <v>0</v>
       </c>
       <c r="AY110" s="7" t="n">
-        <v>19489.13</v>
+        <v>0</v>
       </c>
       <c r="AZ110" s="7" t="n">
-        <v>329676.62</v>
+        <v>0</v>
       </c>
       <c r="BA110" s="7" t="n">
-        <v>783668.37</v>
+        <v>0</v>
       </c>
       <c r="BB110" s="7" t="n">
-        <v>27164.33</v>
+        <v>0</v>
       </c>
       <c r="BC110" s="7" t="n">
-        <v>24944.07</v>
+        <v>0</v>
       </c>
       <c r="BD110" s="7" t="n">
-        <v>14039.67</v>
+        <v>0</v>
       </c>
       <c r="BE110" s="7" t="n">
-        <v>252684.52</v>
+        <v>0</v>
       </c>
       <c r="BF110" s="7" t="n">
-        <v>119159.34</v>
+        <v>0</v>
       </c>
       <c r="BG110" s="7" t="n">
-        <v>370897.39</v>
+        <v>0</v>
       </c>
       <c r="BH110" s="7" t="n">
-        <v>712517.77</v>
+        <v>0</v>
       </c>
       <c r="BI110" s="7" t="n">
-        <v>528677.09</v>
+        <v>0</v>
       </c>
       <c r="BJ110" s="7" t="n">
-        <v>598849.04</v>
+        <v>0</v>
       </c>
       <c r="BK110" s="7" t="n">
-        <v>430454.97</v>
+        <v>0</v>
       </c>
       <c r="BL110" s="7" t="n">
-        <v>260173.15</v>
+        <v>0</v>
       </c>
       <c r="BM110" s="7" t="n">
-        <v>10469.41</v>
+        <v>0</v>
       </c>
       <c r="BN110" s="7" t="n">
         <v>0</v>
       </c>
       <c r="BO110" s="7" t="n">
-        <v>21239.88</v>
+        <v>0</v>
       </c>
       <c r="BP110" s="7" t="n">
-        <v>95373.96000000001</v>
+        <v>0</v>
       </c>
       <c r="BQ110" s="7" t="n">
-        <v>37461.02</v>
+        <v>0</v>
       </c>
       <c r="BR110" s="7" t="n">
-        <v>556889.17</v>
+        <v>0</v>
       </c>
       <c r="BS110" s="7" t="n">
         <v>0</v>
@@ -46587,7 +46866,7 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>E-17/026/903/2019</t>
+          <t>150001/012862/2022</t>
         </is>
       </c>
       <c r="C111" s="14" t="inlineStr">
@@ -46596,25 +46875,25 @@
         </is>
       </c>
       <c r="D111" s="4" t="n">
-        <v>980</v>
+        <v>603</v>
       </c>
       <c r="E111" s="6" t="n">
-        <v>44581</v>
+        <v>44872</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>45561</v>
+        <v>45475</v>
       </c>
       <c r="G111" s="7" t="n">
-        <v>13677862.32</v>
+        <v>56185153.92</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>NÃO CONCLUÍDA</t>
+          <t>CONCLUÍDA</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>JAQUELINE PASTÓRIO</t>
+          <t>AIMAR FILHO</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr"/>
@@ -46630,7 +46909,7 @@
       </c>
       <c r="M111" s="4" t="inlineStr">
         <is>
-          <t>CARLETTI</t>
+          <t>CONCREJATO</t>
         </is>
       </c>
       <c r="N111" s="7" t="n">
@@ -46640,13 +46919,13 @@
         <v>0</v>
       </c>
       <c r="P111" s="7" t="n">
-        <v>13677862.32</v>
+        <v>56185153.92</v>
       </c>
       <c r="Q111" s="9" t="n">
-        <v>0.0216</v>
+        <v>0.9765999999999999</v>
       </c>
       <c r="R111" s="7" t="n">
-        <v>13381760.45</v>
+        <v>1313090.52</v>
       </c>
       <c r="S111" s="7" t="n">
         <v>0</v>
@@ -46685,7 +46964,7 @@
         <v>0</v>
       </c>
       <c r="AE111" s="7" t="n">
-        <v>296101.87</v>
+        <v>0</v>
       </c>
       <c r="AF111" s="7" t="n">
         <v>0</v>
@@ -46715,64 +46994,64 @@
         <v>0</v>
       </c>
       <c r="AO111" s="7" t="n">
-        <v>0</v>
+        <v>4917768.98</v>
       </c>
       <c r="AP111" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AQ111" s="7" t="n">
-        <v>0</v>
+        <v>4084624.43</v>
       </c>
       <c r="AR111" s="7" t="n">
-        <v>0</v>
+        <v>2615258.13</v>
       </c>
       <c r="AS111" s="7" t="n">
-        <v>0</v>
+        <v>1996564.64</v>
       </c>
       <c r="AT111" s="7" t="n">
-        <v>0</v>
+        <v>3446190.41</v>
       </c>
       <c r="AU111" s="7" t="n">
-        <v>0</v>
+        <v>3298907.18</v>
       </c>
       <c r="AV111" s="7" t="n">
-        <v>0</v>
+        <v>1197688.75</v>
       </c>
       <c r="AW111" s="7" t="n">
-        <v>0</v>
+        <v>1419668.82</v>
       </c>
       <c r="AX111" s="7" t="n">
-        <v>0</v>
+        <v>2758314.48</v>
       </c>
       <c r="AY111" s="7" t="n">
-        <v>0</v>
+        <v>2881415.58</v>
       </c>
       <c r="AZ111" s="7" t="n">
-        <v>0</v>
+        <v>3900694.84</v>
       </c>
       <c r="BA111" s="7" t="n">
-        <v>0</v>
+        <v>5538821.25</v>
       </c>
       <c r="BB111" s="7" t="n">
-        <v>0</v>
+        <v>5714410.31</v>
       </c>
       <c r="BC111" s="7" t="n">
-        <v>0</v>
+        <v>2210832.53</v>
       </c>
       <c r="BD111" s="7" t="n">
-        <v>0</v>
+        <v>1969001.82</v>
       </c>
       <c r="BE111" s="7" t="n">
-        <v>0</v>
+        <v>2703342.32</v>
       </c>
       <c r="BF111" s="7" t="n">
-        <v>0</v>
+        <v>2217624.94</v>
       </c>
       <c r="BG111" s="7" t="n">
-        <v>0</v>
+        <v>419916.91</v>
       </c>
       <c r="BH111" s="7" t="n">
-        <v>0</v>
+        <v>1581017.08</v>
       </c>
       <c r="BI111" s="7" t="n">
         <v>0</v>
@@ -46871,7 +47150,7 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>150001/012862/2022</t>
+          <t>460001/000251/2023</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
@@ -46880,16 +47159,16 @@
         </is>
       </c>
       <c r="D112" s="4" t="n">
-        <v>603</v>
+        <v>219</v>
       </c>
       <c r="E112" s="6" t="n">
-        <v>44872</v>
+        <v>45034</v>
       </c>
       <c r="F112" s="6" t="n">
-        <v>45475</v>
+        <v>45253</v>
       </c>
       <c r="G112" s="7" t="n">
-        <v>56185153.92</v>
+        <v>16880240</v>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
@@ -46898,23 +47177,23 @@
       </c>
       <c r="I112" s="4" t="inlineStr">
         <is>
-          <t>AIMAR FILHO</t>
+          <t>JAQUELINE PASTÓRIO</t>
         </is>
       </c>
       <c r="J112" s="4" t="inlineStr"/>
-      <c r="K112" s="12" t="inlineStr">
-        <is>
-          <t>MT</t>
+      <c r="K112" s="10" t="inlineStr">
+        <is>
+          <t>NT</t>
         </is>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>Campos dos Goytacazes</t>
         </is>
       </c>
       <c r="M112" s="4" t="inlineStr">
         <is>
-          <t>CONCREJATO</t>
+          <t>DRV ENG.</t>
         </is>
       </c>
       <c r="N112" s="7" t="n">
@@ -46924,13 +47203,13 @@
         <v>0</v>
       </c>
       <c r="P112" s="7" t="n">
-        <v>56185153.92</v>
+        <v>16880240</v>
       </c>
       <c r="Q112" s="9" t="n">
-        <v>0.9765999999999999</v>
+        <v>0.773</v>
       </c>
       <c r="R112" s="7" t="n">
-        <v>1313090.52</v>
+        <v>3831703.46</v>
       </c>
       <c r="S112" s="7" t="n">
         <v>0</v>
@@ -46978,85 +47257,85 @@
         <v>0</v>
       </c>
       <c r="AH112" s="7" t="n">
-        <v>0</v>
+        <v>5595220.28</v>
       </c>
       <c r="AI112" s="7" t="n">
-        <v>0</v>
+        <v>4766337.5</v>
       </c>
       <c r="AJ112" s="7" t="n">
-        <v>0</v>
+        <v>1606580.64</v>
       </c>
       <c r="AK112" s="7" t="n">
-        <v>0</v>
+        <v>679932.12</v>
       </c>
       <c r="AL112" s="7" t="n">
-        <v>0</v>
+        <v>194089.8</v>
       </c>
       <c r="AM112" s="7" t="n">
-        <v>0</v>
+        <v>206376.2</v>
       </c>
       <c r="AN112" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AO112" s="7" t="n">
-        <v>4917768.98</v>
+        <v>0</v>
       </c>
       <c r="AP112" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AQ112" s="7" t="n">
-        <v>4084624.43</v>
+        <v>0</v>
       </c>
       <c r="AR112" s="7" t="n">
-        <v>2615258.13</v>
+        <v>0</v>
       </c>
       <c r="AS112" s="7" t="n">
-        <v>1996564.64</v>
+        <v>0</v>
       </c>
       <c r="AT112" s="7" t="n">
-        <v>3446190.41</v>
+        <v>0</v>
       </c>
       <c r="AU112" s="7" t="n">
-        <v>3298907.18</v>
+        <v>0</v>
       </c>
       <c r="AV112" s="7" t="n">
-        <v>1197688.75</v>
+        <v>0</v>
       </c>
       <c r="AW112" s="7" t="n">
-        <v>1419668.82</v>
+        <v>0</v>
       </c>
       <c r="AX112" s="7" t="n">
-        <v>2758314.48</v>
+        <v>0</v>
       </c>
       <c r="AY112" s="7" t="n">
-        <v>2881415.58</v>
+        <v>0</v>
       </c>
       <c r="AZ112" s="7" t="n">
-        <v>3900694.84</v>
+        <v>0</v>
       </c>
       <c r="BA112" s="7" t="n">
-        <v>5538821.25</v>
+        <v>0</v>
       </c>
       <c r="BB112" s="7" t="n">
-        <v>5714410.31</v>
+        <v>0</v>
       </c>
       <c r="BC112" s="7" t="n">
-        <v>2210832.53</v>
+        <v>0</v>
       </c>
       <c r="BD112" s="7" t="n">
-        <v>1969001.82</v>
+        <v>0</v>
       </c>
       <c r="BE112" s="7" t="n">
-        <v>2703342.32</v>
+        <v>0</v>
       </c>
       <c r="BF112" s="7" t="n">
-        <v>2217624.94</v>
+        <v>0</v>
       </c>
       <c r="BG112" s="7" t="n">
-        <v>419916.91</v>
+        <v>0</v>
       </c>
       <c r="BH112" s="7" t="n">
-        <v>1581017.08</v>
+        <v>0</v>
       </c>
       <c r="BI112" s="7" t="n">
         <v>0</v>
@@ -47155,7 +47434,7 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>460001/000251/2023</t>
+          <t>170026/001228/2022</t>
         </is>
       </c>
       <c r="C113" s="14" t="inlineStr">
@@ -47164,16 +47443,16 @@
         </is>
       </c>
       <c r="D113" s="4" t="n">
-        <v>219</v>
+        <v>765</v>
       </c>
       <c r="E113" s="6" t="n">
-        <v>45034</v>
+        <v>44804</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>45253</v>
+        <v>45569</v>
       </c>
       <c r="G113" s="7" t="n">
-        <v>16880240</v>
+        <v>6519257.05</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
@@ -47186,14 +47465,14 @@
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr"/>
-      <c r="K113" s="10" t="inlineStr">
-        <is>
-          <t>NT</t>
+      <c r="K113" s="11" t="inlineStr">
+        <is>
+          <t>BX</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
-          <t>Campos dos Goytacazes</t>
+          <t>Mangaratiba</t>
         </is>
       </c>
       <c r="M113" s="4" t="inlineStr">
@@ -47208,13 +47487,13 @@
         <v>0</v>
       </c>
       <c r="P113" s="7" t="n">
-        <v>16880240</v>
+        <v>6519257.05</v>
       </c>
       <c r="Q113" s="9" t="n">
-        <v>0.773</v>
+        <v>0.8787</v>
       </c>
       <c r="R113" s="7" t="n">
-        <v>3831703.46</v>
+        <v>791016.1899999999</v>
       </c>
       <c r="S113" s="7" t="n">
         <v>0</v>
@@ -47262,25 +47541,25 @@
         <v>0</v>
       </c>
       <c r="AH113" s="7" t="n">
-        <v>5595220.28</v>
+        <v>0</v>
       </c>
       <c r="AI113" s="7" t="n">
-        <v>4766337.5</v>
+        <v>0</v>
       </c>
       <c r="AJ113" s="7" t="n">
-        <v>1606580.64</v>
+        <v>0</v>
       </c>
       <c r="AK113" s="7" t="n">
-        <v>679932.12</v>
+        <v>0</v>
       </c>
       <c r="AL113" s="7" t="n">
-        <v>194089.8</v>
+        <v>0</v>
       </c>
       <c r="AM113" s="7" t="n">
-        <v>206376.2</v>
+        <v>538825.27</v>
       </c>
       <c r="AN113" s="7" t="n">
-        <v>0</v>
+        <v>2681512.23</v>
       </c>
       <c r="AO113" s="7" t="n">
         <v>0</v>
@@ -47289,7 +47568,7 @@
         <v>0</v>
       </c>
       <c r="AQ113" s="7" t="n">
-        <v>0</v>
+        <v>2507903.22</v>
       </c>
       <c r="AR113" s="7" t="n">
         <v>0</v>
@@ -47439,7 +47718,7 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>170026/001228/2022</t>
+          <t>460001/000779/2023</t>
         </is>
       </c>
       <c r="C114" s="14" t="inlineStr">
@@ -47448,16 +47727,16 @@
         </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>765</v>
+        <v>540</v>
       </c>
       <c r="E114" s="6" t="n">
-        <v>44804</v>
+        <v>45189</v>
       </c>
       <c r="F114" s="6" t="n">
-        <v>45569</v>
+        <v>45729</v>
       </c>
       <c r="G114" s="7" t="n">
-        <v>6519257.05</v>
+        <v>48302952.43</v>
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
@@ -47466,39 +47745,39 @@
       </c>
       <c r="I114" s="4" t="inlineStr">
         <is>
-          <t>JAQUELINE PASTÓRIO</t>
+          <t>ERICK HYLARIO</t>
         </is>
       </c>
       <c r="J114" s="4" t="inlineStr"/>
-      <c r="K114" s="11" t="inlineStr">
-        <is>
-          <t>BX</t>
+      <c r="K114" s="10" t="inlineStr">
+        <is>
+          <t>NT</t>
         </is>
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t>Mangaratiba</t>
+          <t>Petrópolis</t>
         </is>
       </c>
       <c r="M114" s="4" t="inlineStr">
         <is>
-          <t>DRV ENG.</t>
+          <t>ENGEPRAT</t>
         </is>
       </c>
       <c r="N114" s="7" t="n">
-        <v>0</v>
+        <v>6549937.15</v>
       </c>
       <c r="O114" s="7" t="n">
         <v>0</v>
       </c>
       <c r="P114" s="7" t="n">
-        <v>6519257.05</v>
+        <v>48302952.43</v>
       </c>
       <c r="Q114" s="9" t="n">
-        <v>0.8787</v>
+        <v>0.9493</v>
       </c>
       <c r="R114" s="7" t="n">
-        <v>791016.1899999999</v>
+        <v>2449729.13</v>
       </c>
       <c r="S114" s="7" t="n">
         <v>0</v>
@@ -47561,10 +47840,10 @@
         <v>0</v>
       </c>
       <c r="AM114" s="7" t="n">
-        <v>538825.27</v>
+        <v>0</v>
       </c>
       <c r="AN114" s="7" t="n">
-        <v>2681512.23</v>
+        <v>0</v>
       </c>
       <c r="AO114" s="7" t="n">
         <v>0</v>
@@ -47573,7 +47852,7 @@
         <v>0</v>
       </c>
       <c r="AQ114" s="7" t="n">
-        <v>2507903.22</v>
+        <v>0</v>
       </c>
       <c r="AR114" s="7" t="n">
         <v>0</v>
@@ -47600,58 +47879,58 @@
         <v>0</v>
       </c>
       <c r="AZ114" s="7" t="n">
-        <v>0</v>
+        <v>530046.99</v>
       </c>
       <c r="BA114" s="7" t="n">
-        <v>0</v>
+        <v>3744825.03</v>
       </c>
       <c r="BB114" s="7" t="n">
-        <v>0</v>
+        <v>4587347.48</v>
       </c>
       <c r="BC114" s="7" t="n">
-        <v>0</v>
+        <v>2755200.28</v>
       </c>
       <c r="BD114" s="7" t="n">
-        <v>0</v>
+        <v>3749782.71</v>
       </c>
       <c r="BE114" s="7" t="n">
-        <v>0</v>
+        <v>4084991.2</v>
       </c>
       <c r="BF114" s="7" t="n">
-        <v>0</v>
+        <v>2697356.03</v>
       </c>
       <c r="BG114" s="7" t="n">
-        <v>0</v>
+        <v>2306916.13</v>
       </c>
       <c r="BH114" s="7" t="n">
-        <v>0</v>
+        <v>4379824.62</v>
       </c>
       <c r="BI114" s="7" t="n">
-        <v>0</v>
+        <v>2501809.42</v>
       </c>
       <c r="BJ114" s="7" t="n">
-        <v>0</v>
+        <v>2500299.87</v>
       </c>
       <c r="BK114" s="7" t="n">
-        <v>0</v>
+        <v>1747578.28</v>
       </c>
       <c r="BL114" s="7" t="n">
-        <v>0</v>
+        <v>1273341.59</v>
       </c>
       <c r="BM114" s="7" t="n">
-        <v>0</v>
+        <v>870280.71</v>
       </c>
       <c r="BN114" s="7" t="n">
-        <v>0</v>
+        <v>1578681.69</v>
       </c>
       <c r="BO114" s="7" t="n">
-        <v>0</v>
+        <v>5763188.08</v>
       </c>
       <c r="BP114" s="7" t="n">
-        <v>0</v>
+        <v>741529.04</v>
       </c>
       <c r="BQ114" s="7" t="n">
-        <v>0</v>
+        <v>45220.03</v>
       </c>
       <c r="BR114" s="7" t="n">
         <v>0</v>
@@ -47723,7 +48002,7 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>460001/000779/2023</t>
+          <t>170026/001757/2021</t>
         </is>
       </c>
       <c r="C115" s="14" t="inlineStr">
@@ -47732,20 +48011,20 @@
         </is>
       </c>
       <c r="D115" s="4" t="n">
-        <v>540</v>
+        <v>468</v>
       </c>
       <c r="E115" s="6" t="n">
-        <v>45189</v>
+        <v>44791</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>45729</v>
+        <v>45259</v>
       </c>
       <c r="G115" s="7" t="n">
-        <v>48302952.43</v>
+        <v>3615856.15</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>CONCLUÍDA</t>
+          <t>NÃO CONCLUÍDA</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
@@ -47754,35 +48033,35 @@
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr"/>
-      <c r="K115" s="10" t="inlineStr">
-        <is>
-          <t>NT</t>
+      <c r="K115" s="12" t="inlineStr">
+        <is>
+          <t>MT</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
-          <t>Petrópolis</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="M115" s="4" t="inlineStr">
         <is>
-          <t>ENGEPRAT</t>
+          <t>MPE</t>
         </is>
       </c>
       <c r="N115" s="7" t="n">
-        <v>6549937.15</v>
+        <v>0</v>
       </c>
       <c r="O115" s="7" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="7" t="n">
-        <v>48302952.43</v>
+        <v>3615856.15</v>
       </c>
       <c r="Q115" s="9" t="n">
-        <v>0.9493</v>
+        <v>0.0707</v>
       </c>
       <c r="R115" s="7" t="n">
-        <v>2449729.13</v>
+        <v>3360171.68</v>
       </c>
       <c r="S115" s="7" t="n">
         <v>0</v>
@@ -47842,13 +48121,13 @@
         <v>0</v>
       </c>
       <c r="AL115" s="7" t="n">
-        <v>0</v>
+        <v>3879.08</v>
       </c>
       <c r="AM115" s="7" t="n">
-        <v>0</v>
+        <v>4074.61</v>
       </c>
       <c r="AN115" s="7" t="n">
-        <v>0</v>
+        <v>17364.98</v>
       </c>
       <c r="AO115" s="7" t="n">
         <v>0</v>
@@ -47863,79 +48142,79 @@
         <v>0</v>
       </c>
       <c r="AS115" s="7" t="n">
-        <v>0</v>
+        <v>19750.62</v>
       </c>
       <c r="AT115" s="7" t="n">
-        <v>0</v>
+        <v>88980.25</v>
       </c>
       <c r="AU115" s="7" t="n">
-        <v>0</v>
+        <v>20906.54</v>
       </c>
       <c r="AV115" s="7" t="n">
-        <v>0</v>
+        <v>16695.77</v>
       </c>
       <c r="AW115" s="7" t="n">
-        <v>0</v>
+        <v>42691.31</v>
       </c>
       <c r="AX115" s="7" t="n">
-        <v>0</v>
+        <v>16197.36</v>
       </c>
       <c r="AY115" s="7" t="n">
-        <v>0</v>
+        <v>6051.68</v>
       </c>
       <c r="AZ115" s="7" t="n">
-        <v>530046.99</v>
+        <v>15072.3</v>
       </c>
       <c r="BA115" s="7" t="n">
-        <v>3744825.03</v>
+        <v>4019.97</v>
       </c>
       <c r="BB115" s="7" t="n">
-        <v>4587347.48</v>
+        <v>0</v>
       </c>
       <c r="BC115" s="7" t="n">
-        <v>2755200.28</v>
+        <v>0</v>
       </c>
       <c r="BD115" s="7" t="n">
-        <v>3749782.71</v>
+        <v>0</v>
       </c>
       <c r="BE115" s="7" t="n">
-        <v>4084991.2</v>
+        <v>0</v>
       </c>
       <c r="BF115" s="7" t="n">
-        <v>2697356.03</v>
+        <v>0</v>
       </c>
       <c r="BG115" s="7" t="n">
-        <v>2306916.13</v>
+        <v>0</v>
       </c>
       <c r="BH115" s="7" t="n">
-        <v>4379824.62</v>
+        <v>0</v>
       </c>
       <c r="BI115" s="7" t="n">
-        <v>2501809.42</v>
+        <v>0</v>
       </c>
       <c r="BJ115" s="7" t="n">
-        <v>2500299.87</v>
+        <v>0</v>
       </c>
       <c r="BK115" s="7" t="n">
-        <v>1747578.28</v>
+        <v>0</v>
       </c>
       <c r="BL115" s="7" t="n">
-        <v>1273341.59</v>
+        <v>0</v>
       </c>
       <c r="BM115" s="7" t="n">
-        <v>870280.71</v>
+        <v>0</v>
       </c>
       <c r="BN115" s="7" t="n">
-        <v>1578681.69</v>
+        <v>0</v>
       </c>
       <c r="BO115" s="7" t="n">
-        <v>5763188.08</v>
+        <v>0</v>
       </c>
       <c r="BP115" s="7" t="n">
-        <v>741529.04</v>
+        <v>0</v>
       </c>
       <c r="BQ115" s="7" t="n">
-        <v>45220.03</v>
+        <v>0</v>
       </c>
       <c r="BR115" s="7" t="n">
         <v>0</v>
@@ -48007,7 +48286,7 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>170026/001757/2021</t>
+          <t>170026/001756/2021</t>
         </is>
       </c>
       <c r="C116" s="14" t="inlineStr">
@@ -48016,16 +48295,16 @@
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>468</v>
+        <v>888</v>
       </c>
       <c r="E116" s="6" t="n">
-        <v>44791</v>
+        <v>44538</v>
       </c>
       <c r="F116" s="6" t="n">
-        <v>45259</v>
+        <v>45426</v>
       </c>
       <c r="G116" s="7" t="n">
-        <v>3615856.15</v>
+        <v>24165422.12</v>
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
@@ -48060,13 +48339,13 @@
         <v>0</v>
       </c>
       <c r="P116" s="7" t="n">
-        <v>3615856.15</v>
+        <v>24165422.12</v>
       </c>
       <c r="Q116" s="9" t="n">
-        <v>0.0707</v>
+        <v>0.3475</v>
       </c>
       <c r="R116" s="7" t="n">
-        <v>3360171.68</v>
+        <v>15767014.89</v>
       </c>
       <c r="S116" s="7" t="n">
         <v>0</v>
@@ -48102,40 +48381,40 @@
         <v>0</v>
       </c>
       <c r="AD116" s="7" t="n">
-        <v>0</v>
+        <v>5630.73</v>
       </c>
       <c r="AE116" s="7" t="n">
-        <v>0</v>
+        <v>85270.45</v>
       </c>
       <c r="AF116" s="7" t="n">
-        <v>0</v>
+        <v>183497.2</v>
       </c>
       <c r="AG116" s="7" t="n">
-        <v>0</v>
+        <v>269577.72</v>
       </c>
       <c r="AH116" s="7" t="n">
-        <v>0</v>
+        <v>270437.77</v>
       </c>
       <c r="AI116" s="7" t="n">
-        <v>0</v>
+        <v>273799.2</v>
       </c>
       <c r="AJ116" s="7" t="n">
-        <v>0</v>
+        <v>371021.51</v>
       </c>
       <c r="AK116" s="7" t="n">
-        <v>0</v>
+        <v>954612.39</v>
       </c>
       <c r="AL116" s="7" t="n">
-        <v>3879.08</v>
+        <v>656379.84</v>
       </c>
       <c r="AM116" s="7" t="n">
-        <v>4074.61</v>
+        <v>317135.78</v>
       </c>
       <c r="AN116" s="7" t="n">
-        <v>17364.98</v>
+        <v>161899.02</v>
       </c>
       <c r="AO116" s="7" t="n">
-        <v>0</v>
+        <v>367581.73</v>
       </c>
       <c r="AP116" s="7" t="n">
         <v>0</v>
@@ -48144,34 +48423,34 @@
         <v>0</v>
       </c>
       <c r="AR116" s="7" t="n">
-        <v>0</v>
+        <v>578603.54</v>
       </c>
       <c r="AS116" s="7" t="n">
-        <v>19750.62</v>
+        <v>182465.36</v>
       </c>
       <c r="AT116" s="7" t="n">
-        <v>88980.25</v>
+        <v>205227.45</v>
       </c>
       <c r="AU116" s="7" t="n">
-        <v>20906.54</v>
+        <v>102363.86</v>
       </c>
       <c r="AV116" s="7" t="n">
-        <v>16695.77</v>
+        <v>82676.64999999999</v>
       </c>
       <c r="AW116" s="7" t="n">
-        <v>42691.31</v>
+        <v>86196.17</v>
       </c>
       <c r="AX116" s="7" t="n">
-        <v>16197.36</v>
+        <v>133423.93</v>
       </c>
       <c r="AY116" s="7" t="n">
-        <v>6051.68</v>
+        <v>33929.2</v>
       </c>
       <c r="AZ116" s="7" t="n">
-        <v>15072.3</v>
+        <v>1505821.47</v>
       </c>
       <c r="BA116" s="7" t="n">
-        <v>4019.97</v>
+        <v>1570856.26</v>
       </c>
       <c r="BB116" s="7" t="n">
         <v>0</v>
@@ -48291,7 +48570,7 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>170026/001756/2021</t>
+          <t>330018/000566/2021</t>
         </is>
       </c>
       <c r="C117" s="14" t="inlineStr">
@@ -48300,41 +48579,41 @@
         </is>
       </c>
       <c r="D117" s="4" t="n">
-        <v>888</v>
+        <v>757</v>
       </c>
       <c r="E117" s="6" t="n">
-        <v>44538</v>
+        <v>44719</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>45426</v>
+        <v>45476</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>24165422.12</v>
+        <v>14995089.28</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>NÃO CONCLUÍDA</t>
+          <t>CONCLUÍDA</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>ERICK HYLARIO</t>
+          <t>GISELLE G. FONSECA</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr"/>
-      <c r="K117" s="12" t="inlineStr">
-        <is>
-          <t>MT</t>
+      <c r="K117" s="11" t="inlineStr">
+        <is>
+          <t>BX</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>Japeri</t>
         </is>
       </c>
       <c r="M117" s="4" t="inlineStr">
         <is>
-          <t>MPE</t>
+          <t>OMEGA</t>
         </is>
       </c>
       <c r="N117" s="7" t="n">
@@ -48344,13 +48623,13 @@
         <v>0</v>
       </c>
       <c r="P117" s="7" t="n">
-        <v>24165422.12</v>
+        <v>14995089.28</v>
       </c>
       <c r="Q117" s="9" t="n">
-        <v>0.3475</v>
+        <v>0.9994</v>
       </c>
       <c r="R117" s="7" t="n">
-        <v>15767014.89</v>
+        <v>9530.83</v>
       </c>
       <c r="S117" s="7" t="n">
         <v>0</v>
@@ -48386,91 +48665,91 @@
         <v>0</v>
       </c>
       <c r="AD117" s="7" t="n">
-        <v>5630.73</v>
+        <v>0</v>
       </c>
       <c r="AE117" s="7" t="n">
-        <v>85270.45</v>
+        <v>0</v>
       </c>
       <c r="AF117" s="7" t="n">
-        <v>183497.2</v>
+        <v>0</v>
       </c>
       <c r="AG117" s="7" t="n">
-        <v>269577.72</v>
+        <v>0</v>
       </c>
       <c r="AH117" s="7" t="n">
-        <v>270437.77</v>
+        <v>0</v>
       </c>
       <c r="AI117" s="7" t="n">
-        <v>273799.2</v>
+        <v>0</v>
       </c>
       <c r="AJ117" s="7" t="n">
-        <v>371021.51</v>
+        <v>906377.1</v>
       </c>
       <c r="AK117" s="7" t="n">
-        <v>954612.39</v>
+        <v>0</v>
       </c>
       <c r="AL117" s="7" t="n">
-        <v>656379.84</v>
+        <v>404014.96</v>
       </c>
       <c r="AM117" s="7" t="n">
-        <v>317135.78</v>
+        <v>0</v>
       </c>
       <c r="AN117" s="7" t="n">
-        <v>161899.02</v>
+        <v>1077897.62</v>
       </c>
       <c r="AO117" s="7" t="n">
-        <v>367581.73</v>
+        <v>966233.6</v>
       </c>
       <c r="AP117" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AQ117" s="7" t="n">
-        <v>0</v>
+        <v>530099.8100000001</v>
       </c>
       <c r="AR117" s="7" t="n">
-        <v>578603.54</v>
+        <v>0</v>
       </c>
       <c r="AS117" s="7" t="n">
-        <v>182465.36</v>
+        <v>0</v>
       </c>
       <c r="AT117" s="7" t="n">
-        <v>205227.45</v>
+        <v>684869.85</v>
       </c>
       <c r="AU117" s="7" t="n">
-        <v>102363.86</v>
+        <v>5687199.09</v>
       </c>
       <c r="AV117" s="7" t="n">
-        <v>82676.64999999999</v>
+        <v>1674842.39</v>
       </c>
       <c r="AW117" s="7" t="n">
-        <v>86196.17</v>
+        <v>541001.23</v>
       </c>
       <c r="AX117" s="7" t="n">
-        <v>133423.93</v>
+        <v>126807.47</v>
       </c>
       <c r="AY117" s="7" t="n">
-        <v>33929.2</v>
+        <v>146131.83</v>
       </c>
       <c r="AZ117" s="7" t="n">
-        <v>1505821.47</v>
+        <v>146617.42</v>
       </c>
       <c r="BA117" s="7" t="n">
-        <v>1570856.26</v>
+        <v>146617.42</v>
       </c>
       <c r="BB117" s="7" t="n">
-        <v>0</v>
+        <v>314540.25</v>
       </c>
       <c r="BC117" s="7" t="n">
-        <v>0</v>
+        <v>76060.21000000001</v>
       </c>
       <c r="BD117" s="7" t="n">
-        <v>0</v>
+        <v>60941.37</v>
       </c>
       <c r="BE117" s="7" t="n">
-        <v>0</v>
+        <v>473175.5</v>
       </c>
       <c r="BF117" s="7" t="n">
-        <v>0</v>
+        <v>1022166.32</v>
       </c>
       <c r="BG117" s="7" t="n">
         <v>0</v>
@@ -48575,7 +48854,7 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>330018/000566/2021</t>
+          <t>330018/000981/2021</t>
         </is>
       </c>
       <c r="C118" s="14" t="inlineStr">
@@ -48584,16 +48863,16 @@
         </is>
       </c>
       <c r="D118" s="4" t="n">
-        <v>757</v>
+        <v>-196</v>
       </c>
       <c r="E118" s="6" t="n">
-        <v>44719</v>
+        <v>45497</v>
       </c>
       <c r="F118" s="6" t="n">
-        <v>45476</v>
+        <v>45301</v>
       </c>
       <c r="G118" s="7" t="n">
-        <v>14995089.28</v>
+        <v>15078640.21</v>
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
@@ -48602,18 +48881,18 @@
       </c>
       <c r="I118" s="4" t="inlineStr">
         <is>
-          <t>GISELLE G. FONSECA</t>
+          <t>JAQUELINE PASTÓRIO</t>
         </is>
       </c>
       <c r="J118" s="4" t="inlineStr"/>
-      <c r="K118" s="11" t="inlineStr">
-        <is>
-          <t>BX</t>
+      <c r="K118" s="10" t="inlineStr">
+        <is>
+          <t>NT</t>
         </is>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>Japeri</t>
+          <t>Nova Friburgo</t>
         </is>
       </c>
       <c r="M118" s="4" t="inlineStr">
@@ -48628,13 +48907,13 @@
         <v>0</v>
       </c>
       <c r="P118" s="7" t="n">
-        <v>14995089.28</v>
+        <v>15078640.21</v>
       </c>
       <c r="Q118" s="9" t="n">
-        <v>0.9994</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="R118" s="7" t="n">
-        <v>9530.83</v>
+        <v>418357.84</v>
       </c>
       <c r="S118" s="7" t="n">
         <v>0</v>
@@ -48688,73 +48967,73 @@
         <v>0</v>
       </c>
       <c r="AJ118" s="7" t="n">
-        <v>906377.1</v>
+        <v>0</v>
       </c>
       <c r="AK118" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AL118" s="7" t="n">
-        <v>404014.96</v>
+        <v>0</v>
       </c>
       <c r="AM118" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AN118" s="7" t="n">
-        <v>1077897.62</v>
+        <v>1333049.52</v>
       </c>
       <c r="AO118" s="7" t="n">
-        <v>966233.6</v>
+        <v>858093.92</v>
       </c>
       <c r="AP118" s="7" t="n">
-        <v>0</v>
+        <v>826667.6899999999</v>
       </c>
       <c r="AQ118" s="7" t="n">
-        <v>530099.8100000001</v>
+        <v>1972999.74</v>
       </c>
       <c r="AR118" s="7" t="n">
-        <v>0</v>
+        <v>1495567.39</v>
       </c>
       <c r="AS118" s="7" t="n">
-        <v>0</v>
+        <v>1569024.42</v>
       </c>
       <c r="AT118" s="7" t="n">
-        <v>684869.85</v>
+        <v>264400.36</v>
       </c>
       <c r="AU118" s="7" t="n">
-        <v>5687199.09</v>
+        <v>598937.96</v>
       </c>
       <c r="AV118" s="7" t="n">
-        <v>1674842.39</v>
+        <v>2639504.72</v>
       </c>
       <c r="AW118" s="7" t="n">
-        <v>541001.23</v>
+        <v>845829.28</v>
       </c>
       <c r="AX118" s="7" t="n">
-        <v>126807.47</v>
+        <v>505241.22</v>
       </c>
       <c r="AY118" s="7" t="n">
-        <v>146131.83</v>
+        <v>10772.04</v>
       </c>
       <c r="AZ118" s="7" t="n">
-        <v>146617.42</v>
+        <v>1740193.73</v>
       </c>
       <c r="BA118" s="7" t="n">
-        <v>146617.42</v>
+        <v>0</v>
       </c>
       <c r="BB118" s="7" t="n">
-        <v>314540.25</v>
+        <v>0</v>
       </c>
       <c r="BC118" s="7" t="n">
-        <v>76060.21000000001</v>
+        <v>0</v>
       </c>
       <c r="BD118" s="7" t="n">
-        <v>60941.37</v>
+        <v>0</v>
       </c>
       <c r="BE118" s="7" t="n">
-        <v>473175.5</v>
+        <v>0</v>
       </c>
       <c r="BF118" s="7" t="n">
-        <v>1022166.32</v>
+        <v>0</v>
       </c>
       <c r="BG118" s="7" t="n">
         <v>0</v>
@@ -48859,7 +49138,7 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>330018/000981/2021</t>
+          <t>170026/003470/2021</t>
         </is>
       </c>
       <c r="C119" s="14" t="inlineStr">
@@ -48868,16 +49147,16 @@
         </is>
       </c>
       <c r="D119" s="4" t="n">
-        <v>-196</v>
+        <v>1298</v>
       </c>
       <c r="E119" s="6" t="n">
-        <v>45497</v>
+        <v>44638</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>45301</v>
+        <v>45936</v>
       </c>
       <c r="G119" s="7" t="n">
-        <v>15078640.21</v>
+        <v>24590858.27</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
@@ -48886,39 +49165,39 @@
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>JAQUELINE PASTÓRIO</t>
+          <t>ERICK HYLARIO</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr"/>
-      <c r="K119" s="10" t="inlineStr">
-        <is>
-          <t>NT</t>
+      <c r="K119" s="12" t="inlineStr">
+        <is>
+          <t>MT</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
-          <t>Nova Friburgo</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="M119" s="4" t="inlineStr">
         <is>
-          <t>OMEGA</t>
+          <t>PETROPUMP</t>
         </is>
       </c>
       <c r="N119" s="7" t="n">
-        <v>0</v>
+        <v>1082086.63</v>
       </c>
       <c r="O119" s="7" t="n">
         <v>0</v>
       </c>
       <c r="P119" s="7" t="n">
-        <v>15078640.21</v>
+        <v>24590858.27</v>
       </c>
       <c r="Q119" s="9" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="R119" s="7" t="n">
-        <v>418357.84</v>
+        <v>2665219.75</v>
       </c>
       <c r="S119" s="7" t="n">
         <v>0</v>
@@ -48963,94 +49242,94 @@
         <v>0</v>
       </c>
       <c r="AG119" s="7" t="n">
-        <v>0</v>
+        <v>821885</v>
       </c>
       <c r="AH119" s="7" t="n">
-        <v>0</v>
+        <v>666034.7</v>
       </c>
       <c r="AI119" s="7" t="n">
-        <v>0</v>
+        <v>1095907.96</v>
       </c>
       <c r="AJ119" s="7" t="n">
-        <v>0</v>
+        <v>1222093.58</v>
       </c>
       <c r="AK119" s="7" t="n">
-        <v>0</v>
+        <v>2272889.86</v>
       </c>
       <c r="AL119" s="7" t="n">
-        <v>0</v>
+        <v>1932781.91</v>
       </c>
       <c r="AM119" s="7" t="n">
-        <v>0</v>
+        <v>1242290.54</v>
       </c>
       <c r="AN119" s="7" t="n">
-        <v>1333049.52</v>
+        <v>2722433.3</v>
       </c>
       <c r="AO119" s="7" t="n">
-        <v>858093.92</v>
+        <v>405050.42</v>
       </c>
       <c r="AP119" s="7" t="n">
-        <v>826667.6899999999</v>
+        <v>0</v>
       </c>
       <c r="AQ119" s="7" t="n">
-        <v>1972999.74</v>
+        <v>0</v>
       </c>
       <c r="AR119" s="7" t="n">
-        <v>1495567.39</v>
+        <v>1642646.17</v>
       </c>
       <c r="AS119" s="7" t="n">
-        <v>1569024.42</v>
+        <v>0</v>
       </c>
       <c r="AT119" s="7" t="n">
-        <v>264400.36</v>
+        <v>0</v>
       </c>
       <c r="AU119" s="7" t="n">
-        <v>598937.96</v>
+        <v>806289.21</v>
       </c>
       <c r="AV119" s="7" t="n">
-        <v>2639504.72</v>
+        <v>242831.56</v>
       </c>
       <c r="AW119" s="7" t="n">
-        <v>845829.28</v>
+        <v>0</v>
       </c>
       <c r="AX119" s="7" t="n">
-        <v>505241.22</v>
+        <v>0</v>
       </c>
       <c r="AY119" s="7" t="n">
-        <v>10772.04</v>
+        <v>0</v>
       </c>
       <c r="AZ119" s="7" t="n">
-        <v>1740193.73</v>
+        <v>2616751.77</v>
       </c>
       <c r="BA119" s="7" t="n">
-        <v>0</v>
+        <v>1471882.58</v>
       </c>
       <c r="BB119" s="7" t="n">
-        <v>0</v>
+        <v>320045.3</v>
       </c>
       <c r="BC119" s="7" t="n">
-        <v>0</v>
+        <v>106063.07</v>
       </c>
       <c r="BD119" s="7" t="n">
-        <v>0</v>
+        <v>666241.8100000001</v>
       </c>
       <c r="BE119" s="7" t="n">
-        <v>0</v>
+        <v>164508.72</v>
       </c>
       <c r="BF119" s="7" t="n">
-        <v>0</v>
+        <v>168270.58</v>
       </c>
       <c r="BG119" s="7" t="n">
-        <v>0</v>
+        <v>103689.92</v>
       </c>
       <c r="BH119" s="7" t="n">
-        <v>0</v>
+        <v>70369.31</v>
       </c>
       <c r="BI119" s="7" t="n">
-        <v>0</v>
+        <v>71213.94</v>
       </c>
       <c r="BJ119" s="7" t="n">
-        <v>0</v>
+        <v>11380.68</v>
       </c>
       <c r="BK119" s="7" t="n">
         <v>0</v>
@@ -49065,28 +49344,28 @@
         <v>0</v>
       </c>
       <c r="BO119" s="7" t="n">
-        <v>0</v>
+        <v>19745.72</v>
       </c>
       <c r="BP119" s="7" t="n">
-        <v>0</v>
+        <v>21277.54</v>
       </c>
       <c r="BQ119" s="7" t="n">
-        <v>0</v>
+        <v>16538.76</v>
       </c>
       <c r="BR119" s="7" t="n">
-        <v>0</v>
+        <v>106535.28</v>
       </c>
       <c r="BS119" s="7" t="n">
-        <v>0</v>
+        <v>80543.75</v>
       </c>
       <c r="BT119" s="7" t="n">
-        <v>0</v>
+        <v>93138.75999999999</v>
       </c>
       <c r="BU119" s="7" t="n">
-        <v>0</v>
+        <v>498838.01</v>
       </c>
       <c r="BV119" s="7" t="n">
-        <v>0</v>
+        <v>245468.81</v>
       </c>
       <c r="BW119" s="7" t="n">
         <v>0</v>
@@ -49143,7 +49422,7 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>170026/003470/2021</t>
+          <t>E-17/026/1514/2019</t>
         </is>
       </c>
       <c r="C120" s="14" t="inlineStr">
@@ -49152,25 +49431,25 @@
         </is>
       </c>
       <c r="D120" s="4" t="n">
-        <v>1298</v>
+        <v>602</v>
       </c>
       <c r="E120" s="6" t="n">
-        <v>44638</v>
+        <v>44791</v>
       </c>
       <c r="F120" s="6" t="n">
-        <v>45936</v>
+        <v>45393</v>
       </c>
       <c r="G120" s="7" t="n">
-        <v>24590858.27</v>
+        <v>16932981.45</v>
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>CONCLUÍDA</t>
+          <t>NÃO CONCLUÍDA</t>
         </is>
       </c>
       <c r="I120" s="4" t="inlineStr">
         <is>
-          <t>ERICK HYLARIO</t>
+          <t>AIMAR FILHO</t>
         </is>
       </c>
       <c r="J120" s="4" t="inlineStr"/>
@@ -49186,23 +49465,23 @@
       </c>
       <c r="M120" s="4" t="inlineStr">
         <is>
-          <t>PETROPUMP</t>
+          <t>VCE PROJETOS</t>
         </is>
       </c>
       <c r="N120" s="7" t="n">
-        <v>1082086.63</v>
+        <v>0</v>
       </c>
       <c r="O120" s="7" t="n">
         <v>0</v>
       </c>
       <c r="P120" s="7" t="n">
-        <v>24590858.27</v>
+        <v>16932981.45</v>
       </c>
       <c r="Q120" s="9" t="n">
-        <v>0.8915999999999999</v>
+        <v>0.5364</v>
       </c>
       <c r="R120" s="7" t="n">
-        <v>2665219.75</v>
+        <v>7850572.78</v>
       </c>
       <c r="S120" s="7" t="n">
         <v>0</v>
@@ -49247,94 +49526,94 @@
         <v>0</v>
       </c>
       <c r="AG120" s="7" t="n">
-        <v>821885</v>
+        <v>0</v>
       </c>
       <c r="AH120" s="7" t="n">
-        <v>666034.7</v>
+        <v>0</v>
       </c>
       <c r="AI120" s="7" t="n">
-        <v>1095907.96</v>
+        <v>0</v>
       </c>
       <c r="AJ120" s="7" t="n">
-        <v>1222093.58</v>
+        <v>0</v>
       </c>
       <c r="AK120" s="7" t="n">
-        <v>2272889.86</v>
+        <v>0</v>
       </c>
       <c r="AL120" s="7" t="n">
-        <v>1932781.91</v>
+        <v>504952.03</v>
       </c>
       <c r="AM120" s="7" t="n">
-        <v>1242290.54</v>
+        <v>1403267.01</v>
       </c>
       <c r="AN120" s="7" t="n">
-        <v>2722433.3</v>
+        <v>0</v>
       </c>
       <c r="AO120" s="7" t="n">
-        <v>405050.42</v>
+        <v>0</v>
       </c>
       <c r="AP120" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AQ120" s="7" t="n">
-        <v>0</v>
+        <v>1990376.22</v>
       </c>
       <c r="AR120" s="7" t="n">
-        <v>1642646.17</v>
+        <v>2880472.76</v>
       </c>
       <c r="AS120" s="7" t="n">
-        <v>0</v>
+        <v>1278952.46</v>
       </c>
       <c r="AT120" s="7" t="n">
-        <v>0</v>
+        <v>989161.5699999999</v>
       </c>
       <c r="AU120" s="7" t="n">
-        <v>806289.21</v>
+        <v>7064.64</v>
       </c>
       <c r="AV120" s="7" t="n">
-        <v>242831.56</v>
+        <v>5884.18</v>
       </c>
       <c r="AW120" s="7" t="n">
-        <v>0</v>
+        <v>5569.45</v>
       </c>
       <c r="AX120" s="7" t="n">
-        <v>0</v>
+        <v>5569.45</v>
       </c>
       <c r="AY120" s="7" t="n">
-        <v>0</v>
+        <v>5569.45</v>
       </c>
       <c r="AZ120" s="7" t="n">
-        <v>2616751.77</v>
+        <v>5569.45</v>
       </c>
       <c r="BA120" s="7" t="n">
-        <v>1471882.58</v>
+        <v>0</v>
       </c>
       <c r="BB120" s="7" t="n">
-        <v>320045.3</v>
+        <v>0</v>
       </c>
       <c r="BC120" s="7" t="n">
-        <v>106063.07</v>
+        <v>0</v>
       </c>
       <c r="BD120" s="7" t="n">
-        <v>666241.8100000001</v>
+        <v>0</v>
       </c>
       <c r="BE120" s="7" t="n">
-        <v>164508.72</v>
+        <v>0</v>
       </c>
       <c r="BF120" s="7" t="n">
-        <v>168270.58</v>
+        <v>0</v>
       </c>
       <c r="BG120" s="7" t="n">
-        <v>103689.92</v>
+        <v>0</v>
       </c>
       <c r="BH120" s="7" t="n">
-        <v>70369.31</v>
+        <v>0</v>
       </c>
       <c r="BI120" s="7" t="n">
-        <v>71213.94</v>
+        <v>0</v>
       </c>
       <c r="BJ120" s="7" t="n">
-        <v>11380.68</v>
+        <v>0</v>
       </c>
       <c r="BK120" s="7" t="n">
         <v>0</v>
@@ -49349,28 +49628,28 @@
         <v>0</v>
       </c>
       <c r="BO120" s="7" t="n">
-        <v>19745.72</v>
+        <v>0</v>
       </c>
       <c r="BP120" s="7" t="n">
-        <v>21277.54</v>
+        <v>0</v>
       </c>
       <c r="BQ120" s="7" t="n">
-        <v>16538.76</v>
+        <v>0</v>
       </c>
       <c r="BR120" s="7" t="n">
-        <v>106535.28</v>
+        <v>0</v>
       </c>
       <c r="BS120" s="7" t="n">
-        <v>80543.75</v>
+        <v>0</v>
       </c>
       <c r="BT120" s="7" t="n">
-        <v>93138.75999999999</v>
+        <v>0</v>
       </c>
       <c r="BU120" s="7" t="n">
-        <v>498838.01</v>
+        <v>0</v>
       </c>
       <c r="BV120" s="7" t="n">
-        <v>245468.81</v>
+        <v>0</v>
       </c>
       <c r="BW120" s="7" t="n">
         <v>0</v>
@@ -49418,290 +49697,6 @@
         <v>0</v>
       </c>
       <c r="CL120" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="B121" s="4" t="inlineStr">
-        <is>
-          <t>E-17/026/1514/2019</t>
-        </is>
-      </c>
-      <c r="C121" s="14" t="inlineStr">
-        <is>
-          <t>ESPECIAIS</t>
-        </is>
-      </c>
-      <c r="D121" s="4" t="n">
-        <v>602</v>
-      </c>
-      <c r="E121" s="6" t="n">
-        <v>44791</v>
-      </c>
-      <c r="F121" s="6" t="n">
-        <v>45393</v>
-      </c>
-      <c r="G121" s="7" t="n">
-        <v>16932981.45</v>
-      </c>
-      <c r="H121" s="4" t="inlineStr">
-        <is>
-          <t>NÃO CONCLUÍDA</t>
-        </is>
-      </c>
-      <c r="I121" s="4" t="inlineStr">
-        <is>
-          <t>AIMAR FILHO</t>
-        </is>
-      </c>
-      <c r="J121" s="4" t="inlineStr"/>
-      <c r="K121" s="12" t="inlineStr">
-        <is>
-          <t>MT</t>
-        </is>
-      </c>
-      <c r="L121" s="4" t="inlineStr">
-        <is>
-          <t>Rio de Janeiro</t>
-        </is>
-      </c>
-      <c r="M121" s="4" t="inlineStr">
-        <is>
-          <t>VCE PROJETOS</t>
-        </is>
-      </c>
-      <c r="N121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P121" s="7" t="n">
-        <v>16932981.45</v>
-      </c>
-      <c r="Q121" s="9" t="n">
-        <v>0.5364</v>
-      </c>
-      <c r="R121" s="7" t="n">
-        <v>7850572.78</v>
-      </c>
-      <c r="S121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL121" s="7" t="n">
-        <v>504952.03</v>
-      </c>
-      <c r="AM121" s="7" t="n">
-        <v>1403267.01</v>
-      </c>
-      <c r="AN121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ121" s="7" t="n">
-        <v>1990376.22</v>
-      </c>
-      <c r="AR121" s="7" t="n">
-        <v>2880472.76</v>
-      </c>
-      <c r="AS121" s="7" t="n">
-        <v>1278952.46</v>
-      </c>
-      <c r="AT121" s="7" t="n">
-        <v>989161.5699999999</v>
-      </c>
-      <c r="AU121" s="7" t="n">
-        <v>7064.64</v>
-      </c>
-      <c r="AV121" s="7" t="n">
-        <v>5884.18</v>
-      </c>
-      <c r="AW121" s="7" t="n">
-        <v>5569.45</v>
-      </c>
-      <c r="AX121" s="7" t="n">
-        <v>5569.45</v>
-      </c>
-      <c r="AY121" s="7" t="n">
-        <v>5569.45</v>
-      </c>
-      <c r="AZ121" s="7" t="n">
-        <v>5569.45</v>
-      </c>
-      <c r="BA121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL121" s="7" t="n">
         <v>0</v>
       </c>
     </row>

--- a/MEDIÇÕES_CONSOLIDADO.xlsx
+++ b/MEDIÇÕES_CONSOLIDADO.xlsx
@@ -9586,7 +9586,7 @@
         <v>2715707.77</v>
       </c>
       <c r="N32" s="7" t="n">
-        <v>0</v>
+        <v>905475.02</v>
       </c>
       <c r="O32" s="7" t="n">
         <v>22825141.32</v>
@@ -9778,7 +9778,7 @@
         <v>392686.6</v>
       </c>
       <c r="BZ32" s="7" t="n">
-        <v>0</v>
+        <v>905475.02</v>
       </c>
       <c r="CA32" s="7" t="n">
         <v>0</v>

--- a/MEDIÇÕES_CONSOLIDADO.xlsx
+++ b/MEDIÇÕES_CONSOLIDADO.xlsx
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="M14" s="7" t="n">
-        <v>0</v>
+        <v>842876.36</v>
       </c>
       <c r="N14" s="7" t="n">
-        <v>0</v>
+        <v>1284711.9</v>
       </c>
       <c r="O14" s="7" t="n">
         <v>7848019.53</v>
@@ -4681,10 +4681,10 @@
         <v>0</v>
       </c>
       <c r="BY14" s="7" t="n">
-        <v>0</v>
+        <v>842876.36</v>
       </c>
       <c r="BZ14" s="7" t="n">
-        <v>0</v>
+        <v>1284711.9</v>
       </c>
       <c r="CA14" s="7" t="n">
         <v>0</v>
@@ -15236,7 +15236,7 @@
         <v>55173009.47</v>
       </c>
       <c r="N52" s="7" t="n">
-        <v>1537890.45</v>
+        <v>5219382.56</v>
       </c>
       <c r="O52" s="7" t="n">
         <v>74609626.42</v>
@@ -15431,7 +15431,7 @@
         <v>1537890.45</v>
       </c>
       <c r="CA52" s="7" t="n">
-        <v>0</v>
+        <v>3681492.11</v>
       </c>
       <c r="CB52" s="7" t="n">
         <v>0</v>

--- a/MEDIÇÕES_CONSOLIDADO.xlsx
+++ b/MEDIÇÕES_CONSOLIDADO.xlsx
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="M14" s="7" t="n">
-        <v>842876.36</v>
+        <v>0</v>
       </c>
       <c r="N14" s="7" t="n">
-        <v>1284711.9</v>
+        <v>0</v>
       </c>
       <c r="O14" s="7" t="n">
         <v>7848019.53</v>
@@ -4681,10 +4681,10 @@
         <v>0</v>
       </c>
       <c r="BY14" s="7" t="n">
-        <v>842876.36</v>
+        <v>0</v>
       </c>
       <c r="BZ14" s="7" t="n">
-        <v>1284711.9</v>
+        <v>0</v>
       </c>
       <c r="CA14" s="7" t="n">
         <v>0</v>
@@ -9869,7 +9869,7 @@
         <v>3253833.79</v>
       </c>
       <c r="N33" s="7" t="n">
-        <v>0</v>
+        <v>458840.15</v>
       </c>
       <c r="O33" s="7" t="n">
         <v>26504288.68</v>
@@ -10061,10 +10061,10 @@
         <v>129126.61</v>
       </c>
       <c r="BZ33" s="7" t="n">
-        <v>0</v>
+        <v>228840.15</v>
       </c>
       <c r="CA33" s="7" t="n">
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="CB33" s="7" t="n">
         <v>0</v>
@@ -13538,7 +13538,7 @@
         <v>10511270.47</v>
       </c>
       <c r="N46" s="7" t="n">
-        <v>206846.35</v>
+        <v>673703.46</v>
       </c>
       <c r="O46" s="7" t="n">
         <v>12432476.25</v>
@@ -13733,7 +13733,7 @@
         <v>206846.35</v>
       </c>
       <c r="CA46" s="7" t="n">
-        <v>0</v>
+        <v>466857.11</v>
       </c>
       <c r="CB46" s="7" t="n">
         <v>0</v>

--- a/MEDIÇÕES_CONSOLIDADO.xlsx
+++ b/MEDIÇÕES_CONSOLIDADO.xlsx
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="M14" s="7" t="n">
-        <v>0</v>
+        <v>842876.36</v>
       </c>
       <c r="N14" s="7" t="n">
-        <v>0</v>
+        <v>1284711.9</v>
       </c>
       <c r="O14" s="7" t="n">
         <v>7848019.53</v>
@@ -4681,10 +4681,10 @@
         <v>0</v>
       </c>
       <c r="BY14" s="7" t="n">
-        <v>0</v>
+        <v>842876.36</v>
       </c>
       <c r="BZ14" s="7" t="n">
-        <v>0</v>
+        <v>1284711.9</v>
       </c>
       <c r="CA14" s="7" t="n">
         <v>0</v>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>JAQUELINE PASTÓRIO</t>
+          <t>IGOR MARTINS</t>
         </is>
       </c>
       <c r="J17" s="8" t="inlineStr">
@@ -8171,7 +8171,7 @@
         <v>425261.4</v>
       </c>
       <c r="N27" s="7" t="n">
-        <v>0</v>
+        <v>64834.03</v>
       </c>
       <c r="O27" s="7" t="n">
         <v>544550.48</v>
@@ -8363,7 +8363,7 @@
         <v>0</v>
       </c>
       <c r="BZ27" s="7" t="n">
-        <v>0</v>
+        <v>64834.03</v>
       </c>
       <c r="CA27" s="7" t="n">
         <v>0</v>
@@ -31040,7 +31040,7 @@
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>NICHOLAS TAVARES / OTAVIO FEITOSA</t>
+          <t>HIGOR GAMA / OTAVIO FEITOSA</t>
         </is>
       </c>
       <c r="K55" s="8" t="inlineStr">
@@ -33332,7 +33332,7 @@
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>ARLINDO BASILIO / OTAVIO FEITOSA</t>
+          <t>LUCIANA POSTIÇO / OTAVIO FEITOSA</t>
         </is>
       </c>
       <c r="K63" s="11" t="inlineStr">
@@ -45209,7 +45209,7 @@
         </is>
       </c>
       <c r="N105" s="7" t="n">
-        <v>666913.6800000001</v>
+        <v>666913.6899999999</v>
       </c>
       <c r="O105" s="7" t="n">
         <v>0</v>
@@ -45380,7 +45380,7 @@
         <v>0</v>
       </c>
       <c r="BS105" s="7" t="n">
-        <v>54982.84</v>
+        <v>54982.85</v>
       </c>
       <c r="BT105" s="7" t="n">
         <v>0</v>

--- a/MEDIÇÕES_CONSOLIDADO.xlsx
+++ b/MEDIÇÕES_CONSOLIDADO.xlsx
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="M14" s="7" t="n">
-        <v>842876.36</v>
+        <v>0</v>
       </c>
       <c r="N14" s="7" t="n">
-        <v>1284711.9</v>
+        <v>0</v>
       </c>
       <c r="O14" s="7" t="n">
         <v>7848019.53</v>
@@ -4681,10 +4681,10 @@
         <v>0</v>
       </c>
       <c r="BY14" s="7" t="n">
-        <v>842876.36</v>
+        <v>0</v>
       </c>
       <c r="BZ14" s="7" t="n">
-        <v>1284711.9</v>
+        <v>0</v>
       </c>
       <c r="CA14" s="7" t="n">
         <v>0</v>
@@ -5058,7 +5058,7 @@
         <v>10584628.26</v>
       </c>
       <c r="N16" s="7" t="n">
-        <v>519586.74</v>
+        <v>1199631.94</v>
       </c>
       <c r="O16" s="7" t="n">
         <v>48872552.26</v>
@@ -5253,7 +5253,7 @@
         <v>519586.74</v>
       </c>
       <c r="CA16" s="7" t="n">
-        <v>0</v>
+        <v>680045.2</v>
       </c>
       <c r="CB16" s="7" t="n">
         <v>0</v>
@@ -46348,7 +46348,7 @@
         <v>710964.03</v>
       </c>
       <c r="O109" s="7" t="n">
-        <v>0</v>
+        <v>294655.66</v>
       </c>
       <c r="P109" s="7" t="n">
         <v>13554947.83</v>
@@ -46486,7 +46486,7 @@
         <v>712517.77</v>
       </c>
       <c r="BI109" s="7" t="n">
-        <v>528677.09</v>
+        <v>528577.09</v>
       </c>
       <c r="BJ109" s="7" t="n">
         <v>598849.04</v>
@@ -46540,7 +46540,7 @@
         <v>0</v>
       </c>
       <c r="CA109" s="7" t="n">
-        <v>0</v>
+        <v>294655.66</v>
       </c>
       <c r="CB109" s="7" t="n">
         <v>0</v>

--- a/MEDIÇÕES_CONSOLIDADO.xlsx
+++ b/MEDIÇÕES_CONSOLIDADO.xlsx
@@ -3900,7 +3900,11 @@
           <t>EXECUÇÃO</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr"/>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>ISADORA ROSALINO</t>
+        </is>
+      </c>
       <c r="J12" s="10" t="inlineStr">
         <is>
           <t>NT</t>
@@ -5592,7 +5596,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>IGOR MARTINS</t>
+          <t>JAQUELINE PASTÓRIO</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -16883,8 +16887,16 @@
           <t>NÃO CONCLUÍDA</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr"/>
-      <c r="J3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>CARLOS FERNANDES</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>ANDERSON / OTAVIO FEITOSA</t>
+        </is>
+      </c>
       <c r="K3" s="11" t="inlineStr">
         <is>
           <t>BX</t>
@@ -17163,8 +17175,16 @@
           <t>NÃO CONCLUÍDA</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>CARLOS FERNANDES</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>ANDERSON / OTAVIO FEITOSA</t>
+        </is>
+      </c>
       <c r="K4" s="11" t="inlineStr">
         <is>
           <t>BX</t>
@@ -17450,7 +17470,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>NICHOLAS TAVARES / OTAVIO FEITOSA</t>
+          <t>ANDERSON / OTAVIO FEITOSA</t>
         </is>
       </c>
       <c r="K5" s="11" t="inlineStr">
@@ -19711,8 +19731,16 @@
           <t>CONCLUÍDA</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr"/>
-      <c r="J13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>CARLOS FERNANDES</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>ANDERSON / OTAVIO FEITOSA</t>
+        </is>
+      </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
           <t>SL</t>
@@ -23394,7 +23422,7 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>NICHOLAS TAVARES / OTAVIO FEITOSA</t>
+          <t>ANDERSON / OTAVIO FEITOSA</t>
         </is>
       </c>
       <c r="K26" s="11" t="inlineStr">
@@ -29881,10 +29909,14 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>GISELLE G. FONSECA</t>
-        </is>
-      </c>
-      <c r="J49" s="4" t="inlineStr"/>
+          <t>CARLOS FERNANDES</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>ANDERSON / OTAVIO FEITOSA</t>
+        </is>
+      </c>
       <c r="K49" s="11" t="inlineStr">
         <is>
           <t>BX</t>
@@ -31586,7 +31618,7 @@
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>HIGOR GAMA / OTAVIO FEITOSA</t>
+          <t>HIGOR GAMA / JOAO JOSE</t>
         </is>
       </c>
       <c r="K55" s="8" t="inlineStr">
@@ -33018,7 +33050,7 @@
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>NICHOLAS TAVARES / ARLINDO BASILIO</t>
+          <t>ANDERSON / OTAVIO FEITOSA</t>
         </is>
       </c>
       <c r="K60" s="11" t="inlineStr">
@@ -33306,7 +33338,7 @@
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>ARLINDO BASILIO / OTAVIO FEITOSA</t>
+          <t>ANDERSON / OTAVIO FEITOSA</t>
         </is>
       </c>
       <c r="K61" s="11" t="inlineStr">
@@ -33878,7 +33910,7 @@
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>LUCIANA POSTIÇO / OTAVIO FEITOSA</t>
+          <t>HIGOR GAMA / JOAO JOSE</t>
         </is>
       </c>
       <c r="K63" s="11" t="inlineStr">
@@ -38680,7 +38712,7 @@
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>NICHOLAS TAVARES / OSVALDO NETO</t>
+          <t>ANDERSON / OTAVIO FEITOSA</t>
         </is>
       </c>
       <c r="K80" s="11" t="inlineStr">
@@ -39243,12 +39275,12 @@
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>JEHNIFFER PIRES</t>
+          <t>GISELLE G. FONSECA</t>
         </is>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>LUCIANA POSTIÇO / ARLINDO BASILIO</t>
+          <t>HIGOR GAMA / JOAO JOSE</t>
         </is>
       </c>
       <c r="K82" s="8" t="inlineStr">
@@ -50257,7 +50289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50395,394 +50427,346 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>330018/000424/2021</t>
+          <t>170026/001865/2021</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ALBERTO COUTO ALVES - BRASIL LTDA.</t>
+          <t>SANTA LUZIA ENGENHARIA E CONSTRUCOES LTDA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>330018/000423/2021</t>
+          <t>330018/000235/2020</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ALBERTO COUTO ALVES - BRASIL LTDA.</t>
+          <t>CRATER CONSTRUÇÕES LTDA.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>170026/001178/2021</t>
+          <t>170026/001229/2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>COLÔNIA ARQUITETURA E CONSTRUÇÃO EIRELI EPP</t>
+          <t>BARRA NOVA ENGENHARIA LTDA</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>170026/001865/2021</t>
+          <t>170026/001230/2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SANTA LUZIA ENGENHARIA E CONSTRUCOES LTDA</t>
+          <t>RIVALL ENGENHARIA LTDA</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>330018/000235/2020</t>
+          <t>170026/001231/2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CRATER CONSTRUÇÕES LTDA.</t>
+          <t>ECONORTE, MEIO AMBIENTE, INFRAESTRUTURA E SERVIÇOS LTDA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>170026/001229/2022</t>
+          <t>170026/002388/2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BARRA NOVA ENGENHARIA LTDA</t>
+          <t>WTE ENGENHARIA EIRELI</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>170026/001230/2022</t>
+          <t>330018/000712/2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RIVALL ENGENHARIA LTDA</t>
+          <t>SEEL SERVICOS ESPECIAIS DE ENGENHARIA LTDA</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>170026/001231/2022</t>
+          <t>330018/001017/2021</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ECONORTE, MEIO AMBIENTE, INFRAESTRUTURA E SERVIÇOS LTDA</t>
+          <t>NOVACAP ENGENHARIA, INDUSTRIS E COMERCIO LTDA</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>170026/002388/2021</t>
+          <t>170026/000549/2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WTE ENGENHARIA EIRELI</t>
+          <t>BARRA NOVA ENGENHARIA LTDA</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>330001/001238/2025</t>
+          <t>170026/001072/2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ENEX CONSTRUÇÕES LTDA</t>
+          <t>COORDENA COORDENAÇÃO DE PROJETOS LTDA</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>330018/000712/2021</t>
+          <t>170026/000548/2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SEEL SERVICOS ESPECIAIS DE ENGENHARIA LTDA</t>
+          <t>ENGE PRAT ENGENHARIA E SERVICOS LTDA.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>330018/001017/2021</t>
+          <t>170026/000537/2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NOVACAP ENGENHARIA, INDUSTRIS E COMERCIO LTDA</t>
+          <t>ERWIL CONSTRUÇÕES LTDA</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>170026/000549/2022</t>
+          <t>170026/000545/2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BARRA NOVA ENGENHARIA LTDA</t>
+          <t>GEOLOGUS ENGENHARIA LTDA</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>170026/001072/2022</t>
+          <t>170026/000539/2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>COORDENA COORDENAÇÃO DE PROJETOS LTDA</t>
+          <t>CONSTRUTORA SOLIDUM  LTDA</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>170026/000548/2022</t>
+          <t>330018/000580/2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ENGE PRAT ENGENHARIA E SERVICOS LTDA.</t>
+          <t>MEDEIROS E MEDEIROS CIVIL E MONTAGEM LTDA-ME</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>170026/000537/2022</t>
+          <t>170026/001303/2020</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ERWIL CONSTRUÇÕES LTDA</t>
+          <t>WTE ENGENHARIA EIRELI</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>170026/000545/2022</t>
+          <t>170026/001868/2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GEOLOGUS ENGENHARIA LTDA</t>
+          <t>WTE ENGENHARIA EIRELI</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>170026/000539/2022</t>
+          <t>330018/001037/2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CONSTRUTORA SOLIDUM  LTDA</t>
+          <t>COMAL CONSTRUTORA LTDA</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>330018/000580/2022</t>
+          <t>170026/002018/2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MEDEIROS E MEDEIROS CIVIL E MONTAGEM LTDA-ME</t>
+          <t>DE SÁ CONSTRUÇÕES E SERVIÇOS LTDA</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>170026/001303/2020</t>
+          <t>170026/000379/2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>WTE ENGENHARIA EIRELI</t>
+          <t>GEOMECÂNICA S/A TECNOLOGIA DE SOLOS ROCHAS E MATERIAIS LTDA</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>170026/001868/2021</t>
+          <t>e-17/026/1892/2019-2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>WTE ENGENHARIA EIRELI</t>
+          <t>FAB MIX CONCRETOS LTDA</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>330018/001037/2021</t>
+          <t>e-17/026/1892/2019-1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>COMAL CONSTRUTORA LTDA</t>
+          <t>METALURGICA BIG FARM LTDA</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>170026/002018/2021</t>
+          <t>170026/001763/2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DE SÁ CONSTRUÇÕES E SERVIÇOS LTDA</t>
+          <t>COMPASS - BUILD CONTROL LTDA</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>170026/000379/2022</t>
+          <t>E-17/001/81/2013</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GEOMECÂNICA S/A TECNOLOGIA DE SOLOS ROCHAS E MATERIAIS LTDA</t>
+          <t>SEVEME INDUSTRIAS METALURGICAS S.A.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>e-17/026/1892/2019-2</t>
+          <t>330001/000434/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FAB MIX CONCRETOS LTDA</t>
+          <t>Não existe na tabela Contratadas</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>e-17/026/1892/2019-1</t>
+          <t>330001/000113/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>METALURGICA BIG FARM LTDA</t>
+          <t>Não existe na tabela Contratadas</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>170026/001763/2021</t>
+          <t>330001/001152/2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>COMPASS - BUILD CONTROL LTDA</t>
+          <t>Não existe na tabela Contratadas</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>E-17/001/81/2013</t>
+          <t>330018/000559/2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SEVEME INDUSTRIAS METALURGICAS S.A.</t>
+          <t>CONSTRUTORA METROPOLITANA S A</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>330001/000434/2026</t>
+          <t>330018/000221/2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
-        <is>
-          <t>Não existe na tabela Contratadas</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>330001/000113/2026</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Não existe na tabela Contratadas</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>330001/001152/2025</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Não existe na tabela Contratadas</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>330018/000559/2022</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>CONSTRUTORA METROPOLITANA S A</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>330018/000221/2022</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
         <is>
           <t>CONSTRUTORA LYTORANEA S A</t>
         </is>
